--- a/Result/checksun_type/酚醛樹脂.xlsx
+++ b/Result/checksun_type/酚醛樹脂.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6136.175</t>
+          <t>13085.646</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>11.70</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>42.31</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>41.19</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>39.51000000000001</t>
+          <t>39.57000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>39.76</t>
+          <t>39.78</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.87</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-36.08</t>
+          <t>-28.47</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-104.19</t>
+          <t>-104.51</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>206045136.894356</t>
+          <t>206901190.2919075</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>240426749.0</t>
+          <t>532289392.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>234858276.4</t>
+          <t>317585660.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>236240878.5</t>
+          <t>263274442.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>679732391.62</t>
+          <t>673739372.28</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1382602</t>
+          <t>54311217</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-40673808.27865538</t>
+          <t>-39813408.42361735</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-60282226.95</v>
+        <v>-35081209.22</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,42 +1177,42 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.829816337462134</t>
+          <t>-9.48290326317574</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-15.00614046121911</t>
+          <t>-12.03721295307491</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-7.407597612834184</t>
+          <t>-7.644513672598537</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>25.79</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>45659</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6635.823</t>
+          <t>6136.175</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-17.42</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.80</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.51000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>39.76</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>41.14</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>38.33</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>-36.08</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-103.81</t>
+          <t>-104.19</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>206045136.894356</t>
+          <t>206901190.2919075</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>267989366.0</t>
+          <t>240426749.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>223432348.8</t>
+          <t>234858276.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>270578244.9</t>
+          <t>236240878.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>693037521.34</t>
+          <t>679732391.62</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-47145896</t>
+          <t>-1382602</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-37108641.24703376</t>
+          <t>-40673808.27865538</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-62859746.71</v>
+        <v>-60282226.95</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>40.61</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,42 +1608,42 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.829816337462134</t>
+          <t>-9.48290326317574</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-15.00614046121911</t>
+          <t>-12.03721295307491</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-7.407597612834184</t>
+          <t>-7.644513672598537</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>25.79</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>45659</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5872.775</t>
+          <t>6635.823</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-33.41</t>
+          <t>-17.42</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>77.42</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>7.80</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>39.52</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>39.78</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.14</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>38.16</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-40.75</t>
+          <t>-11.77</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-103.70</t>
+          <t>-103.81</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>206045136.894356</t>
+          <t>206901190.2919075</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>235105290.0</t>
+          <t>267989366.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>211553687.2</t>
+          <t>223432348.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>317718579.4</t>
+          <t>270578244.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>694915339.42</t>
+          <t>693037521.34</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-106164892</t>
+          <t>-47145896</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-32426622.07125968</t>
+          <t>-37108641.24703376</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-67250064.38</v>
+        <v>-62859746.71</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>43.86</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,42 +2039,42 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.829816337462134</t>
+          <t>-9.48290326317574</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-15.00614046121911</t>
+          <t>-12.03721295307491</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-7.407597612834184</t>
+          <t>-7.644513672598537</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>25.79</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>45659</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7951.184</t>
+          <t>5872.775</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-50.07</t>
+          <t>-33.41</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>48.72</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>28.81</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.52</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.98</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-72.18</t>
+          <t>-40.75</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-103.32</t>
+          <t>-103.70</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>206045136.894356</t>
+          <t>206901190.2919075</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>312117506.0</t>
+          <t>235105290.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>220149093.2</t>
+          <t>211553687.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>440884400.6</t>
+          <t>317718579.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>697689583.68</t>
+          <t>694915339.42</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-220735307</t>
+          <t>-106164892</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-26095087.10550797</t>
+          <t>-32426622.07125968</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-67596864.90000001</v>
+        <v>-67250064.38</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>42.60</t>
+          <t>43.86</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,42 +2470,42 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.829816337462134</t>
+          <t>-9.48290326317574</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-15.00614046121911</t>
+          <t>-12.03721295307491</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-7.407597612834184</t>
+          <t>-7.644513672598537</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>25.79</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>45659</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,109 +2602,109 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7951.184</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-2.52</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-50.07</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>39.25</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>40.85</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
           <t>0.64</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>3041.179</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>39.15</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-1.82</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-66.98</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>27.6</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>40.85</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
       <c r="X6" t="inlineStr">
         <is>
           <t>4.04</t>
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>41.34</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>37.61</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-99.28</t>
+          <t>-72.18</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-102.72</t>
+          <t>-103.32</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>206045136.894356</t>
+          <t>206901190.2919075</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>118652471.0</t>
+          <t>312117506.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>208963225.0</t>
+          <t>220149093.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>632911197.7</t>
+          <t>440884400.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>701089842.98</t>
+          <t>697689583.68</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-423947972</t>
+          <t>-220735307</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-18549309.32532593</t>
+          <t>-26095087.10550797</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-73929429.31</v>
+        <v>-67596864.90000001</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>41.34</t>
+          <t>42.60</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.829816337462134</t>
+          <t>-9.48290326317574</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-15.00614046121911</t>
+          <t>-12.03721295307491</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-7.407597612834184</t>
+          <t>-7.644513672598537</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>25.79</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>45659</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4678.818</t>
+          <t>3041.179</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-64.91</t>
+          <t>-66.98</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>39.47</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>39.96</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.34</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>37.43</t>
+          <t>37.61</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-100.53</t>
+          <t>-99.28</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-102.05</t>
+          <t>-102.72</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>206045136.894356</t>
+          <t>206901190.2919075</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>183297111.0</t>
+          <t>118652471.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>237623480.6</t>
+          <t>208963225.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>677103255.3</t>
+          <t>632911197.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>708421794.36</t>
+          <t>701089842.98</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-439479774</t>
+          <t>-423947972</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-8480196.600382902</t>
+          <t>-18549309.32532593</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-59607216.54</v>
+        <v>-73929429.31</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>41.34</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,27 +3332,27 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.829816337462134</t>
+          <t>-9.48290326317574</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-15.00614046121911</t>
+          <t>-12.03721295307491</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-7.407597612834184</t>
+          <t>-7.644513672598537</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>25.79</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>45659</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5259.933</t>
+          <t>4678.818</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-53.20</t>
+          <t>-64.91</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>26.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>39.96</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>41.47</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>37.24</t>
+          <t>37.43</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-100.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-101.53</t>
+          <t>-102.05</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>206045136.894356</t>
+          <t>206901190.2919075</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>208596058.0</t>
+          <t>183297111.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>317724141.0</t>
+          <t>237623480.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>678874486.1</t>
+          <t>677103255.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>711908904.88</t>
+          <t>708421794.36</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-361150345</t>
+          <t>-439479774</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>815625.206547319</t>
+          <t>-8480196.600382902</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-43944294.84</v>
+        <v>-59607216.54</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,42 +3763,42 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.829816337462134</t>
+          <t>-9.48290326317574</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-15.00614046121911</t>
+          <t>-12.03721295307491</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-7.407597612834184</t>
+          <t>-7.644513672598537</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>25.79</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>45659</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7140.111</t>
+          <t>5259.933</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,72 +3910,72 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>40.2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-1.9</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-2.52</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-53.20</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>39.25</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-0.77</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-1.82</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-36.72</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,52 +4026,52 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>26.76</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>31.82</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>40.06</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4081,17 +4081,17 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>37.24</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-29.31</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-101.48</t>
+          <t>-101.53</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,45 +4116,45 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>206045136.894356</t>
+          <t>206901190.2919075</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>278082320.0</t>
+          <t>208596058.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>423883471.6</t>
+          <t>317724141.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>669852008.1</t>
+          <t>678874486.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>715483441.44</t>
+          <t>711908904.88</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-245968536</t>
+          <t>-361150345</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>8953792.488120452</t>
+          <t>815625.206547319</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-22709854.78</v>
+        <v>-43944294.84</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>41.70</t>
+          <t>45.13</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,42 +4194,42 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.829816337462134</t>
+          <t>-9.48290326317574</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-15.00614046121911</t>
+          <t>-12.03721295307491</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-7.407597612834184</t>
+          <t>-7.644513672598537</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>25.79</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>45659</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6398.955</t>
+          <t>7140.111</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-36.72</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,72 +4457,72 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
+          <t>28.28</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
           <t>40.4</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>51.18</t>
-        </is>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>12.67</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>40.84</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>40.26</t>
+          <t>40.14</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>41.52</t>
+          <t>41.47</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>117.63</t>
+          <t>-29.31</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.37</t>
+          <t>-101.48</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>206045136.894356</t>
+          <t>206901190.2919075</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>256188165.0</t>
+          <t>278082320.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>661619708.0</t>
+          <t>423883471.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>663664779.1</t>
+          <t>669852008.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>720815035.62</t>
+          <t>715483441.44</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2045071</t>
+          <t>-245968536</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>14710819.26440901</t>
+          <t>8953792.488120452</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>991169.1899999999</v>
+        <v>-22709854.78</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>43.86</t>
+          <t>41.70</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,27 +4625,27 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.829816337462134</t>
+          <t>-9.48290326317574</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-15.00614046121911</t>
+          <t>-12.03721295307491</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-7.407597612834184</t>
+          <t>-7.644513672598537</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>25.79</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>45659</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6429.228</t>
+          <t>6398.955</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>60.63</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>55.89</t>
+          <t>51.18</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>12.67</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>40.84</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.26</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.52</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>184.79</t>
+          <t>117.63</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-101.78</t>
+          <t>-101.37</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>206045136.894356</t>
+          <t>206901190.2919075</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>261953749.0</t>
+          <t>256188165.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1056859170.4</t>
+          <t>661619708.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>657954566.6</t>
+          <t>663664779.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>735264469.26</t>
+          <t>720815035.62</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>398904603</t>
+          <t>-2045071</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>17205301.09608119</t>
+          <t>14710819.26440901</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>37160178.29</v>
+        <v>991169.1899999999</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>43.86</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.829816337462134</t>
+          <t>-9.48290326317574</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-15.00614046121911</t>
+          <t>-12.03721295307491</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-7.407597612834184</t>
+          <t>-7.644513672598537</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>25.79</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>45659</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>14109.347</t>
+          <t>6429.228</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,92 +5203,92 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>40.45</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-2.53</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-2.52</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>60.63</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>39.25</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>40.85</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-4.88</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-1.82</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>71.03</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>27.6</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>40.85</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>60.61</t>
+          <t>52.53</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>55.89</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>40.33</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>41.58</t>
+          <t>41.54</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>162.06</t>
+          <t>184.79</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.60</t>
+          <t>-101.78</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>206045136.894356</t>
+          <t>206901190.2919075</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>583800413.0</t>
+          <t>261953749.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1116583030.0</t>
+          <t>1056859170.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>652843622.8</t>
+          <t>657954566.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>821538035.32</t>
+          <t>735264469.26</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>463739407</t>
+          <t>398904603</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>13577141.60703838</t>
+          <t>17205301.09608119</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>86885300.91</v>
+        <v>37160178.29</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,22 +5487,22 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.829816337462134</t>
+          <t>-9.48290326317574</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-15.00614046121911</t>
+          <t>-12.03721295307491</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-7.407597612834184</t>
+          <t>-7.644513672598537</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>25.79</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>45659</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>235389.305</t>
+          <t>216309.874</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>73.90</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>64.20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1,171</t>
+          <t>1,160</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>235389</t>
+          <t>216310</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.62</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>41.17</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>104.45</t>
+          <t>91.69</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-55.23</t>
+          <t>-41.91</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,27 +5840,27 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1208553772.146165</t>
+          <t>1234133851.987717</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>12847401961.0</t>
+          <t>12606646015.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>9374723094.8</t>
+          <t>11463824233.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>5390815186.5</t>
+          <t>6558502593.2</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>2722439698.1</t>
+          <t>2879764455.78</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -5870,15 +5870,15 @@
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>563495307.060791</t>
+          <t>790537525.8613333</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>1918555066.05</v>
+        <v>2039269729.26</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>32.70</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5923,37 +5923,37 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>-1.417668633394819</t>
+          <t>-4.249662585945642</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-7.171298548667624</t>
+          <t>-6.718506037644686</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>1.906817985210032</t>
+          <t>1.146736876787111</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>440954</t>
+          <t>448091</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>336947.705</t>
+          <t>235389.305</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>70.38</t>
+          <t>73.90</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>22.74</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1,171</t>
+          <t>1,160</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>235389</t>
+          <t>216310</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>43.19</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.17</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>105.78</t>
+          <t>104.45</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-66.92</t>
+          <t>-55.23</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,27 +6271,27 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1208553772.146165</t>
+          <t>1234133851.987717</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>17904603214.0</t>
+          <t>12847401961.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>7326001062.4</t>
+          <t>9374723094.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>4299803431.4</t>
+          <t>5390815186.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>2525457286.94</t>
+          <t>2722439698.1</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -6301,15 +6301,15 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>317120805.4261836</t>
+          <t>563495307.060791</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>1651790443.46</v>
+        <v>1918555066.05</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>28.40</t>
+          <t>32.70</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6354,17 +6354,17 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>-1.417668633394819</t>
+          <t>-4.249662585945642</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-7.171298548667624</t>
+          <t>-6.718506037644686</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>1.906817985210032</t>
+          <t>1.146736876787111</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
@@ -6374,17 +6374,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>440954</t>
+          <t>448091</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>174611.856</t>
+          <t>336947.705</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>51.82</t>
+          <t>70.38</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6591,33 +6591,33 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>51.82</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1,171</t>
+          <t>1,160</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>235389</t>
+          <t>216310</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>44.51000000000001</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>43.19</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>105.78</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-75.67</t>
+          <t>-66.92</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,45 +6702,45 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1208553772.146165</t>
+          <t>1234133851.987717</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>8385497650.0</t>
+          <t>17904603214.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>3945941494.4</t>
+          <t>7326001062.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>2599113437.9</t>
+          <t>4299803431.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>2229827006.08</t>
+          <t>2525457286.94</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>1346828056</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>74453598.5111188</t>
+          <t>317120805.4261836</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>669862618.24</v>
+        <v>1651790443.46</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>28.40</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6785,22 +6785,22 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>-1.417668633394819</t>
+          <t>-4.249662585945642</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-7.171298548667624</t>
+          <t>-6.718506037644686</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>1.906817985210032</t>
+          <t>1.146736876787111</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>440954</t>
+          <t>448091</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>123131.763</t>
+          <t>174611.856</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,74 +6927,74 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>49.8</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>11.86</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4.69</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>51.82</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>18.53</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3.69</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>33.84</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
       <c r="T16" t="inlineStr">
         <is>
           <t>41.45</t>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>51.82</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1,171</t>
+          <t>1,160</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>235389</t>
+          <t>216310</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,57 +7063,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>44.51000000000001</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>42.04</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>39.67</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-80.44</t>
+          <t>-75.67</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,45 +7133,45 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1208553772.146165</t>
+          <t>1234133851.987717</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>5574972326.0</t>
+          <t>8385497650.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>2520009219.6</t>
+          <t>3945941494.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1882831584.8</t>
+          <t>2599113437.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>2124977087.88</t>
+          <t>2229827006.08</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>637177634</t>
+          <t>1346828056</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-33802586.89407057</t>
+          <t>74453598.5111188</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>263089084.85</v>
+        <v>669862618.24</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7216,22 +7216,22 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>-1.417668633394819</t>
+          <t>-4.249662585945642</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-7.171298548667624</t>
+          <t>-6.718506037644686</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>1.906817985210032</t>
+          <t>1.146736876787111</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>440954</t>
+          <t>448091</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>50200.655</t>
+          <t>123131.763</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,22 +7368,22 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>33.84</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14.90</t>
+          <t>36.54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1,171</t>
+          <t>1,160</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>235389</t>
+          <t>216310</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,62 +7489,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>42.04</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.67</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-81.87</t>
+          <t>-80.44</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,45 +7564,45 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1208553772.146165</t>
+          <t>1234133851.987717</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2161140323.0</t>
+          <t>5574972326.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>1653180953.2</t>
+          <t>2520009219.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1524676764.0</t>
+          <t>1882831584.8</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>2166955811.48</t>
+          <t>2124977087.88</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>128504189</t>
+          <t>637177634</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-87782890.84686022</t>
+          <t>-33802586.89407057</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-26284288.32</v>
+        <v>263089084.85</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7647,22 +7647,22 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>-1.417668633394819</t>
+          <t>-4.249662585945642</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-7.171298548667624</t>
+          <t>-6.718506037644686</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>1.906817985210032</t>
+          <t>1.146736876787111</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>440954</t>
+          <t>448091</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
+          <t>43.65</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
+          <t>46.45</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
           <t>43.5</t>
         </is>
       </c>
-      <c r="CD17" t="inlineStr">
-        <is>
-          <t>43.6</t>
-        </is>
-      </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>42.2</t>
-        </is>
-      </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>61106.691</t>
+          <t>50200.655</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7884,33 +7884,33 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>14.90</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1,171</t>
+          <t>1,160</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>235389</t>
+          <t>216310</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7920,57 +7920,57 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>44.17</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>41.58</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>40.57</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-20.69</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-81.72</t>
+          <t>-81.87</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1208553772.146165</t>
+          <t>1234133851.987717</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>2603791799.0</t>
+          <t>2161140323.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1406907278.2</t>
+          <t>1653180953.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1594504915.6</t>
+          <t>1524676764.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>2259840073.84</t>
+          <t>2166955811.48</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-187597637</t>
+          <t>128504189</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-98964454.94313243</t>
+          <t>-87782890.84686022</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-72968382.22</v>
+        <v>-26284288.32</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8078,37 +8078,37 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>-1.417668633394819</t>
+          <t>-4.249662585945642</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-7.171298548667624</t>
+          <t>-6.718506037644686</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>1.906817985210032</t>
+          <t>1.146736876787111</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>440954</t>
+          <t>448091</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>24192.572</t>
+          <t>61106.691</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-26.02</t>
+          <t>-11.77</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>7.18</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,52 +8336,52 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1,171</t>
+          <t>1,160</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>235389</t>
+          <t>216310</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>44.17</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.58</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.84</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
@@ -8391,22 +8391,22 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>39.07</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-33.02</t>
+          <t>-20.69</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-80.77</t>
+          <t>-81.72</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1208553772.146165</t>
+          <t>1234133851.987717</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>1004305374.0</t>
+          <t>2603791799.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1273605800.4</t>
+          <t>1406907278.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1721626446.0</t>
+          <t>1594504915.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>2273444052.96</t>
+          <t>2259840073.84</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-448020645</t>
+          <t>-187597637</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-103691013.6203629</t>
+          <t>-98964454.94313243</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-184480875.14</v>
+        <v>-72968382.22</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8509,37 +8509,37 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>-1.417668633394819</t>
+          <t>-4.249662585945642</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-7.171298548667624</t>
+          <t>-6.718506037644686</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>1.906817985210032</t>
+          <t>1.146736876787111</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>440954</t>
+          <t>448091</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>31076.84</t>
+          <t>24192.572</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>26.26</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-34.62</t>
+          <t>-26.02</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,32 +8767,32 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1,171</t>
+          <t>1,160</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>235389</t>
+          <t>216310</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -8802,42 +8802,42 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>41.79</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.57</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>38.88</t>
+          <t>39.07</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-33.84</t>
+          <t>-33.02</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-79.19</t>
+          <t>-80.77</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1208553772.146165</t>
+          <t>1234133851.987717</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1255836276.0</t>
+          <t>1004305374.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>1252285381.4</t>
+          <t>1273605800.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1915488903.2</t>
+          <t>1721626446.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>2294509276.16</t>
+          <t>2273444052.96</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-663203521</t>
+          <t>-448020645</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-89001947.88941646</t>
+          <t>-103691013.6203629</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-165822288.24</v>
+        <v>-184480875.14</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8940,22 +8940,22 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>-1.417668633394819</t>
+          <t>-4.249662585945642</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-7.171298548667624</t>
+          <t>-6.718506037644686</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>1.906817985210032</t>
+          <t>1.146736876787111</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>440954</t>
+          <t>448091</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>29726.51</t>
+          <t>31076.84</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>27.43</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-34.55</t>
+          <t>-34.62</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9198,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1,171</t>
+          <t>1,160</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>235389</t>
+          <t>216310</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9218,57 +9218,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>41.62</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>41.79</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>38.88</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-24.80</t>
+          <t>-33.84</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-77.42</t>
+          <t>-79.19</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1208553772.146165</t>
+          <t>1234133851.987717</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1240830994.0</t>
+          <t>1255836276.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>1245653950.0</t>
+          <t>1252285381.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1903186736.8</t>
+          <t>1915488903.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>2354204015.62</t>
+          <t>2294509276.16</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-657532786</t>
+          <t>-663203521</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-75034613.28045648</t>
+          <t>-89001947.88941646</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-160194679.01</v>
+        <v>-165822288.24</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>-1.417668633394819</t>
+          <t>-4.249662585945642</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-7.171298548667624</t>
+          <t>-6.718506037644686</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>1.906817985210032</t>
+          <t>1.146736876787111</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>440954</t>
+          <t>448091</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>22474.641</t>
+          <t>29726.51</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.81</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-27.22</t>
+          <t>-34.55</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1,171</t>
+          <t>1,160</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>235389</t>
+          <t>216310</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9644,62 +9644,62 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>41.79000000000001</t>
+          <t>41.62</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>40.57</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-18.24</t>
+          <t>-24.80</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-76.03</t>
+          <t>-77.42</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1208553772.146165</t>
+          <t>1234133851.987717</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>929771948.0</t>
+          <t>1240830994.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>1396172574.8</t>
+          <t>1245653950.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1918373479.4</t>
+          <t>1903186736.8</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>2411046387.7</t>
+          <t>2354204015.62</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-522200904</t>
+          <t>-657532786</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-59550964.96541016</t>
+          <t>-75034613.28045648</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-144826289.94</v>
+        <v>-160194679.01</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9802,22 +9802,22 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>-1.417668633394819</t>
+          <t>-4.249662585945642</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-7.171298548667624</t>
+          <t>-6.718506037644686</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>1.906817985210032</t>
+          <t>1.146736876787111</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>440954</t>
+          <t>448091</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,17 +9882,17 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45640.364</t>
+          <t>22474.641</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,87 +9944,87 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>41.35</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>26.81</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4.69</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-27.22</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>41.45</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
           <t>41.5</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>25.36</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3.69</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>-9.89</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>41.45</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>41.45</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1,171</t>
+          <t>1,160</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>235389</t>
+          <t>216310</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10075,62 +10075,62 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>41.79000000000001</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>41.44</t>
+          <t>41.54</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>40.57</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>38.37</t>
+          <t>38.53</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-9.58</t>
+          <t>-18.24</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-74.93</t>
+          <t>-76.03</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,45 +10150,45 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1208553772.146165</t>
+          <t>1234133851.987717</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1937284410.0</t>
+          <t>929771948.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>1782102553.0</t>
+          <t>1396172574.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1977597878.5</t>
+          <t>1918373479.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>2560250586.88</t>
+          <t>2411046387.7</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-195495325</t>
+          <t>-522200904</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-44046360.42446328</t>
+          <t>-59550964.96541016</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-84371325.98</v>
+        <v>-144826289.94</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10233,22 +10233,22 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>-1.417668633394819</t>
+          <t>-4.249662585945642</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-7.171298548667624</t>
+          <t>-6.718506037644686</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>1.906817985210032</t>
+          <t>1.146736876787111</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>440954</t>
+          <t>448091</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/酚醛樹脂.xlsx
+++ b/Result/checksun_type/酚醛樹脂.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13085.646</t>
+          <t>7632.447</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.70</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,67 +1009,67 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>13086</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>42.31</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>41.19</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>39.57000000000001</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>39.83</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.66</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-28.47</t>
+          <t>-23.20</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-104.51</t>
+          <t>-104.79</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>206901190.2919075</t>
+          <t>207258057.2207792</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>532289392.0</t>
+          <t>302806648.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>317585660.6</t>
+          <t>315723489.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>263274442.8</t>
+          <t>267936291.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>673739372.28</t>
+          <t>654424013.3</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>54311217</t>
+          <t>47787197</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-39813408.42361735</t>
+          <t>-38884372.1089407</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-35081209.22</v>
+        <v>-33774672.38</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>42.24</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>46245</t>
+          <t>46186</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6136.175</t>
+          <t>13085.646</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>11.70</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>13086</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>42.31</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>41.19</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>39.51000000000001</t>
+          <t>39.57000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>39.76</t>
+          <t>39.78</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.87</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-36.08</t>
+          <t>-28.47</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.19</t>
+          <t>-104.51</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>206901190.2919075</t>
+          <t>207258057.2207792</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>240426749.0</t>
+          <t>532289392.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>234858276.4</t>
+          <t>317585660.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>236240878.5</t>
+          <t>263274442.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>679732391.62</t>
+          <t>673739372.28</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1382602</t>
+          <t>54311217</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-40673808.27865538</t>
+          <t>-39813408.42361735</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-60282226.95</v>
+        <v>-35081209.22</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>46245</t>
+          <t>46186</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6635.823</t>
+          <t>6136.175</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-17.42</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13086</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.80</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.51000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>39.76</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>41.14</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>38.33</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>-36.08</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-103.81</t>
+          <t>-104.19</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>206901190.2919075</t>
+          <t>207258057.2207792</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>267989366.0</t>
+          <t>240426749.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>223432348.8</t>
+          <t>234858276.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>270578244.9</t>
+          <t>236240878.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>693037521.34</t>
+          <t>679732391.62</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-47145896</t>
+          <t>-1382602</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-37108641.24703376</t>
+          <t>-40673808.27865538</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-62859746.71</v>
+        <v>-60282226.95</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>40.61</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>46245</t>
+          <t>46186</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5872.775</t>
+          <t>6635.823</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-33.41</t>
+          <t>-17.42</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>13086</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>77.42</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>7.80</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>39.52</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>39.78</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.14</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>38.16</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-40.75</t>
+          <t>-11.77</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-103.70</t>
+          <t>-103.81</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>206901190.2919075</t>
+          <t>207258057.2207792</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>235105290.0</t>
+          <t>267989366.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>211553687.2</t>
+          <t>223432348.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>317718579.4</t>
+          <t>270578244.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>694915339.42</t>
+          <t>693037521.34</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-106164892</t>
+          <t>-47145896</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-32426622.07125968</t>
+          <t>-37108641.24703376</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-67250064.38</v>
+        <v>-62859746.71</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>43.86</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>46245</t>
+          <t>46186</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7951.184</t>
+          <t>5872.775</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-50.07</t>
+          <t>-33.41</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>13086</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>48.72</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>28.81</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.52</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.98</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-72.18</t>
+          <t>-40.75</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-103.32</t>
+          <t>-103.70</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>206901190.2919075</t>
+          <t>207258057.2207792</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>312117506.0</t>
+          <t>235105290.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>220149093.2</t>
+          <t>211553687.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>440884400.6</t>
+          <t>317718579.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>697689583.68</t>
+          <t>694915339.42</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-220735307</t>
+          <t>-106164892</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-26095087.10550797</t>
+          <t>-32426622.07125968</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-67596864.90000001</v>
+        <v>-67250064.38</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>42.60</t>
+          <t>43.86</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>46245</t>
+          <t>46186</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,109 +3033,109 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7951.184</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-1.81</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-50.07</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>39.25</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>40.85</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>0.64</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>3041.179</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>39.15</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-2.52</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-66.98</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>27.6</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>40.85</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
       <c r="X7" t="inlineStr">
         <is>
           <t>4.04</t>
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>13086</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>41.34</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>37.61</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-99.28</t>
+          <t>-72.18</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-102.72</t>
+          <t>-103.32</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>206901190.2919075</t>
+          <t>207258057.2207792</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>118652471.0</t>
+          <t>312117506.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>208963225.0</t>
+          <t>220149093.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>632911197.7</t>
+          <t>440884400.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>701089842.98</t>
+          <t>697689583.68</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-423947972</t>
+          <t>-220735307</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-18549309.32532593</t>
+          <t>-26095087.10550797</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-73929429.31</v>
+        <v>-67596864.90000001</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>41.34</t>
+          <t>42.60</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>46245</t>
+          <t>46186</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4678.818</t>
+          <t>3041.179</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-64.91</t>
+          <t>-66.98</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>13086</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>39.47</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>39.96</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.34</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>37.43</t>
+          <t>37.61</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-100.53</t>
+          <t>-99.28</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-102.05</t>
+          <t>-102.72</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>206901190.2919075</t>
+          <t>207258057.2207792</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>183297111.0</t>
+          <t>118652471.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>237623480.6</t>
+          <t>208963225.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>677103255.3</t>
+          <t>632911197.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>708421794.36</t>
+          <t>701089842.98</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-439479774</t>
+          <t>-423947972</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-8480196.600382902</t>
+          <t>-18549309.32532593</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-59607216.54</v>
+        <v>-73929429.31</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>41.34</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>46245</t>
+          <t>46186</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5259.933</t>
+          <t>4678.818</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-53.20</t>
+          <t>-64.91</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>13086</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>26.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>39.96</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>41.47</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>37.24</t>
+          <t>37.43</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-100.53</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-101.53</t>
+          <t>-102.05</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>206901190.2919075</t>
+          <t>207258057.2207792</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>208596058.0</t>
+          <t>183297111.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>317724141.0</t>
+          <t>237623480.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>678874486.1</t>
+          <t>677103255.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>711908904.88</t>
+          <t>708421794.36</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-361150345</t>
+          <t>-439479774</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>815625.206547319</t>
+          <t>-8480196.600382902</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-43944294.84</v>
+        <v>-59607216.54</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>46245</t>
+          <t>46186</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7140.111</t>
+          <t>5259.933</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,72 +4341,72 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>40.2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-2.03</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-1.81</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-53.20</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>39.25</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-2.52</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-36.72</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,52 +4457,52 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>13086</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>26.76</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>31.82</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>40.06</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4512,17 +4512,17 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>37.24</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-29.31</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.48</t>
+          <t>-101.53</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,45 +4547,45 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>206901190.2919075</t>
+          <t>207258057.2207792</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>278082320.0</t>
+          <t>208596058.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>423883471.6</t>
+          <t>317724141.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>669852008.1</t>
+          <t>678874486.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>715483441.44</t>
+          <t>711908904.88</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-245968536</t>
+          <t>-361150345</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>8953792.488120452</t>
+          <t>815625.206547319</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-22709854.78</v>
+        <v>-43944294.84</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>41.70</t>
+          <t>45.13</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>46245</t>
+          <t>46186</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6398.955</t>
+          <t>7140.111</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-36.72</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,72 +4888,72 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>13086</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
+          <t>28.28</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
           <t>40.4</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>51.18</t>
-        </is>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>12.67</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>40.84</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>40.26</t>
+          <t>40.14</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>41.52</t>
+          <t>41.47</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>117.63</t>
+          <t>-29.31</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-101.37</t>
+          <t>-101.48</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>206901190.2919075</t>
+          <t>207258057.2207792</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>256188165.0</t>
+          <t>278082320.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>661619708.0</t>
+          <t>423883471.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>663664779.1</t>
+          <t>669852008.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>720815035.62</t>
+          <t>715483441.44</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2045071</t>
+          <t>-245968536</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>14710819.26440901</t>
+          <t>8953792.488120452</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>991169.1899999999</v>
+        <v>-22709854.78</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>43.86</t>
+          <t>41.70</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>46245</t>
+          <t>46186</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6429.228</t>
+          <t>6398.955</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>60.63</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>13086</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>55.89</t>
+          <t>51.18</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>12.67</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>40.84</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.26</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.52</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>184.79</t>
+          <t>117.63</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-101.78</t>
+          <t>-101.37</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>206901190.2919075</t>
+          <t>207258057.2207792</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>261953749.0</t>
+          <t>256188165.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1056859170.4</t>
+          <t>661619708.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>657954566.6</t>
+          <t>663664779.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>735264469.26</t>
+          <t>720815035.62</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>398904603</t>
+          <t>-2045071</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>17205301.09608119</t>
+          <t>14710819.26440901</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>37160178.29</v>
+        <v>991169.1899999999</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>43.86</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>46245</t>
+          <t>46186</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>216309.874</t>
+          <t>237895.796</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>67.79</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>26.49</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>64.20</t>
+          <t>70.60</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1,160</t>
+          <t>1,411</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>216310</t>
+          <t>237896</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>20.30</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>44.62</t>
+          <t>45.39</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.22</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>91.69</t>
+          <t>77.41</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-41.91</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,27 +5840,27 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1234133851.987717</t>
+          <t>1262428330.062771</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>12606646015.0</t>
+          <t>13894804772.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>11463824233.2</t>
+          <t>13127790722.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>6558502593.2</t>
+          <t>7823899971.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>2879764455.78</t>
+          <t>3109382048.22</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -5870,15 +5870,15 @@
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>790537525.8613333</t>
+          <t>1002670238.352965</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>2039269729.26</v>
+        <v>2169400157.06</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.66</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>448091</t>
+          <t>454436</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>235389.305</t>
+          <t>216309.874</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>73.90</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>64.20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1,160</t>
+          <t>1,411</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>216310</t>
+          <t>237896</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.62</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>41.17</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>104.45</t>
+          <t>91.69</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-55.23</t>
+          <t>-41.91</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,27 +6271,27 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1234133851.987717</t>
+          <t>1262428330.062771</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>12847401961.0</t>
+          <t>12606646015.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>9374723094.8</t>
+          <t>11463824233.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>5390815186.5</t>
+          <t>6558502593.2</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>2722439698.1</t>
+          <t>2879764455.78</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -6301,15 +6301,15 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>563495307.060791</t>
+          <t>790537525.8613333</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>1918555066.05</v>
+        <v>2039269729.26</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>32.70</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.66</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>448091</t>
+          <t>454436</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>336947.705</t>
+          <t>235389.305</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>70.38</t>
+          <t>73.90</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>22.74</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1,160</t>
+          <t>1,411</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>216310</t>
+          <t>237896</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>43.19</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.17</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>105.78</t>
+          <t>104.45</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-66.92</t>
+          <t>-55.23</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,27 +6702,27 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1234133851.987717</t>
+          <t>1262428330.062771</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>17904603214.0</t>
+          <t>12847401961.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>7326001062.4</t>
+          <t>9374723094.8</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>4299803431.4</t>
+          <t>5390815186.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>2525457286.94</t>
+          <t>2722439698.1</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -6732,15 +6732,15 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>317120805.4261836</t>
+          <t>563495307.060791</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>1651790443.46</v>
+        <v>1918555066.05</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>28.40</t>
+          <t>32.70</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6805,17 +6805,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.66</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>448091</t>
+          <t>454436</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>174611.856</t>
+          <t>336947.705</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>51.82</t>
+          <t>70.38</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7022,33 +7022,33 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>51.82</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1,160</t>
+          <t>1,411</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>216310</t>
+          <t>237896</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,57 +7063,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>44.51000000000001</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>43.19</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>105.78</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-75.67</t>
+          <t>-66.92</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,45 +7133,45 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1234133851.987717</t>
+          <t>1262428330.062771</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>8385497650.0</t>
+          <t>17904603214.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>3945941494.4</t>
+          <t>7326001062.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2599113437.9</t>
+          <t>4299803431.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>2229827006.08</t>
+          <t>2525457286.94</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>1346828056</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>74453598.5111188</t>
+          <t>317120805.4261836</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>669862618.24</v>
+        <v>1651790443.46</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>28.40</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.66</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>448091</t>
+          <t>454436</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>123131.763</t>
+          <t>174611.856</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,74 +7358,74 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>49.8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>13.09</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5.12</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>51.82</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-11-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>19.82</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4.69</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>33.84</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
       <c r="T17" t="inlineStr">
         <is>
           <t>41.45</t>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>51.82</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1,160</t>
+          <t>1,411</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>216310</t>
+          <t>237896</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7494,57 +7494,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>44.51000000000001</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>42.04</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>39.67</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-80.44</t>
+          <t>-75.67</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,45 +7564,45 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1234133851.987717</t>
+          <t>1262428330.062771</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>5574972326.0</t>
+          <t>8385497650.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>2520009219.6</t>
+          <t>3945941494.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1882831584.8</t>
+          <t>2599113437.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>2124977087.88</t>
+          <t>2229827006.08</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>637177634</t>
+          <t>1346828056</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-33802586.89407057</t>
+          <t>74453598.5111188</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>263089084.85</v>
+        <v>669862618.24</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.66</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>448091</t>
+          <t>454436</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>50200.655</t>
+          <t>123131.763</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,22 +7799,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>20.94</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>33.84</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14.90</t>
+          <t>36.54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1,160</t>
+          <t>1,411</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>216310</t>
+          <t>237896</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7920,62 +7920,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>42.04</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.67</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-81.87</t>
+          <t>-80.44</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,45 +7995,45 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1234133851.987717</t>
+          <t>1262428330.062771</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>2161140323.0</t>
+          <t>5574972326.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1653180953.2</t>
+          <t>2520009219.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1524676764.0</t>
+          <t>1882831584.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>2166955811.48</t>
+          <t>2124977087.88</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>128504189</t>
+          <t>637177634</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-87782890.84686022</t>
+          <t>-33802586.89407057</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-26284288.32</v>
+        <v>263089084.85</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.66</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>448091</t>
+          <t>454436</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
+          <t>43.65</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
+          <t>46.45</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
           <t>43.5</t>
         </is>
       </c>
-      <c r="CD18" t="inlineStr">
-        <is>
-          <t>43.6</t>
-        </is>
-      </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>42.2</t>
-        </is>
-      </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>61106.691</t>
+          <t>50200.655</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>24.52</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8315,33 +8315,33 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>14.90</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1,160</t>
+          <t>1,411</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>216310</t>
+          <t>237896</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8351,57 +8351,57 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>44.17</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>41.58</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>40.57</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-20.69</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-81.72</t>
+          <t>-81.87</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1234133851.987717</t>
+          <t>1262428330.062771</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2603791799.0</t>
+          <t>2161140323.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1406907278.2</t>
+          <t>1653180953.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1594504915.6</t>
+          <t>1524676764.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>2259840073.84</t>
+          <t>2166955811.48</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-187597637</t>
+          <t>128504189</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-98964454.94313243</t>
+          <t>-87782890.84686022</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-72968382.22</v>
+        <v>-26284288.32</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.66</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>448091</t>
+          <t>454436</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>24192.572</t>
+          <t>61106.691</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>25.74</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-26.02</t>
+          <t>-11.77</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7.18</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,52 +8767,52 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1,160</t>
+          <t>1,411</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>216310</t>
+          <t>237896</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>44.17</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.58</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.84</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
@@ -8822,22 +8822,22 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>39.07</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-33.02</t>
+          <t>-20.69</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-80.77</t>
+          <t>-81.72</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1234133851.987717</t>
+          <t>1262428330.062771</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1004305374.0</t>
+          <t>2603791799.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>1273605800.4</t>
+          <t>1406907278.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1721626446.0</t>
+          <t>1594504915.6</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>2273444052.96</t>
+          <t>2259840073.84</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-448020645</t>
+          <t>-187597637</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-103691013.6203629</t>
+          <t>-98964454.94313243</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-184480875.14</v>
+        <v>-72968382.22</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.66</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>448091</t>
+          <t>454436</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>31076.84</t>
+          <t>24192.572</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>27.31</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-34.62</t>
+          <t>-26.02</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,32 +9198,32 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1,160</t>
+          <t>1,411</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>216310</t>
+          <t>237896</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -9233,42 +9233,42 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>41.79</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.57</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>38.88</t>
+          <t>39.07</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-33.84</t>
+          <t>-33.02</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-79.19</t>
+          <t>-80.77</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1234133851.987717</t>
+          <t>1262428330.062771</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1255836276.0</t>
+          <t>1004305374.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>1252285381.4</t>
+          <t>1273605800.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1915488903.2</t>
+          <t>1721626446.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>2294509276.16</t>
+          <t>2273444052.96</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-663203521</t>
+          <t>-448020645</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-89001947.88941646</t>
+          <t>-103691013.6203629</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-165822288.24</v>
+        <v>-184480875.14</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.66</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>448091</t>
+          <t>454436</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>29726.51</t>
+          <t>31076.84</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>26.81</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-34.55</t>
+          <t>-34.62</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1,160</t>
+          <t>1,411</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>216310</t>
+          <t>237896</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9649,57 +9649,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>41.62</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>41.79</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>38.88</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-24.80</t>
+          <t>-33.84</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-77.42</t>
+          <t>-79.19</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1234133851.987717</t>
+          <t>1262428330.062771</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1240830994.0</t>
+          <t>1255836276.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>1245653950.0</t>
+          <t>1252285381.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1903186736.8</t>
+          <t>1915488903.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>2354204015.62</t>
+          <t>2294509276.16</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-657532786</t>
+          <t>-663203521</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-75034613.28045648</t>
+          <t>-89001947.88941646</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-160194679.01</v>
+        <v>-165822288.24</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.66</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>448091</t>
+          <t>454436</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22474.641</t>
+          <t>29726.51</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>26.81</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-27.22</t>
+          <t>-34.55</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1,160</t>
+          <t>1,411</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>216310</t>
+          <t>237896</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10075,62 +10075,62 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>41.79000000000001</t>
+          <t>41.62</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>40.57</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-18.24</t>
+          <t>-24.80</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-76.03</t>
+          <t>-77.42</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1234133851.987717</t>
+          <t>1262428330.062771</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>929771948.0</t>
+          <t>1240830994.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>1396172574.8</t>
+          <t>1245653950.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1918373479.4</t>
+          <t>1903186736.8</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>2411046387.7</t>
+          <t>2354204015.62</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-522200904</t>
+          <t>-657532786</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-59550964.96541016</t>
+          <t>-75034613.28045648</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-144826289.94</v>
+        <v>-160194679.01</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.66</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>448091</t>
+          <t>454436</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,17 +10313,17 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">

--- a/Result/checksun_type/酚醛樹脂.xlsx
+++ b/Result/checksun_type/酚醛樹脂.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7632.447</t>
+          <t>5612.57</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>39.83</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>38.66</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-23.20</t>
+          <t>-26.63</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-104.79</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>207258057.2207792</t>
+          <t>207432458.0878963</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>302806648.0</t>
+          <t>218861506.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>315723489.0</t>
+          <t>312474732.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>267936291.1</t>
+          <t>262014209.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>654424013.3</t>
+          <t>631667121.94</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>47787197</t>
+          <t>50460522</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-38884372.1089407</t>
+          <t>-38796255.69662388</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-33774672.38</v>
+        <v>-38311615.43</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>46186</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>38.5</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>39.1</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>40.45</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>38.85</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>39.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13085.646</t>
+          <t>7632.447</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.70</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,67 +1440,67 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>42.31</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>41.19</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>39.57000000000001</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>39.83</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.66</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-28.47</t>
+          <t>-23.20</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.51</t>
+          <t>-104.79</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>207258057.2207792</t>
+          <t>207432458.0878963</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>532289392.0</t>
+          <t>302806648.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>317585660.6</t>
+          <t>315723489.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>263274442.8</t>
+          <t>267936291.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>673739372.28</t>
+          <t>654424013.3</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>54311217</t>
+          <t>47787197</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-39813408.42361735</t>
+          <t>-38884372.1089407</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-35081209.22</v>
+        <v>-33774672.38</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>42.24</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,12 +1628,12 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>46186</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6136.175</t>
+          <t>13085.646</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>11.70</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>42.31</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>41.19</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>39.51000000000001</t>
+          <t>39.57000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>39.76</t>
+          <t>39.78</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.87</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-36.08</t>
+          <t>-28.47</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.19</t>
+          <t>-104.51</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>207258057.2207792</t>
+          <t>207432458.0878963</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>240426749.0</t>
+          <t>532289392.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>234858276.4</t>
+          <t>317585660.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>236240878.5</t>
+          <t>263274442.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>679732391.62</t>
+          <t>673739372.28</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1382602</t>
+          <t>54311217</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-40673808.27865538</t>
+          <t>-39813408.42361735</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-60282226.95</v>
+        <v>-35081209.22</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>46186</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6635.823</t>
+          <t>6136.175</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-17.42</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.80</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.51000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>39.76</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>41.14</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>38.33</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>-36.08</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-103.81</t>
+          <t>-104.19</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>207258057.2207792</t>
+          <t>207432458.0878963</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>267989366.0</t>
+          <t>240426749.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>223432348.8</t>
+          <t>234858276.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>270578244.9</t>
+          <t>236240878.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>693037521.34</t>
+          <t>679732391.62</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-47145896</t>
+          <t>-1382602</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-37108641.24703376</t>
+          <t>-40673808.27865538</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-62859746.71</v>
+        <v>-60282226.95</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>40.61</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>46186</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5872.775</t>
+          <t>6635.823</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-33.41</t>
+          <t>-17.42</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>77.42</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>7.80</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>39.52</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>39.78</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.14</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>38.16</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-40.75</t>
+          <t>-11.77</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-103.70</t>
+          <t>-103.81</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>207258057.2207792</t>
+          <t>207432458.0878963</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>235105290.0</t>
+          <t>267989366.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>211553687.2</t>
+          <t>223432348.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>317718579.4</t>
+          <t>270578244.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>694915339.42</t>
+          <t>693037521.34</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-106164892</t>
+          <t>-47145896</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-32426622.07125968</t>
+          <t>-37108641.24703376</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-67250064.38</v>
+        <v>-62859746.71</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>43.86</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>46186</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7951.184</t>
+          <t>5872.775</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-50.07</t>
+          <t>-33.41</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>48.72</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>28.81</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.52</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.98</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-72.18</t>
+          <t>-40.75</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-103.32</t>
+          <t>-103.70</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>207258057.2207792</t>
+          <t>207432458.0878963</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>312117506.0</t>
+          <t>235105290.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>220149093.2</t>
+          <t>211553687.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>440884400.6</t>
+          <t>317718579.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>697689583.68</t>
+          <t>694915339.42</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-220735307</t>
+          <t>-106164892</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-26095087.10550797</t>
+          <t>-32426622.07125968</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-67596864.90000001</v>
+        <v>-67250064.38</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>42.60</t>
+          <t>43.86</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>46186</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,109 +3464,109 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7951.184</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-1.02</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-2.22</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-50.07</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>39.25</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>40.85</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
           <t>0.64</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>3041.179</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>39.15</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-1.81</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-66.98</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>27.6</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>40.85</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
       <c r="X8" t="inlineStr">
         <is>
           <t>4.04</t>
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>41.34</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>37.61</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-99.28</t>
+          <t>-72.18</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-102.72</t>
+          <t>-103.32</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>207258057.2207792</t>
+          <t>207432458.0878963</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>118652471.0</t>
+          <t>312117506.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>208963225.0</t>
+          <t>220149093.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>632911197.7</t>
+          <t>440884400.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>701089842.98</t>
+          <t>697689583.68</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-423947972</t>
+          <t>-220735307</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-18549309.32532593</t>
+          <t>-26095087.10550797</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-73929429.31</v>
+        <v>-67596864.90000001</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>41.34</t>
+          <t>42.60</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>46186</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4678.818</t>
+          <t>3041.179</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-64.91</t>
+          <t>-66.98</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>39.47</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>39.96</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.34</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>37.43</t>
+          <t>37.61</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-100.53</t>
+          <t>-99.28</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-102.05</t>
+          <t>-102.72</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>207258057.2207792</t>
+          <t>207432458.0878963</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>183297111.0</t>
+          <t>118652471.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>237623480.6</t>
+          <t>208963225.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>677103255.3</t>
+          <t>632911197.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>708421794.36</t>
+          <t>701089842.98</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-439479774</t>
+          <t>-423947972</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-8480196.600382902</t>
+          <t>-18549309.32532593</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-59607216.54</v>
+        <v>-73929429.31</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>41.34</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>46186</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5259.933</t>
+          <t>4678.818</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-53.20</t>
+          <t>-64.91</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>26.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>39.96</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>41.47</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>37.24</t>
+          <t>37.43</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-100.53</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.53</t>
+          <t>-102.05</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>207258057.2207792</t>
+          <t>207432458.0878963</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>208596058.0</t>
+          <t>183297111.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>317724141.0</t>
+          <t>237623480.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>678874486.1</t>
+          <t>677103255.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>711908904.88</t>
+          <t>708421794.36</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-361150345</t>
+          <t>-439479774</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>815625.206547319</t>
+          <t>-8480196.600382902</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-43944294.84</v>
+        <v>-59607216.54</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>46186</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7140.111</t>
+          <t>5259.933</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,72 +4772,72 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>40.2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-2.81</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-2.22</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-53.20</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>39.25</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-1.81</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-36.72</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,52 +4888,52 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>26.76</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>31.82</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>40.06</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -4943,17 +4943,17 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>37.24</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-29.31</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-101.48</t>
+          <t>-101.53</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,45 +4978,45 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>207258057.2207792</t>
+          <t>207432458.0878963</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>278082320.0</t>
+          <t>208596058.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>423883471.6</t>
+          <t>317724141.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>669852008.1</t>
+          <t>678874486.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>715483441.44</t>
+          <t>711908904.88</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-245968536</t>
+          <t>-361150345</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>8953792.488120452</t>
+          <t>815625.206547319</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-22709854.78</v>
+        <v>-43944294.84</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>41.70</t>
+          <t>45.13</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>46186</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6398.955</t>
+          <t>7140.111</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-36.72</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,72 +5319,72 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
+          <t>28.28</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
           <t>40.4</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>51.18</t>
-        </is>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>12.67</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>40.84</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>40.26</t>
+          <t>40.14</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>41.52</t>
+          <t>41.47</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>117.63</t>
+          <t>-29.31</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-101.37</t>
+          <t>-101.48</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>207258057.2207792</t>
+          <t>207432458.0878963</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>256188165.0</t>
+          <t>278082320.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>661619708.0</t>
+          <t>423883471.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>663664779.1</t>
+          <t>669852008.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>720815035.62</t>
+          <t>715483441.44</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2045071</t>
+          <t>-245968536</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>14710819.26440901</t>
+          <t>8953792.488120452</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>991169.1899999999</v>
+        <v>-22709854.78</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>43.86</t>
+          <t>41.70</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>46186</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>237895.796</t>
+          <t>141242.686</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>67.79</t>
+          <t>53.41</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>70.60</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1,411</t>
+          <t>864</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>237896</t>
+          <t>141243</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.27</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.09</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>45.39</t>
+          <t>45.98</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>41.49</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>77.41</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-27.97</t>
+          <t>-16.45</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,27 +5840,27 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1262428330.062771</t>
+          <t>1277290203.855908</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>13894804772.0</t>
+          <t>7717712495.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>13127790722.4</t>
+          <t>12994233691.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7823899971.0</t>
+          <t>8470087592.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>3109382048.22</t>
+          <t>3233128694.92</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -5870,15 +5870,15 @@
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>1002670238.352965</t>
+          <t>1116563206.577178</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>2169400157.06</v>
+        <v>1742974531.81</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>28.40</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>62.66</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>454436</t>
+          <t>426678</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>216309.874</t>
+          <t>237895.796</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>67.79</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>26.49</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>64.20</t>
+          <t>70.60</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1,411</t>
+          <t>864</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>237896</t>
+          <t>141243</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>20.30</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>44.62</t>
+          <t>45.39</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.22</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>91.69</t>
+          <t>77.41</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-41.91</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,27 +6271,27 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1262428330.062771</t>
+          <t>1277290203.855908</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>12606646015.0</t>
+          <t>13894804772.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>11463824233.2</t>
+          <t>13127790722.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>6558502593.2</t>
+          <t>7823899971.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>2879764455.78</t>
+          <t>3109382048.22</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -6301,15 +6301,15 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>790537525.8613333</t>
+          <t>1002670238.352965</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>2039269729.26</v>
+        <v>2169400157.06</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>62.66</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>454436</t>
+          <t>426678</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>235389.305</t>
+          <t>216309.874</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>73.90</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>64.20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1,411</t>
+          <t>864</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>237896</t>
+          <t>141243</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.62</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>41.17</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>104.45</t>
+          <t>91.69</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-55.23</t>
+          <t>-41.91</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,27 +6702,27 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1262428330.062771</t>
+          <t>1277290203.855908</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>12847401961.0</t>
+          <t>12606646015.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>9374723094.8</t>
+          <t>11463824233.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>5390815186.5</t>
+          <t>6558502593.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>2722439698.1</t>
+          <t>2879764455.78</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -6732,15 +6732,15 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>563495307.060791</t>
+          <t>790537525.8613333</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>1918555066.05</v>
+        <v>2039269729.26</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>32.70</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>62.66</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>454436</t>
+          <t>426678</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>336947.705</t>
+          <t>235389.305</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>70.38</t>
+          <t>73.90</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>22.74</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1,411</t>
+          <t>864</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>237896</t>
+          <t>141243</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,57 +7063,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>43.19</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.17</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>105.78</t>
+          <t>104.45</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-66.92</t>
+          <t>-55.23</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,27 +7133,27 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1262428330.062771</t>
+          <t>1277290203.855908</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>17904603214.0</t>
+          <t>12847401961.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>7326001062.4</t>
+          <t>9374723094.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>4299803431.4</t>
+          <t>5390815186.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>2525457286.94</t>
+          <t>2722439698.1</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -7163,15 +7163,15 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>317120805.4261836</t>
+          <t>563495307.060791</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>1651790443.46</v>
+        <v>1918555066.05</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>28.40</t>
+          <t>32.70</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7236,17 +7236,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>62.66</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>454436</t>
+          <t>426678</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>174611.856</t>
+          <t>336947.705</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>51.82</t>
+          <t>70.38</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7453,33 +7453,33 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>51.82</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1,411</t>
+          <t>864</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>237896</t>
+          <t>141243</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7494,57 +7494,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>44.51000000000001</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>43.19</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>105.78</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-75.67</t>
+          <t>-66.92</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,45 +7564,45 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1262428330.062771</t>
+          <t>1277290203.855908</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>8385497650.0</t>
+          <t>17904603214.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>3945941494.4</t>
+          <t>7326001062.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2599113437.9</t>
+          <t>4299803431.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>2229827006.08</t>
+          <t>2525457286.94</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>1346828056</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>74453598.5111188</t>
+          <t>317120805.4261836</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>669862618.24</v>
+        <v>1651790443.46</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>28.40</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>62.66</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>454436</t>
+          <t>426678</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>123131.763</t>
+          <t>174611.856</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,74 +7789,74 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>49.8</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>7.43</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4.79</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>51.82</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-11-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>20.94</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5.12</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>33.84</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
         <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
       <c r="T18" t="inlineStr">
         <is>
           <t>41.45</t>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>51.82</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1,411</t>
+          <t>864</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>237896</t>
+          <t>141243</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7925,57 +7925,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>44.51000000000001</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>42.04</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>39.67</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-80.44</t>
+          <t>-75.67</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,45 +7995,45 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1262428330.062771</t>
+          <t>1277290203.855908</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>5574972326.0</t>
+          <t>8385497650.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>2520009219.6</t>
+          <t>3945941494.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1882831584.8</t>
+          <t>2599113437.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>2124977087.88</t>
+          <t>2229827006.08</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>637177634</t>
+          <t>1346828056</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-33802586.89407057</t>
+          <t>74453598.5111188</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>263089084.85</v>
+        <v>669862618.24</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>62.66</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>454436</t>
+          <t>426678</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>50200.655</t>
+          <t>123131.763</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,22 +8230,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>24.52</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>33.84</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14.90</t>
+          <t>36.54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1,411</t>
+          <t>864</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>237896</t>
+          <t>141243</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8351,62 +8351,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>42.04</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.67</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-81.87</t>
+          <t>-80.44</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,45 +8426,45 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1262428330.062771</t>
+          <t>1277290203.855908</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2161140323.0</t>
+          <t>5574972326.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1653180953.2</t>
+          <t>2520009219.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1524676764.0</t>
+          <t>1882831584.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>2166955811.48</t>
+          <t>2124977087.88</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>128504189</t>
+          <t>637177634</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-87782890.84686022</t>
+          <t>-33802586.89407057</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-26284288.32</v>
+        <v>263089084.85</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>62.66</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>454436</t>
+          <t>426678</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
+          <t>43.65</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
+          <t>46.45</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
           <t>43.5</t>
         </is>
       </c>
-      <c r="CD19" t="inlineStr">
-        <is>
-          <t>43.6</t>
-        </is>
-      </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>42.2</t>
-        </is>
-      </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>61106.691</t>
+          <t>50200.655</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>25.74</t>
+          <t>19.61</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8746,33 +8746,33 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>14.90</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1,411</t>
+          <t>864</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>237896</t>
+          <t>141243</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8782,57 +8782,57 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>44.17</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>41.58</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>40.57</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-20.69</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-81.72</t>
+          <t>-81.87</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1262428330.062771</t>
+          <t>1277290203.855908</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>2603791799.0</t>
+          <t>2161140323.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>1406907278.2</t>
+          <t>1653180953.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1594504915.6</t>
+          <t>1524676764.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>2259840073.84</t>
+          <t>2166955811.48</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-187597637</t>
+          <t>128504189</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-98964454.94313243</t>
+          <t>-87782890.84686022</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-72968382.22</v>
+        <v>-26284288.32</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>62.66</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>454436</t>
+          <t>426678</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>24192.572</t>
+          <t>61106.691</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>27.31</t>
+          <t>20.91</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-26.02</t>
+          <t>-11.77</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.18</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,52 +9198,52 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1,411</t>
+          <t>864</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>237896</t>
+          <t>141243</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>44.17</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.58</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.84</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
@@ -9253,22 +9253,22 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>39.07</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-33.02</t>
+          <t>-20.69</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-80.77</t>
+          <t>-81.72</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1262428330.062771</t>
+          <t>1277290203.855908</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1004305374.0</t>
+          <t>2603791799.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>1273605800.4</t>
+          <t>1406907278.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1721626446.0</t>
+          <t>1594504915.6</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>2273444052.96</t>
+          <t>2259840073.84</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-448020645</t>
+          <t>-187597637</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-103691013.6203629</t>
+          <t>-98964454.94313243</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-184480875.14</v>
+        <v>-72968382.22</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>62.66</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>454436</t>
+          <t>426678</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>31076.84</t>
+          <t>24192.572</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>22.58</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-34.62</t>
+          <t>-26.02</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,32 +9629,32 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1,411</t>
+          <t>864</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>237896</t>
+          <t>141243</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -9664,42 +9664,42 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>41.79</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.57</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>38.88</t>
+          <t>39.07</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-33.84</t>
+          <t>-33.02</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-79.19</t>
+          <t>-80.77</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1262428330.062771</t>
+          <t>1277290203.855908</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1255836276.0</t>
+          <t>1004305374.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>1252285381.4</t>
+          <t>1273605800.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1915488903.2</t>
+          <t>1721626446.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>2294509276.16</t>
+          <t>2273444052.96</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-663203521</t>
+          <t>-448020645</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-89001947.88941646</t>
+          <t>-103691013.6203629</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-165822288.24</v>
+        <v>-184480875.14</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>62.66</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>454436</t>
+          <t>426678</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>29726.51</t>
+          <t>31076.84</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>23.79</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-34.55</t>
+          <t>-34.62</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1,411</t>
+          <t>864</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>237896</t>
+          <t>141243</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10080,57 +10080,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>41.62</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>41.79</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>38.88</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-24.80</t>
+          <t>-33.84</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-77.42</t>
+          <t>-79.19</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1262428330.062771</t>
+          <t>1277290203.855908</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1240830994.0</t>
+          <t>1255836276.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>1245653950.0</t>
+          <t>1252285381.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1903186736.8</t>
+          <t>1915488903.2</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>2354204015.62</t>
+          <t>2294509276.16</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-657532786</t>
+          <t>-663203521</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-75034613.28045648</t>
+          <t>-89001947.88941646</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-160194679.01</v>
+        <v>-165822288.24</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>62.66</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>454436</t>
+          <t>426678</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/酚醛樹脂.xlsx
+++ b/Result/checksun_type/酚醛樹脂.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5612.57</t>
+          <t>7921.053</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>18.21</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,42 +1009,42 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>51.71</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,27 +1054,27 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>40.66</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>38.97</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-26.63</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1089,51 +1089,51 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-105.13</t>
+          <t>-105.10</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/20</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>207432458.0878963</t>
+          <t>207825374.4215828</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>218861506.0</t>
+          <t>320339540.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>312474732.2</t>
+          <t>322944767.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>262014209.7</t>
+          <t>273188557.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>631667121.94</t>
+          <t>613979125.7</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>50460522</t>
+          <t>49756209</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-38796255.69662388</t>
+          <t>-37892036.76308528</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-38311615.43</v>
+        <v>-32918832.63</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>47007</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7632.447</t>
+          <t>5612.57</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>39.83</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>38.66</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-23.20</t>
+          <t>-26.63</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,51 +1520,51 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.79</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/20</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>207432458.0878963</t>
+          <t>207825374.4215828</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>302806648.0</t>
+          <t>218861506.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>315723489.0</t>
+          <t>312474732.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>267936291.1</t>
+          <t>262014209.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>654424013.3</t>
+          <t>631667121.94</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>47787197</t>
+          <t>50460522</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-38884372.1089407</t>
+          <t>-38796255.69662388</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-33774672.38</v>
+        <v>-38311615.43</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>47007</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>38.5</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>39.1</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>40.45</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>38.85</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>39.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13085.646</t>
+          <t>7632.447</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.70</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,67 +1871,67 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>42.31</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>41.19</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>39.57000000000001</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>39.83</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.66</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-28.47</t>
+          <t>-23.20</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.51</t>
+          <t>-104.79</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/20</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>207432458.0878963</t>
+          <t>207825374.4215828</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>532289392.0</t>
+          <t>302806648.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>317585660.6</t>
+          <t>315723489.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>263274442.8</t>
+          <t>267936291.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>673739372.28</t>
+          <t>654424013.3</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>54311217</t>
+          <t>47787197</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-39813408.42361735</t>
+          <t>-38884372.1089407</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-35081209.22</v>
+        <v>-33774672.38</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>42.24</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>47007</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6136.175</t>
+          <t>13085.646</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>11.70</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>42.31</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>41.19</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>39.51000000000001</t>
+          <t>39.57000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>39.76</t>
+          <t>39.78</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.87</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-36.08</t>
+          <t>-28.47</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,51 +2382,51 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.19</t>
+          <t>-104.51</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/20</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>207432458.0878963</t>
+          <t>207825374.4215828</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>240426749.0</t>
+          <t>532289392.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>234858276.4</t>
+          <t>317585660.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>236240878.5</t>
+          <t>263274442.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>679732391.62</t>
+          <t>673739372.28</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1382602</t>
+          <t>54311217</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-40673808.27865538</t>
+          <t>-39813408.42361735</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-60282226.95</v>
+        <v>-35081209.22</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>47007</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6635.823</t>
+          <t>6136.175</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-17.42</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.80</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.51000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>39.76</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>41.14</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>38.33</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>-36.08</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,51 +2813,51 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-103.81</t>
+          <t>-104.19</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/20</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>207432458.0878963</t>
+          <t>207825374.4215828</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>267989366.0</t>
+          <t>240426749.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>223432348.8</t>
+          <t>234858276.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>270578244.9</t>
+          <t>236240878.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>693037521.34</t>
+          <t>679732391.62</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-47145896</t>
+          <t>-1382602</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-37108641.24703376</t>
+          <t>-40673808.27865538</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-62859746.71</v>
+        <v>-60282226.95</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>40.61</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>47007</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5872.775</t>
+          <t>6635.823</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-33.41</t>
+          <t>-17.42</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>77.42</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>7.80</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>39.52</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>39.78</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.14</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>38.16</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-40.75</t>
+          <t>-11.77</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,51 +3244,51 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-103.70</t>
+          <t>-103.81</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/20</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>207432458.0878963</t>
+          <t>207825374.4215828</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>235105290.0</t>
+          <t>267989366.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>211553687.2</t>
+          <t>223432348.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>317718579.4</t>
+          <t>270578244.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>694915339.42</t>
+          <t>693037521.34</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-106164892</t>
+          <t>-47145896</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-32426622.07125968</t>
+          <t>-37108641.24703376</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-67250064.38</v>
+        <v>-62859746.71</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>43.86</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>47007</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7951.184</t>
+          <t>5872.775</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-50.07</t>
+          <t>-33.41</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>48.72</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>28.81</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.52</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.98</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-72.18</t>
+          <t>-40.75</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,51 +3675,51 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.32</t>
+          <t>-103.70</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/20</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>207432458.0878963</t>
+          <t>207825374.4215828</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>312117506.0</t>
+          <t>235105290.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>220149093.2</t>
+          <t>211553687.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>440884400.6</t>
+          <t>317718579.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>697689583.68</t>
+          <t>694915339.42</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-220735307</t>
+          <t>-106164892</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-26095087.10550797</t>
+          <t>-32426622.07125968</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-67596864.90000001</v>
+        <v>-67250064.38</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>42.60</t>
+          <t>43.86</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>47007</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,109 +3895,109 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>7951.184</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-1.68</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-50.07</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>39.25</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>40.85</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>0.64</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>3041.179</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>39.15</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-2.22</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-66.98</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>27.6</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>40.85</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
       <c r="X9" t="inlineStr">
         <is>
           <t>4.04</t>
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>41.34</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>37.61</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-99.28</t>
+          <t>-72.18</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,51 +4106,51 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-102.72</t>
+          <t>-103.32</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/20</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>207432458.0878963</t>
+          <t>207825374.4215828</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>118652471.0</t>
+          <t>312117506.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>208963225.0</t>
+          <t>220149093.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>632911197.7</t>
+          <t>440884400.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>701089842.98</t>
+          <t>697689583.68</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-423947972</t>
+          <t>-220735307</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-18549309.32532593</t>
+          <t>-26095087.10550797</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-73929429.31</v>
+        <v>-67596864.90000001</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>41.34</t>
+          <t>42.60</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>47007</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4678.818</t>
+          <t>3041.179</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-64.91</t>
+          <t>-66.98</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>39.47</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>39.96</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.34</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>37.43</t>
+          <t>37.61</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-100.53</t>
+          <t>-99.28</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,51 +4537,51 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-102.05</t>
+          <t>-102.72</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/20</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>207432458.0878963</t>
+          <t>207825374.4215828</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>183297111.0</t>
+          <t>118652471.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>237623480.6</t>
+          <t>208963225.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>677103255.3</t>
+          <t>632911197.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>708421794.36</t>
+          <t>701089842.98</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-439479774</t>
+          <t>-423947972</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-8480196.600382902</t>
+          <t>-18549309.32532593</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-59607216.54</v>
+        <v>-73929429.31</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>41.34</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>47007</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5259.933</t>
+          <t>4678.818</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-53.20</t>
+          <t>-64.91</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>26.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>39.96</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>41.47</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>37.24</t>
+          <t>37.43</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-100.53</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,51 +4968,51 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-101.53</t>
+          <t>-102.05</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/20</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>207432458.0878963</t>
+          <t>207825374.4215828</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>208596058.0</t>
+          <t>183297111.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>317724141.0</t>
+          <t>237623480.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>678874486.1</t>
+          <t>677103255.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>711908904.88</t>
+          <t>708421794.36</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-361150345</t>
+          <t>-439479774</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>815625.206547319</t>
+          <t>-8480196.600382902</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-43944294.84</v>
+        <v>-59607216.54</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>47007</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7140.111</t>
+          <t>5259.933</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,72 +5203,72 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>40.2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-1.68</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-53.20</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>39.25</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-0.38</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-2.22</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-36.72</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,52 +5319,52 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>26.76</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>31.82</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>40.06</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5374,17 +5374,17 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>37.24</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-29.31</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5399,55 +5399,55 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-101.48</t>
+          <t>-101.53</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/20</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>207432458.0878963</t>
+          <t>207825374.4215828</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>278082320.0</t>
+          <t>208596058.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>423883471.6</t>
+          <t>317724141.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>669852008.1</t>
+          <t>678874486.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>715483441.44</t>
+          <t>711908904.88</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-245968536</t>
+          <t>-361150345</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>8953792.488120452</t>
+          <t>815625.206547319</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-22709854.78</v>
+        <v>-43944294.84</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>41.70</t>
+          <t>45.13</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>47007</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>141242.686</t>
+          <t>187213.322</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>53.41</t>
+          <t>22.40</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>885</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>141243</t>
+          <t>187213</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>76.27</t>
+          <t>95.02</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>92.09</t>
+          <t>90.43</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>55.96</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>45.98</t>
+          <t>46.69</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.49</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>45.57</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-16.45</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,45 +5840,45 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1277290203.855908</t>
+          <t>1298564577.373381</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>7717712495.0</t>
+          <t>10708653199.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>12994233691.4</t>
+          <t>11555043688.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>8470087592.9</t>
+          <t>9440522375.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>3233128694.92</t>
+          <t>3413291777.02</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>2114521313</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>1116563206.577178</t>
+          <t>1194818526.125685</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>1742974531.81</v>
+        <v>1625222783.64</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>28.40</t>
+          <t>35.08</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>426678</t>
+          <t>448884</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>56.6</t>
-        </is>
-      </c>
-      <c r="CD13" t="inlineStr">
-        <is>
-          <t>56.8</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>53.8</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>237895.796</t>
+          <t>141242.686</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>67.79</t>
+          <t>53.41</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>70.60</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>885</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>141243</t>
+          <t>187213</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.27</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.09</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>45.39</t>
+          <t>45.98</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>41.49</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>77.41</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-27.97</t>
+          <t>-16.45</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,27 +6271,27 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1277290203.855908</t>
+          <t>1298564577.373381</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>13894804772.0</t>
+          <t>7717712495.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>13127790722.4</t>
+          <t>12994233691.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>7823899971.0</t>
+          <t>8470087592.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>3109382048.22</t>
+          <t>3233128694.92</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -6301,15 +6301,15 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>1002670238.352965</t>
+          <t>1116563206.577178</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>2169400157.06</v>
+        <v>1742974531.81</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>28.40</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>426678</t>
+          <t>448884</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>216309.874</t>
+          <t>237895.796</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>67.79</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>26.49</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>64.20</t>
+          <t>70.60</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>885</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>141243</t>
+          <t>187213</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>20.30</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>44.62</t>
+          <t>45.39</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.22</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>91.69</t>
+          <t>77.41</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-41.91</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,27 +6702,27 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1277290203.855908</t>
+          <t>1298564577.373381</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>12606646015.0</t>
+          <t>13894804772.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>11463824233.2</t>
+          <t>13127790722.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>6558502593.2</t>
+          <t>7823899971.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>2879764455.78</t>
+          <t>3109382048.22</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -6732,15 +6732,15 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>790537525.8613333</t>
+          <t>1002670238.352965</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>2039269729.26</v>
+        <v>2169400157.06</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>426678</t>
+          <t>448884</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>235389.305</t>
+          <t>216309.874</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>73.90</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>64.20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>885</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>141243</t>
+          <t>187213</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,57 +7063,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.62</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>41.17</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>104.45</t>
+          <t>91.69</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-55.23</t>
+          <t>-41.91</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,27 +7133,27 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1277290203.855908</t>
+          <t>1298564577.373381</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>12847401961.0</t>
+          <t>12606646015.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>9374723094.8</t>
+          <t>11463824233.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>5390815186.5</t>
+          <t>6558502593.2</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>2722439698.1</t>
+          <t>2879764455.78</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -7163,15 +7163,15 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>563495307.060791</t>
+          <t>790537525.8613333</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>1918555066.05</v>
+        <v>2039269729.26</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>32.70</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>426678</t>
+          <t>448884</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>336947.705</t>
+          <t>235389.305</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>70.38</t>
+          <t>73.90</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>22.74</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>885</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>141243</t>
+          <t>187213</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7494,57 +7494,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>43.19</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.17</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>105.78</t>
+          <t>104.45</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-66.92</t>
+          <t>-55.23</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,27 +7564,27 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1277290203.855908</t>
+          <t>1298564577.373381</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>17904603214.0</t>
+          <t>12847401961.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>7326001062.4</t>
+          <t>9374723094.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>4299803431.4</t>
+          <t>5390815186.5</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>2525457286.94</t>
+          <t>2722439698.1</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -7594,15 +7594,15 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>317120805.4261836</t>
+          <t>563495307.060791</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>1651790443.46</v>
+        <v>1918555066.05</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>28.40</t>
+          <t>32.70</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7667,17 +7667,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>426678</t>
+          <t>448884</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>174611.856</t>
+          <t>336947.705</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>51.82</t>
+          <t>70.38</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7884,33 +7884,33 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>51.82</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>885</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>141243</t>
+          <t>187213</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7925,57 +7925,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>44.51000000000001</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>43.19</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>105.78</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-75.67</t>
+          <t>-66.92</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,45 +7995,45 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1277290203.855908</t>
+          <t>1298564577.373381</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>8385497650.0</t>
+          <t>17904603214.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>3945941494.4</t>
+          <t>7326001062.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>2599113437.9</t>
+          <t>4299803431.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>2229827006.08</t>
+          <t>2525457286.94</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>1346828056</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>74453598.5111188</t>
+          <t>317120805.4261836</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>669862618.24</v>
+        <v>1651790443.46</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>28.40</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>426678</t>
+          <t>448884</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>123131.763</t>
+          <t>174611.856</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,74 +8220,74 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>49.8</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>12.01</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4.44</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>51.82</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>15.8</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4.79</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>33.84</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-11-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
       <c r="T19" t="inlineStr">
         <is>
           <t>41.45</t>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>51.82</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>885</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>141243</t>
+          <t>187213</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8356,57 +8356,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>44.51000000000001</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>42.04</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>39.67</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-80.44</t>
+          <t>-75.67</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,45 +8426,45 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1277290203.855908</t>
+          <t>1298564577.373381</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>5574972326.0</t>
+          <t>8385497650.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>2520009219.6</t>
+          <t>3945941494.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1882831584.8</t>
+          <t>2599113437.9</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>2124977087.88</t>
+          <t>2229827006.08</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>637177634</t>
+          <t>1346828056</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-33802586.89407057</t>
+          <t>74453598.5111188</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>263089084.85</v>
+        <v>669862618.24</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>426678</t>
+          <t>448884</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>50200.655</t>
+          <t>123131.763</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,22 +8661,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>19.96</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>33.84</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14.90</t>
+          <t>36.54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8767,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>885</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>141243</t>
+          <t>187213</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8782,62 +8782,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>42.04</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.67</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-81.87</t>
+          <t>-80.44</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,45 +8857,45 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1277290203.855908</t>
+          <t>1298564577.373381</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>2161140323.0</t>
+          <t>5574972326.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>1653180953.2</t>
+          <t>2520009219.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1524676764.0</t>
+          <t>1882831584.8</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>2166955811.48</t>
+          <t>2124977087.88</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>128504189</t>
+          <t>637177634</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-87782890.84686022</t>
+          <t>-33802586.89407057</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-26284288.32</v>
+        <v>263089084.85</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>426678</t>
+          <t>448884</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
+          <t>43.65</t>
+        </is>
+      </c>
+      <c r="CD20" t="inlineStr">
+        <is>
+          <t>46.45</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
           <t>43.5</t>
         </is>
       </c>
-      <c r="CD20" t="inlineStr">
-        <is>
-          <t>43.6</t>
-        </is>
-      </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>42.2</t>
-        </is>
-      </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>61106.691</t>
+          <t>50200.655</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>20.91</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9177,33 +9177,33 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>14.90</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>885</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>141243</t>
+          <t>187213</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9213,57 +9213,57 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>44.17</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>41.58</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>40.57</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-20.69</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-81.72</t>
+          <t>-81.87</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1277290203.855908</t>
+          <t>1298564577.373381</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>2603791799.0</t>
+          <t>2161140323.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>1406907278.2</t>
+          <t>1653180953.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1594504915.6</t>
+          <t>1524676764.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>2259840073.84</t>
+          <t>2166955811.48</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-187597637</t>
+          <t>128504189</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-98964454.94313243</t>
+          <t>-87782890.84686022</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-72968382.22</v>
+        <v>-26284288.32</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,22 +9386,22 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>426678</t>
+          <t>448884</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>24192.572</t>
+          <t>61106.691</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>22.58</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-26.02</t>
+          <t>-11.77</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.18</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,52 +9629,52 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>885</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>141243</t>
+          <t>187213</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>44.17</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.58</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.84</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
@@ -9684,22 +9684,22 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>39.07</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-33.02</t>
+          <t>-20.69</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-80.77</t>
+          <t>-81.72</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1277290203.855908</t>
+          <t>1298564577.373381</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1004305374.0</t>
+          <t>2603791799.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>1273605800.4</t>
+          <t>1406907278.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1721626446.0</t>
+          <t>1594504915.6</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>2273444052.96</t>
+          <t>2259840073.84</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-448020645</t>
+          <t>-187597637</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-103691013.6203629</t>
+          <t>-98964454.94313243</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-184480875.14</v>
+        <v>-72968382.22</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9862,7 +9862,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>426678</t>
+          <t>448884</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>31076.84</t>
+          <t>24192.572</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>23.79</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-34.62</t>
+          <t>-26.02</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,32 +10060,32 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>885</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>141243</t>
+          <t>187213</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -10095,42 +10095,42 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>41.79</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.57</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>38.88</t>
+          <t>39.07</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-33.84</t>
+          <t>-33.02</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-79.19</t>
+          <t>-80.77</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1277290203.855908</t>
+          <t>1298564577.373381</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1255836276.0</t>
+          <t>1004305374.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>1252285381.4</t>
+          <t>1273605800.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1915488903.2</t>
+          <t>1721626446.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>2294509276.16</t>
+          <t>2273444052.96</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-663203521</t>
+          <t>-448020645</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-89001947.88941646</t>
+          <t>-103691013.6203629</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-165822288.24</v>
+        <v>-184480875.14</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>426678</t>
+          <t>448884</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/酚醛樹脂.xlsx
+++ b/Result/checksun_type/酚醛樹脂.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9258.407</t>
+          <t>4826.572</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.16</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>39.91</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>40.53</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-32.78</t>
+          <t>-27.86</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-105.55</t>
+          <t>-105.97</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>208293665.2801724</t>
+          <t>208400181.8909613</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>355837208.0</t>
+          <t>188357162.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>346026858.8</t>
+          <t>277240412.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>290442567.6</t>
+          <t>297413036.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>558638708.96</t>
+          <t>528814161.92</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>55584291</t>
+          <t>-20172623</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-36009967.83841468</t>
+          <t>-35469350.75108638</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-25658588.75272644</t>
+          <t>-32495956.77078068</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>355837208</v>
+        <v>188357162</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>44780</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7921.053</t>
+          <t>9258.407</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>19.14</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>39.94</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>40.66</t>
+          <t>40.53</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>38.97</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-32.78</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-105.10</t>
+          <t>-105.55</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>208293665.2801724</t>
+          <t>208400181.8909613</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>320339540.0</t>
+          <t>355837208.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>322944767.0</t>
+          <t>346026858.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>273188557.9</t>
+          <t>290442567.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>613979125.7</t>
+          <t>558638708.96</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>49756209</t>
+          <t>55584291</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-37892036.76308528</t>
+          <t>-36009967.83841468</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-32918832.62862295</t>
+          <t>-25658588.75272644</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>320339540</v>
+        <v>355837208</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>44780</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5612.57</t>
+          <t>7921.053</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>18.21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,42 +1886,42 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>51.71</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1931,27 +1931,27 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>40.66</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>38.97</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-26.63</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-105.13</t>
+          <t>-105.10</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>208293665.2801724</t>
+          <t>208400181.8909613</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>218861506.0</t>
+          <t>320339540.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>312474732.2</t>
+          <t>322944767.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>262014209.7</t>
+          <t>273188557.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>631667121.94</t>
+          <t>613979125.7</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>50460522</t>
+          <t>49756209</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-38796255.69662388</t>
+          <t>-37892036.76308528</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-38311615.42888141</t>
+          <t>-32918832.62862295</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>218861506</v>
+        <v>320339540</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>44780</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7632.447</t>
+          <t>5612.57</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>39.83</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>38.66</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-23.20</t>
+          <t>-26.63</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.79</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>208293665.2801724</t>
+          <t>208400181.8909613</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>302806648.0</t>
+          <t>218861506.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>315723489.0</t>
+          <t>312474732.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>267936291.1</t>
+          <t>262014209.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>654424013.3</t>
+          <t>631667121.94</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>47787197</t>
+          <t>50460522</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-38884372.1089407</t>
+          <t>-38796255.69662388</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-33774672.37821913</t>
+          <t>-38311615.42888141</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>302806648</v>
+        <v>218861506</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>44780</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>38.5</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>39.1</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>40.45</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>38.85</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>39.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13085.646</t>
+          <t>7632.447</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.70</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,67 +2758,67 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>42.31</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>41.19</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>39.57000000000001</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>39.83</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.66</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-28.47</t>
+          <t>-23.20</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.51</t>
+          <t>-104.79</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>208293665.2801724</t>
+          <t>208400181.8909613</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>532289392.0</t>
+          <t>302806648.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>317585660.6</t>
+          <t>315723489.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>263274442.8</t>
+          <t>267936291.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>673739372.28</t>
+          <t>654424013.3</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>54311217</t>
+          <t>47787197</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-39813408.42361735</t>
+          <t>-38884372.1089407</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-35081209.22090816</t>
+          <t>-33774672.37821913</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>532289392</v>
+        <v>302806648</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>42.24</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>44780</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6136.175</t>
+          <t>13085.646</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>11.70</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>42.31</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>41.19</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>39.51000000000001</t>
+          <t>39.57000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>39.76</t>
+          <t>39.78</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.87</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-36.08</t>
+          <t>-28.47</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.19</t>
+          <t>-104.51</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>208293665.2801724</t>
+          <t>208400181.8909613</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>240426749.0</t>
+          <t>532289392.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>234858276.4</t>
+          <t>317585660.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>236240878.5</t>
+          <t>263274442.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>679732391.62</t>
+          <t>673739372.28</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1382602</t>
+          <t>54311217</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-40673808.27865538</t>
+          <t>-39813408.42361735</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-60282226.95257431</t>
+          <t>-35081209.22090816</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>240426749</v>
+        <v>532289392</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>44780</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6635.823</t>
+          <t>6136.175</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-17.42</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.80</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.51000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>39.76</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>41.14</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>38.33</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>-36.08</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.81</t>
+          <t>-104.19</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>208293665.2801724</t>
+          <t>208400181.8909613</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>267989366.0</t>
+          <t>240426749.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>223432348.8</t>
+          <t>234858276.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>270578244.9</t>
+          <t>236240878.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>693037521.34</t>
+          <t>679732391.62</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-47145896</t>
+          <t>-1382602</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-37108641.24703376</t>
+          <t>-40673808.27865538</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-62859746.71379119</t>
+          <t>-60282226.95257431</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>267989366</v>
+        <v>240426749</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>40.61</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>44780</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5872.775</t>
+          <t>6635.823</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-33.41</t>
+          <t>-17.42</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>77.42</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>7.80</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>39.52</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>39.78</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.14</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>38.16</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-40.75</t>
+          <t>-11.77</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.70</t>
+          <t>-103.81</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>208293665.2801724</t>
+          <t>208400181.8909613</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>235105290.0</t>
+          <t>267989366.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>211553687.2</t>
+          <t>223432348.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>317718579.4</t>
+          <t>270578244.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>694915339.42</t>
+          <t>693037521.34</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-106164892</t>
+          <t>-47145896</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-32426622.07125968</t>
+          <t>-37108641.24703376</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-67250064.3828941</t>
+          <t>-62859746.71379119</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>235105290</v>
+        <v>267989366</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>43.86</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>44780</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7951.184</t>
+          <t>5872.775</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-50.07</t>
+          <t>-33.41</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>48.72</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>28.81</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.52</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.98</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-72.18</t>
+          <t>-40.75</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.32</t>
+          <t>-103.70</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>208293665.2801724</t>
+          <t>208400181.8909613</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>312117506.0</t>
+          <t>235105290.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>220149093.2</t>
+          <t>211553687.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>440884400.6</t>
+          <t>317718579.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>697689583.68</t>
+          <t>694915339.42</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-220735307</t>
+          <t>-106164892</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-26095087.10550797</t>
+          <t>-32426622.07125968</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-67596864.89650917</t>
+          <t>-67250064.3828941</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>312117506</v>
+        <v>235105290</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>42.60</t>
+          <t>43.86</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>44780</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,109 +4807,109 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>7951.184</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-1.28</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-2.3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-50.07</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>39.25</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>40.85</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>0.64</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>3041.179</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>39.15</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-2.49</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-3.21</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-66.98</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>27.6</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>40.85</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
       <c r="X11" t="inlineStr">
         <is>
           <t>4.04</t>
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>41.34</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>37.61</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-99.28</t>
+          <t>-72.18</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-102.72</t>
+          <t>-103.32</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>208293665.2801724</t>
+          <t>208400181.8909613</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>118652471.0</t>
+          <t>312117506.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>208963225.0</t>
+          <t>220149093.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>632911197.7</t>
+          <t>440884400.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>701089842.98</t>
+          <t>697689583.68</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-423947972</t>
+          <t>-220735307</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-18549309.32532593</t>
+          <t>-26095087.10550797</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-73929429.31251258</t>
+          <t>-67596864.89650917</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>118652471</v>
+        <v>312117506</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>41.34</t>
+          <t>42.60</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>44780</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4678.818</t>
+          <t>3041.179</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-64.91</t>
+          <t>-66.98</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>39.47</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>39.96</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.34</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>37.43</t>
+          <t>37.61</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-100.53</t>
+          <t>-99.28</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.05</t>
+          <t>-102.72</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>208293665.2801724</t>
+          <t>208400181.8909613</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>183297111.0</t>
+          <t>118652471.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>237623480.6</t>
+          <t>208963225.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>677103255.3</t>
+          <t>632911197.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>708421794.36</t>
+          <t>701089842.98</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-439479774</t>
+          <t>-423947972</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-8480196.600382902</t>
+          <t>-18549309.32532593</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-59607216.53849912</t>
+          <t>-73929429.31251258</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>183297111</v>
+        <v>118652471</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>41.34</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>44780</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>87722.137</t>
+          <t>89940.447</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>20.97</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.69</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,82 +5810,82 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>470</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>87722</t>
+          <t>89940</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>73.89</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>15.21</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>55.34</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>47.74</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>43.12</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.97</t>
+          <t>42.21</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>21.20</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
@@ -5900,50 +5900,50 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1306745564.743535</t>
+          <t>1315308613.441894</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>4661687858.0</t>
+          <t>4850127005.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>9917900867.8</t>
+          <t>8366597065.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>9646311981.3</t>
+          <t>9915210649.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>3483979320.62</t>
+          <t>3525171118.12</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>271588886</t>
+          <t>-1548613583</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>1172330074.37695</t>
+          <t>1089349293.753025</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>1048643589.758906</t>
+          <t>632955000.321434</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>4661687858</v>
+        <v>4850127005</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>30.79</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>416368</t>
+          <t>434609</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>187213.322</t>
+          <t>87722.137</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-7.81</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>22.40</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,87 +6246,87 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>470</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>87722</t>
+          <t>89940</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>95.02</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>90.43</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>17.38</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>55.96</t>
+          <t>55.34</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>46.69</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>41.97</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>45.57</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,50 +6336,50 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1306745564.743535</t>
+          <t>1315308613.441894</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>10708653199.0</t>
+          <t>4661687858.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>11555043688.4</t>
+          <t>9917900867.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>9440522375.4</t>
+          <t>9646311981.3</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>3413291777.02</t>
+          <t>3483979320.62</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>2114521313</t>
+          <t>271588886</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>1194818526.125685</t>
+          <t>1172330074.37695</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>1625222783.642477</t>
+          <t>1048643589.758906</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>10708653199</v>
+        <v>4661687858</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>35.08</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>416368</t>
+          <t>434609</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>141242.686</t>
+          <t>187213.322</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>53.41</t>
+          <t>22.40</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,87 +6682,87 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>470</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>87722</t>
+          <t>89940</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>76.27</t>
+          <t>95.02</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>92.09</t>
+          <t>90.43</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>55.96</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>45.98</t>
+          <t>46.69</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.49</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>45.57</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-17.70</t>
+          <t>-12.05</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,50 +6772,50 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1306745564.743535</t>
+          <t>1315308613.441894</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>7717712495.0</t>
+          <t>10708653199.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>12994233691.4</t>
+          <t>11555043688.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>8470087592.9</t>
+          <t>9440522375.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>3233128694.92</t>
+          <t>3413291777.02</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>2114521313</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>1116563206.577178</t>
+          <t>1194818526.125685</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>1742974531.810349</t>
+          <t>1625222783.642477</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>7717712495</v>
+        <v>10708653199</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>28.40</t>
+          <t>35.08</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>416368</t>
+          <t>434609</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
           <t>56.6</t>
-        </is>
-      </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>56.8</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="CG15" t="inlineStr">
-        <is>
-          <t>53.8</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>237895.796</t>
+          <t>141242.686</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>67.79</t>
+          <t>53.41</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>70.60</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,87 +7118,87 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>470</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>87722</t>
+          <t>89940</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.27</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.09</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>45.39</t>
+          <t>45.98</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>41.49</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>77.41</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-29.05</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,27 +7208,27 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1306745564.743535</t>
+          <t>1315308613.441894</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>13894804772.0</t>
+          <t>7717712495.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>13127790722.4</t>
+          <t>12994233691.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>7823899971.0</t>
+          <t>8470087592.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>3109382048.22</t>
+          <t>3233128694.92</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -7238,20 +7238,20 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>1002670238.352965</t>
+          <t>1116563206.577178</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>2169400157.056937</t>
+          <t>1742974531.810349</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>13894804772</v>
+        <v>7717712495</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>28.40</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7321,12 +7321,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>416368</t>
+          <t>434609</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>216309.874</t>
+          <t>237895.796</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>67.79</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>26.49</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>64.20</t>
+          <t>70.60</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>470</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>87722</t>
+          <t>89940</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,67 +7574,67 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>20.30</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>44.62</t>
+          <t>45.39</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.22</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>91.69</t>
+          <t>77.41</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-42.78</t>
+          <t>-32.81</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,27 +7644,27 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1306745564.743535</t>
+          <t>1315308613.441894</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>12606646015.0</t>
+          <t>13894804772.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>11463824233.2</t>
+          <t>13127790722.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>6558502593.2</t>
+          <t>7823899971.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>2879764455.78</t>
+          <t>3109382048.22</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -7674,20 +7674,20 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>790537525.8613333</t>
+          <t>1002670238.352965</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>2039269729.264316</t>
+          <t>2169400157.056937</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>12606646015</v>
+        <v>13894804772</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>416368</t>
+          <t>434609</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>235389.305</t>
+          <t>216309.874</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-5.9</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>73.90</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>64.20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>470</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>87722</t>
+          <t>89940</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,67 +8010,67 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.62</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>41.17</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>104.45</t>
+          <t>91.69</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-55.90</t>
+          <t>-45.82</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,27 +8080,27 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1306745564.743535</t>
+          <t>1315308613.441894</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>12847401961.0</t>
+          <t>12606646015.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>9374723094.8</t>
+          <t>11463824233.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>5390815186.5</t>
+          <t>6558502593.2</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>2722439698.1</t>
+          <t>2879764455.78</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -8110,20 +8110,20 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>563495307.060791</t>
+          <t>790537525.8613333</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>1918555066.051131</t>
+          <t>2039269729.264316</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>12847401961</v>
+        <v>12606646015</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>32.70</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>416368</t>
+          <t>434609</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>336947.705</t>
+          <t>235389.305</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>70.38</t>
+          <t>73.90</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>22.74</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>470</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>87722</t>
+          <t>89940</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,67 +8446,67 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>43.19</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.17</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>105.78</t>
+          <t>104.45</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-67.41</t>
+          <t>-58.24</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,27 +8516,27 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1306745564.743535</t>
+          <t>1315308613.441894</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>17904603214.0</t>
+          <t>12847401961.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>7326001062.4</t>
+          <t>9374723094.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>4299803431.4</t>
+          <t>5390815186.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>2525457286.94</t>
+          <t>2722439698.1</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -8546,20 +8546,20 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>317120805.4261836</t>
+          <t>563495307.060791</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>1651790443.45904</t>
+          <t>1918555066.051131</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>17904603214</v>
+        <v>12847401961</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>28.40</t>
+          <t>32.70</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8624,17 +8624,17 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>416368</t>
+          <t>434609</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>174611.856</t>
+          <t>336947.705</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>51.82</t>
+          <t>70.38</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8841,33 +8841,33 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>51.82</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>470</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>87722</t>
+          <t>89940</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8882,67 +8882,67 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>44.51000000000001</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>43.19</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>105.78</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-76.03</t>
+          <t>-69.14</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,50 +8952,50 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1306745564.743535</t>
+          <t>1315308613.441894</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>8385497650.0</t>
+          <t>17904603214.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>3945941494.4</t>
+          <t>7326001062.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>2599113437.9</t>
+          <t>4299803431.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>2229827006.08</t>
+          <t>2525457286.94</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>1346828056</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>74453598.5111188</t>
+          <t>317120805.4261836</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>669862618.2396603</t>
+          <t>1651790443.45904</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>8385497650</v>
+        <v>17904603214</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>28.40</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>416368</t>
+          <t>434609</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>123131.763</t>
+          <t>174611.856</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,74 +9182,74 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>49.8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>9.12</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>51.82</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>13.71</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>33.84</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-11-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>41.45</t>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>51.82</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>470</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>87722</t>
+          <t>89940</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9318,67 +9318,67 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>44.51000000000001</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>42.04</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>39.67</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-80.73</t>
+          <t>-77.30</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,50 +9388,50 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1306745564.743535</t>
+          <t>1315308613.441894</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>5574972326.0</t>
+          <t>8385497650.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>2520009219.6</t>
+          <t>3945941494.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1882831584.8</t>
+          <t>2599113437.9</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>2124977087.88</t>
+          <t>2229827006.08</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>637177634</t>
+          <t>1346828056</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-33802586.89407057</t>
+          <t>74453598.5111188</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>263089084.8462725</t>
+          <t>669862618.2396603</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>5574972326</v>
+        <v>8385497650</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>416368</t>
+          <t>434609</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>50200.655</t>
+          <t>123131.763</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,27 +9628,27 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>17.62</t>
+          <t>17.34</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>33.84</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14.90</t>
+          <t>36.54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>470</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>87722</t>
+          <t>89940</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9749,72 +9749,72 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>42.04</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.67</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-82.14</t>
+          <t>-81.75</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,50 +9824,50 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1306745564.743535</t>
+          <t>1315308613.441894</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>2161140323.0</t>
+          <t>5574972326.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>1653180953.2</t>
+          <t>2520009219.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1524676764.0</t>
+          <t>1882831584.8</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>2166955811.48</t>
+          <t>2124977087.88</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>128504189</t>
+          <t>637177634</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-87782890.84686022</t>
+          <t>-33802586.89407057</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-26284288.31736302</t>
+          <t>263089084.8462725</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>2161140323</v>
+        <v>5574972326</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>416368</t>
+          <t>434609</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
+          <t>43.65</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
+          <t>46.45</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
           <t>43.5</t>
         </is>
       </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>43.6</t>
-        </is>
-      </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>42.2</t>
-        </is>
-      </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>61106.691</t>
+          <t>50200.655</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>21.08</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10149,33 +10149,33 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>14.90</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>470</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>87722</t>
+          <t>89940</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10185,57 +10185,57 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>44.17</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>41.58</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>40.57</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-20.69</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-81.99</t>
+          <t>-83.09</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1306745564.743535</t>
+          <t>1315308613.441894</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>2603791799.0</t>
+          <t>2161140323.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>1406907278.2</t>
+          <t>1653180953.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1594504915.6</t>
+          <t>1524676764.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>2259840073.84</t>
+          <t>2166955811.48</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-187597637</t>
+          <t>128504189</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-98964454.94313243</t>
+          <t>-87782890.84686022</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-72968382.21836472</t>
+          <t>-26284288.31736302</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>2603791799</v>
+        <v>2161140323</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>62.69</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>416368</t>
+          <t>434609</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/酚醛樹脂.xlsx
+++ b/Result/checksun_type/酚醛樹脂.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4826.572</t>
+          <t>5013.788</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-10.48</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>39.16</t>
+          <t>39.04000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>39.71</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.26</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-27.86</t>
+          <t>-27.08</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-105.97</t>
+          <t>-106.40</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>208400181.8909613</t>
+          <t>208521987.2793697</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>188357162.0</t>
+          <t>195613562.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>277240412.8</t>
+          <t>255801795.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>297413036.7</t>
+          <t>285762642.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>528814161.92</t>
+          <t>457544220.78</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-20172623</t>
+          <t>-29960846</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-35469350.75108638</t>
+          <t>-35539525.3223268</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-32495956.77078068</t>
+          <t>-35925485.46414912</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>188357162</v>
+        <v>195613562</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>45483</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9258.407</t>
+          <t>4826.572</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.16</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>39.91</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>40.53</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-32.78</t>
+          <t>-27.86</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-105.55</t>
+          <t>-105.97</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>208400181.8909613</t>
+          <t>208521987.2793697</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>355837208.0</t>
+          <t>188357162.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>346026858.8</t>
+          <t>277240412.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>290442567.6</t>
+          <t>297413036.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>558638708.96</t>
+          <t>528814161.92</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>55584291</t>
+          <t>-20172623</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-36009967.83841468</t>
+          <t>-35469350.75108638</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-25658588.75272644</t>
+          <t>-32495956.77078068</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>355837208</v>
+        <v>188357162</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>45483</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7921.053</t>
+          <t>9258.407</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>19.14</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>39.94</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>40.66</t>
+          <t>40.53</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>38.97</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-32.78</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-105.10</t>
+          <t>-105.55</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>208400181.8909613</t>
+          <t>208521987.2793697</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>320339540.0</t>
+          <t>355837208.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>322944767.0</t>
+          <t>346026858.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>273188557.9</t>
+          <t>290442567.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>613979125.7</t>
+          <t>558638708.96</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>49756209</t>
+          <t>55584291</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-37892036.76308528</t>
+          <t>-36009967.83841468</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-32918832.62862295</t>
+          <t>-25658588.75272644</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>320339540</v>
+        <v>355837208</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>45483</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5612.57</t>
+          <t>7921.053</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>18.21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,42 +2322,42 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>51.71</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2367,27 +2367,27 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>40.66</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>38.97</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-26.63</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.13</t>
+          <t>-105.10</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>208400181.8909613</t>
+          <t>208521987.2793697</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>218861506.0</t>
+          <t>320339540.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>312474732.2</t>
+          <t>322944767.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>262014209.7</t>
+          <t>273188557.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>631667121.94</t>
+          <t>613979125.7</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>50460522</t>
+          <t>49756209</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-38796255.69662388</t>
+          <t>-37892036.76308528</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-38311615.42888141</t>
+          <t>-32918832.62862295</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>218861506</v>
+        <v>320339540</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>45483</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7632.447</t>
+          <t>5612.57</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>39.83</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>38.66</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-23.20</t>
+          <t>-26.63</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.79</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>208400181.8909613</t>
+          <t>208521987.2793697</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>302806648.0</t>
+          <t>218861506.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>315723489.0</t>
+          <t>312474732.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>267936291.1</t>
+          <t>262014209.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>654424013.3</t>
+          <t>631667121.94</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>47787197</t>
+          <t>50460522</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-38884372.1089407</t>
+          <t>-38796255.69662388</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-33774672.37821913</t>
+          <t>-38311615.42888141</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>302806648</v>
+        <v>218861506</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>45483</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>38.5</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>39.1</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>40.45</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>38.85</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>39.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13085.646</t>
+          <t>7632.447</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.70</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,67 +3194,67 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>42.31</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>41.19</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>39.57000000000001</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>39.83</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.66</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-28.47</t>
+          <t>-23.20</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.51</t>
+          <t>-104.79</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>208400181.8909613</t>
+          <t>208521987.2793697</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>532289392.0</t>
+          <t>302806648.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>317585660.6</t>
+          <t>315723489.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>263274442.8</t>
+          <t>267936291.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>673739372.28</t>
+          <t>654424013.3</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>54311217</t>
+          <t>47787197</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-39813408.42361735</t>
+          <t>-38884372.1089407</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-35081209.22090816</t>
+          <t>-33774672.37821913</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>532289392</v>
+        <v>302806648</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>42.24</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>45483</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6136.175</t>
+          <t>13085.646</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>11.70</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>42.31</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>41.19</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>39.51000000000001</t>
+          <t>39.57000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>39.76</t>
+          <t>39.78</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.87</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-36.08</t>
+          <t>-28.47</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.19</t>
+          <t>-104.51</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>208400181.8909613</t>
+          <t>208521987.2793697</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>240426749.0</t>
+          <t>532289392.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>234858276.4</t>
+          <t>317585660.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>236240878.5</t>
+          <t>263274442.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>679732391.62</t>
+          <t>673739372.28</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1382602</t>
+          <t>54311217</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-40673808.27865538</t>
+          <t>-39813408.42361735</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-60282226.95257431</t>
+          <t>-35081209.22090816</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>240426749</v>
+        <v>532289392</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>45483</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6635.823</t>
+          <t>6136.175</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,102 +3960,102 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-2.09</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-0.59</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>39.25</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>40.85</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>-0.76</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>5.49</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
           <t>-2.82</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-2.3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-17.42</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>27.6</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>40.85</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4.04</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>5.94</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>-0.73</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.80</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.51000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>39.76</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>41.14</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>38.33</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>-36.08</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.81</t>
+          <t>-104.19</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>208400181.8909613</t>
+          <t>208521987.2793697</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>267989366.0</t>
+          <t>240426749.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>223432348.8</t>
+          <t>234858276.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>270578244.9</t>
+          <t>236240878.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>693037521.34</t>
+          <t>679732391.62</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-47145896</t>
+          <t>-1382602</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-37108641.24703376</t>
+          <t>-40673808.27865538</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-62859746.71379119</t>
+          <t>-60282226.95257431</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>267989366</v>
+        <v>240426749</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>40.61</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>45483</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5872.775</t>
+          <t>6635.823</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-33.41</t>
+          <t>-17.42</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>77.42</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>7.80</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>39.52</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>39.78</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.14</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>38.16</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-40.75</t>
+          <t>-11.77</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.70</t>
+          <t>-103.81</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>208400181.8909613</t>
+          <t>208521987.2793697</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>235105290.0</t>
+          <t>267989366.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>211553687.2</t>
+          <t>223432348.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>317718579.4</t>
+          <t>270578244.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>694915339.42</t>
+          <t>693037521.34</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-106164892</t>
+          <t>-47145896</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-32426622.07125968</t>
+          <t>-37108641.24703376</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-67250064.3828941</t>
+          <t>-62859746.71379119</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>235105290</v>
+        <v>267989366</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>43.86</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>45483</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7951.184</t>
+          <t>5872.775</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-50.07</t>
+          <t>-33.41</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>48.72</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>28.81</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.52</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.98</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-72.18</t>
+          <t>-40.75</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.32</t>
+          <t>-103.70</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>208400181.8909613</t>
+          <t>208521987.2793697</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>312117506.0</t>
+          <t>235105290.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>220149093.2</t>
+          <t>211553687.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>440884400.6</t>
+          <t>317718579.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>697689583.68</t>
+          <t>694915339.42</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-220735307</t>
+          <t>-106164892</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-26095087.10550797</t>
+          <t>-32426622.07125968</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-67596864.89650917</t>
+          <t>-67250064.3828941</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>312117506</v>
+        <v>235105290</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>42.60</t>
+          <t>43.86</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>45483</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,109 +5243,109 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>7951.184</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-1.8</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-2.09</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-50.07</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>39.25</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>40.85</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
           <t>0.64</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>3041.179</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>39.15</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-0.38</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-2.3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-66.98</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>27.6</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>40.85</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
       <c r="X12" t="inlineStr">
         <is>
           <t>4.04</t>
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>41.34</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>37.61</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-99.28</t>
+          <t>-72.18</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.72</t>
+          <t>-103.32</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>208400181.8909613</t>
+          <t>208521987.2793697</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>118652471.0</t>
+          <t>312117506.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>208963225.0</t>
+          <t>220149093.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>632911197.7</t>
+          <t>440884400.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>701089842.98</t>
+          <t>697689583.68</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-423947972</t>
+          <t>-220735307</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-18549309.32532593</t>
+          <t>-26095087.10550797</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-73929429.31251258</t>
+          <t>-67596864.89650917</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>118652471</v>
+        <v>312117506</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>41.34</t>
+          <t>42.60</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>45483</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>89940.447</t>
+          <t>126477.283</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-15.62</t>
+          <t>-30.86</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>26.69</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,82 +5810,82 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>701</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>89940</t>
+          <t>126477</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>73.89</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>47.74</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>43.12</t>
+          <t>43.41</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>42.21</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>21.20</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
@@ -5900,50 +5900,50 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1315308613.441894</t>
+          <t>1327917603.891834</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>4850127005.0</t>
+          <t>6744255965.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>8366597065.8</t>
+          <t>6936487304.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>9915210649.5</t>
+          <t>10032139013.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>3525171118.12</t>
+          <t>3632131847.42</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-1548613583</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>1089349293.753025</t>
+          <t>993789215.4382774</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>632955000.321434</t>
+          <t>468208784.7071676</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>4850127005</v>
+        <v>6744255965</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>30.79</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>434609</t>
+          <t>415575</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>87722.137</t>
+          <t>89940.447</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>20.97</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.69</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,87 +6246,87 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>701</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>89940</t>
+          <t>126477</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>73.89</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>15.21</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>55.34</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>47.74</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>43.12</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.97</t>
+          <t>42.21</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>21.20</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,50 +6336,50 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1315308613.441894</t>
+          <t>1327917603.891834</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>4661687858.0</t>
+          <t>4850127005.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>9917900867.8</t>
+          <t>8366597065.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>9646311981.3</t>
+          <t>9915210649.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>3483979320.62</t>
+          <t>3525171118.12</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>271588886</t>
+          <t>-1548613583</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>1172330074.37695</t>
+          <t>1089349293.753025</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>1048643589.758906</t>
+          <t>632955000.321434</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>4661687858</v>
+        <v>4850127005</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>30.79</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>434609</t>
+          <t>415575</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>187213.322</t>
+          <t>87722.137</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>22.40</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,87 +6682,87 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>701</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>89940</t>
+          <t>126477</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>95.02</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>90.43</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>17.38</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>55.96</t>
+          <t>55.34</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>46.69</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>41.97</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>45.57</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-12.05</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,50 +6772,50 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1315308613.441894</t>
+          <t>1327917603.891834</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>10708653199.0</t>
+          <t>4661687858.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>11555043688.4</t>
+          <t>9917900867.8</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>9440522375.4</t>
+          <t>9646311981.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>3413291777.02</t>
+          <t>3483979320.62</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>2114521313</t>
+          <t>271588886</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>1194818526.125685</t>
+          <t>1172330074.37695</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>1625222783.642477</t>
+          <t>1048643589.758906</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>10708653199</v>
+        <v>4661687858</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>35.08</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>434609</t>
+          <t>415575</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>141242.686</t>
+          <t>187213.322</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>53.41</t>
+          <t>22.40</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,87 +7118,87 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>701</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>89940</t>
+          <t>126477</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>76.27</t>
+          <t>95.02</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>92.09</t>
+          <t>90.43</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>55.96</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>45.98</t>
+          <t>46.69</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.49</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>45.57</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-14.32</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,50 +7208,50 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1315308613.441894</t>
+          <t>1327917603.891834</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>7717712495.0</t>
+          <t>10708653199.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>12994233691.4</t>
+          <t>11555043688.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>8470087592.9</t>
+          <t>9440522375.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>3233128694.92</t>
+          <t>3413291777.02</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>2114521313</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>1116563206.577178</t>
+          <t>1194818526.125685</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>1742974531.810349</t>
+          <t>1625222783.642477</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>7717712495</v>
+        <v>10708653199</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>28.40</t>
+          <t>35.08</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>434609</t>
+          <t>415575</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="CG16" t="inlineStr">
+        <is>
           <t>56.6</t>
-        </is>
-      </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>56.8</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="CG16" t="inlineStr">
-        <is>
-          <t>53.8</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>237895.796</t>
+          <t>141242.686</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>67.79</t>
+          <t>53.41</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>70.60</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,87 +7554,87 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>701</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>89940</t>
+          <t>126477</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.27</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.09</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>45.39</t>
+          <t>45.98</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>41.49</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>77.41</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-32.81</t>
+          <t>-24.09</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,27 +7644,27 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1315308613.441894</t>
+          <t>1327917603.891834</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>13894804772.0</t>
+          <t>7717712495.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>13127790722.4</t>
+          <t>12994233691.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7823899971.0</t>
+          <t>8470087592.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>3109382048.22</t>
+          <t>3233128694.92</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -7674,20 +7674,20 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>1002670238.352965</t>
+          <t>1116563206.577178</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>2169400157.056937</t>
+          <t>1742974531.810349</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>13894804772</v>
+        <v>7717712495</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>28.40</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>434609</t>
+          <t>415575</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>216309.874</t>
+          <t>237895.796</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-9.35</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>67.79</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>26.49</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>64.20</t>
+          <t>70.60</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>701</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>89940</t>
+          <t>126477</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,67 +8010,67 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>20.30</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>44.62</t>
+          <t>45.39</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.22</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>91.69</t>
+          <t>77.41</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-45.82</t>
+          <t>-34.55</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,27 +8080,27 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1315308613.441894</t>
+          <t>1327917603.891834</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>12606646015.0</t>
+          <t>13894804772.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>11463824233.2</t>
+          <t>13127790722.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>6558502593.2</t>
+          <t>7823899971.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>2879764455.78</t>
+          <t>3109382048.22</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -8110,20 +8110,20 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>790537525.8613333</t>
+          <t>1002670238.352965</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>2039269729.264316</t>
+          <t>2169400157.056937</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>12606646015</v>
+        <v>13894804772</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>434609</t>
+          <t>415575</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>235389.305</t>
+          <t>216309.874</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-7.82</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>73.90</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>64.20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>701</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>89940</t>
+          <t>126477</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,67 +8446,67 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.62</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>41.17</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>104.45</t>
+          <t>91.69</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-58.24</t>
+          <t>-47.22</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,27 +8516,27 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1315308613.441894</t>
+          <t>1327917603.891834</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>12847401961.0</t>
+          <t>12606646015.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>9374723094.8</t>
+          <t>11463824233.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>5390815186.5</t>
+          <t>6558502593.2</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>2722439698.1</t>
+          <t>2879764455.78</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -8546,20 +8546,20 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>563495307.060791</t>
+          <t>790537525.8613333</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>1918555066.051131</t>
+          <t>2039269729.264316</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>12847401961</v>
+        <v>12606646015</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>32.70</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,24 +8619,24 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr">
+        <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="BT19" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
       <c r="BU19" t="inlineStr">
         <is>
           <t>8.09</t>
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>434609</t>
+          <t>415575</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>336947.705</t>
+          <t>235389.305</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>70.38</t>
+          <t>73.90</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>22.74</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>701</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>89940</t>
+          <t>126477</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8882,67 +8882,67 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>43.19</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.17</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>105.78</t>
+          <t>104.45</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-69.14</t>
+          <t>-59.32</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,27 +8952,27 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1315308613.441894</t>
+          <t>1327917603.891834</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>17904603214.0</t>
+          <t>12847401961.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>7326001062.4</t>
+          <t>9374723094.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>4299803431.4</t>
+          <t>5390815186.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>2525457286.94</t>
+          <t>2722439698.1</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
@@ -8982,20 +8982,20 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>317120805.4261836</t>
+          <t>563495307.060791</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>1651790443.45904</t>
+          <t>1918555066.051131</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>17904603214</v>
+        <v>12847401961</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>28.40</t>
+          <t>32.70</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9060,17 +9060,17 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>434609</t>
+          <t>415575</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>174611.856</t>
+          <t>336947.705</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>51.82</t>
+          <t>70.38</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9277,33 +9277,33 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>51.82</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>701</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>89940</t>
+          <t>126477</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9318,67 +9318,67 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>44.51000000000001</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>43.19</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>105.78</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-77.30</t>
+          <t>-69.94</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,50 +9388,50 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1315308613.441894</t>
+          <t>1327917603.891834</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>8385497650.0</t>
+          <t>17904603214.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>3945941494.4</t>
+          <t>7326001062.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>2599113437.9</t>
+          <t>4299803431.4</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>2229827006.08</t>
+          <t>2525457286.94</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>1346828056</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>74453598.5111188</t>
+          <t>317120805.4261836</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>669862618.2396603</t>
+          <t>1651790443.45904</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>8385497650</v>
+        <v>17904603214</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>28.40</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>434609</t>
+          <t>415575</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>123131.763</t>
+          <t>174611.856</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,74 +9618,74 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>49.8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>4.96</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>51.82</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>17.34</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>33.84</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
       <c r="T22" t="inlineStr">
         <is>
           <t>41.45</t>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>51.82</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>701</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>89940</t>
+          <t>126477</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9754,67 +9754,67 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>44.51000000000001</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>42.04</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>39.67</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-81.75</t>
+          <t>-77.89</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,50 +9824,50 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1315308613.441894</t>
+          <t>1327917603.891834</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>5574972326.0</t>
+          <t>8385497650.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>2520009219.6</t>
+          <t>3945941494.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1882831584.8</t>
+          <t>2599113437.9</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>2124977087.88</t>
+          <t>2229827006.08</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>637177634</t>
+          <t>1346828056</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-33802586.89407057</t>
+          <t>74453598.5111188</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>263089084.8462725</t>
+          <t>669862618.2396603</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>5574972326</v>
+        <v>8385497650</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>434609</t>
+          <t>415575</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>50200.655</t>
+          <t>123131.763</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,27 +10064,27 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>33.84</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14.90</t>
+          <t>36.54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>701</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>89940</t>
+          <t>126477</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10185,72 +10185,72 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>42.04</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.67</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-83.09</t>
+          <t>-82.23</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,50 +10260,50 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1315308613.441894</t>
+          <t>1327917603.891834</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>2161140323.0</t>
+          <t>5574972326.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>1653180953.2</t>
+          <t>2520009219.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1524676764.0</t>
+          <t>1882831584.8</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>2166955811.48</t>
+          <t>2124977087.88</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>128504189</t>
+          <t>637177634</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-87782890.84686022</t>
+          <t>-33802586.89407057</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-26284288.31736302</t>
+          <t>263089084.8462725</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>2161140323</v>
+        <v>5574972326</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>434609</t>
+          <t>415575</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
+          <t>43.65</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>46.45</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
           <t>43.5</t>
         </is>
       </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>43.6</t>
-        </is>
-      </c>
-      <c r="CF23" t="inlineStr">
-        <is>
-          <t>42.2</t>
-        </is>
-      </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/酚醛樹脂.xlsx
+++ b/Result/checksun_type/酚醛樹脂.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5013.788</t>
+          <t>5128.692</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-10.48</t>
+          <t>-10.64</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,67 +1014,67 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>39.04000000000001</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>39.71</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>40.26</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-27.08</t>
+          <t>-19.58</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.40</t>
+          <t>-106.73</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>208521987.2793697</t>
+          <t>208656413.7982833</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>195613562.0</t>
+          <t>201657416.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>255801795.6</t>
+          <t>252360977.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>285762642.3</t>
+          <t>282417854.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>457544220.78</t>
+          <t>423553251.3</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-29960846</t>
+          <t>-30056877</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-35539525.3223268</t>
+          <t>-35760325.94395395</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-35925485.46414912</t>
+          <t>-36974729.3629033</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>195613562</v>
+        <v>201657416</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>45483</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4826.572</t>
+          <t>5013.788</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-10.48</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>39.16</t>
+          <t>39.04000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>39.71</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.26</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-27.86</t>
+          <t>-27.08</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-105.97</t>
+          <t>-106.40</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>208521987.2793697</t>
+          <t>208656413.7982833</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>188357162.0</t>
+          <t>195613562.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>277240412.8</t>
+          <t>255801795.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>297413036.7</t>
+          <t>285762642.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>528814161.92</t>
+          <t>457544220.78</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-20172623</t>
+          <t>-29960846</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-35469350.75108638</t>
+          <t>-35539525.3223268</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-32495956.77078068</t>
+          <t>-35925485.46414912</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>188357162</v>
+        <v>195613562</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1648,17 +1648,17 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>45483</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9258.407</t>
+          <t>4826.572</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.16</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>39.91</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>40.53</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-32.78</t>
+          <t>-27.86</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-105.55</t>
+          <t>-105.97</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>208521987.2793697</t>
+          <t>208656413.7982833</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>355837208.0</t>
+          <t>188357162.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>346026858.8</t>
+          <t>277240412.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>290442567.6</t>
+          <t>297413036.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>558638708.96</t>
+          <t>528814161.92</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>55584291</t>
+          <t>-20172623</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-36009967.83841468</t>
+          <t>-35469350.75108638</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-25658588.75272644</t>
+          <t>-32495956.77078068</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>355837208</v>
+        <v>188357162</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>45483</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7921.053</t>
+          <t>9258.407</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>19.14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>39.94</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>40.66</t>
+          <t>40.53</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>38.97</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-32.78</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.10</t>
+          <t>-105.55</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>208521987.2793697</t>
+          <t>208656413.7982833</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>320339540.0</t>
+          <t>355837208.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>322944767.0</t>
+          <t>346026858.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>273188557.9</t>
+          <t>290442567.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>613979125.7</t>
+          <t>558638708.96</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>49756209</t>
+          <t>55584291</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-37892036.76308528</t>
+          <t>-36009967.83841468</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-32918832.62862295</t>
+          <t>-25658588.75272644</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>320339540</v>
+        <v>355837208</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>45483</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5612.57</t>
+          <t>7921.053</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>18.21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,42 +2758,42 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>51.71</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2803,27 +2803,27 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>40.66</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>38.97</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-26.63</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.13</t>
+          <t>-105.10</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>208521987.2793697</t>
+          <t>208656413.7982833</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>218861506.0</t>
+          <t>320339540.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>312474732.2</t>
+          <t>322944767.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>262014209.7</t>
+          <t>273188557.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>631667121.94</t>
+          <t>613979125.7</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>50460522</t>
+          <t>49756209</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-38796255.69662388</t>
+          <t>-37892036.76308528</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-38311615.42888141</t>
+          <t>-32918832.62862295</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>218861506</v>
+        <v>320339540</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>45483</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7632.447</t>
+          <t>5612.57</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>39.83</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>38.66</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-23.20</t>
+          <t>-26.63</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.79</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>208521987.2793697</t>
+          <t>208656413.7982833</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>302806648.0</t>
+          <t>218861506.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>315723489.0</t>
+          <t>312474732.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>267936291.1</t>
+          <t>262014209.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>654424013.3</t>
+          <t>631667121.94</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>47787197</t>
+          <t>50460522</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-38884372.1089407</t>
+          <t>-38796255.69662388</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-33774672.37821913</t>
+          <t>-38311615.42888141</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>302806648</v>
+        <v>218861506</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>45483</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>38.5</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>39.1</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>40.45</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>38.85</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>39.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13085.646</t>
+          <t>7632.447</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.70</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,67 +3630,67 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>42.31</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>41.19</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>39.57000000000001</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>39.83</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.66</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-28.47</t>
+          <t>-23.20</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.51</t>
+          <t>-104.79</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>208521987.2793697</t>
+          <t>208656413.7982833</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>532289392.0</t>
+          <t>302806648.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>317585660.6</t>
+          <t>315723489.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>263274442.8</t>
+          <t>267936291.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>673739372.28</t>
+          <t>654424013.3</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>54311217</t>
+          <t>47787197</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-39813408.42361735</t>
+          <t>-38884372.1089407</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-35081209.22090816</t>
+          <t>-33774672.37821913</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>532289392</v>
+        <v>302806648</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>42.24</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>45483</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6136.175</t>
+          <t>13085.646</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>11.70</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>42.31</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>41.19</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>39.51000000000001</t>
+          <t>39.57000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>39.76</t>
+          <t>39.78</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.87</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-36.08</t>
+          <t>-28.47</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.19</t>
+          <t>-104.51</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>208521987.2793697</t>
+          <t>208656413.7982833</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>240426749.0</t>
+          <t>532289392.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>234858276.4</t>
+          <t>317585660.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>236240878.5</t>
+          <t>263274442.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>679732391.62</t>
+          <t>673739372.28</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1382602</t>
+          <t>54311217</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-40673808.27865538</t>
+          <t>-39813408.42361735</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-60282226.95257431</t>
+          <t>-35081209.22090816</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>240426749</v>
+        <v>532289392</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>45483</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6635.823</t>
+          <t>6136.175</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-17.42</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.80</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.51000000000001</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>39.76</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>41.14</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>38.33</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>-36.08</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.81</t>
+          <t>-104.19</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>208521987.2793697</t>
+          <t>208656413.7982833</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>267989366.0</t>
+          <t>240426749.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>223432348.8</t>
+          <t>234858276.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>270578244.9</t>
+          <t>236240878.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>693037521.34</t>
+          <t>679732391.62</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-47145896</t>
+          <t>-1382602</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-37108641.24703376</t>
+          <t>-40673808.27865538</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-62859746.71379119</t>
+          <t>-60282226.95257431</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>267989366</v>
+        <v>240426749</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>40.61</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>45483</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5872.775</t>
+          <t>6635.823</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-33.41</t>
+          <t>-17.42</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>77.42</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>7.80</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>39.52</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>39.78</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.14</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>38.16</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-40.75</t>
+          <t>-11.77</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.70</t>
+          <t>-103.81</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>208521987.2793697</t>
+          <t>208656413.7982833</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>235105290.0</t>
+          <t>267989366.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>211553687.2</t>
+          <t>223432348.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>317718579.4</t>
+          <t>270578244.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>694915339.42</t>
+          <t>693037521.34</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-106164892</t>
+          <t>-47145896</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-32426622.07125968</t>
+          <t>-37108641.24703376</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-67250064.3828941</t>
+          <t>-62859746.71379119</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>235105290</v>
+        <v>267989366</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>43.86</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>45483</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7951.184</t>
+          <t>5872.775</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-50.07</t>
+          <t>-33.41</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>48.72</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>28.81</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.52</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.98</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-72.18</t>
+          <t>-40.75</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.32</t>
+          <t>-103.70</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>208521987.2793697</t>
+          <t>208656413.7982833</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>312117506.0</t>
+          <t>235105290.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>220149093.2</t>
+          <t>211553687.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>440884400.6</t>
+          <t>317718579.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>697689583.68</t>
+          <t>694915339.42</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-220735307</t>
+          <t>-106164892</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-26095087.10550797</t>
+          <t>-32426622.07125968</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-67596864.89650917</t>
+          <t>-67250064.3828941</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>312117506</v>
+        <v>235105290</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>42.60</t>
+          <t>43.86</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>45483</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>126477.283</t>
+          <t>68850.257</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-30.86</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,12 +5810,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>126477</t>
+          <t>68850</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5825,57 +5825,57 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>9.80</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>53.48</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>43.41</t>
+          <t>43.68</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,27 +5900,27 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1327917603.891834</t>
+          <t>1333555681.457082</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>6744255965.0</t>
+          <t>3512622548.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>6936487304.4</t>
+          <t>6095469315.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>10032139013.4</t>
+          <t>9544851503.2</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>3632131847.42</t>
+          <t>3663541757.9</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -5930,16 +5930,16 @@
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>993789215.4382774</t>
+          <t>856099906.5838505</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>468208784.7071676</t>
+          <t>98808707.88450241</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>6744255965</v>
+        <v>3512622548</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>415575</t>
+          <t>405265</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>89940.447</t>
+          <t>126477.283</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-15.62</t>
+          <t>-30.86</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -6210,12 +6210,12 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>26.69</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>126477</t>
+          <t>68850</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>73.89</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>47.74</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>43.12</t>
+          <t>43.41</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>42.21</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>21.20</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1327917603.891834</t>
+          <t>1333555681.457082</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>4850127005.0</t>
+          <t>6744255965.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>8366597065.8</t>
+          <t>6936487304.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>9915210649.5</t>
+          <t>10032139013.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>3525171118.12</t>
+          <t>3632131847.42</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-1548613583</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>1089349293.753025</t>
+          <t>993789215.4382774</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>632955000.321434</t>
+          <t>468208784.7071676</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>4850127005</v>
+        <v>6744255965</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>30.79</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>415575</t>
+          <t>405265</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>87722.137</t>
+          <t>89940.447</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-7.24</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>20.97</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.69</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>126477</t>
+          <t>68850</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>73.89</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>15.21</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>55.34</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>47.74</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>43.12</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.97</t>
+          <t>42.21</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>21.20</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1327917603.891834</t>
+          <t>1333555681.457082</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>4661687858.0</t>
+          <t>4850127005.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>9917900867.8</t>
+          <t>8366597065.8</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>9646311981.3</t>
+          <t>9915210649.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>3483979320.62</t>
+          <t>3525171118.12</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>271588886</t>
+          <t>-1548613583</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>1172330074.37695</t>
+          <t>1089349293.753025</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>1048643589.758906</t>
+          <t>632955000.321434</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>4661687858</v>
+        <v>4850127005</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>30.79</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>415575</t>
+          <t>405265</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>187213.322</t>
+          <t>87722.137</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>22.40</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>126477</t>
+          <t>68850</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>95.02</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>90.43</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>17.38</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>55.96</t>
+          <t>55.34</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>46.69</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>41.97</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>45.57</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-14.32</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1327917603.891834</t>
+          <t>1333555681.457082</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>10708653199.0</t>
+          <t>4661687858.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>11555043688.4</t>
+          <t>9917900867.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>9440522375.4</t>
+          <t>9646311981.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>3413291777.02</t>
+          <t>3483979320.62</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2114521313</t>
+          <t>271588886</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>1194818526.125685</t>
+          <t>1172330074.37695</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>1625222783.642477</t>
+          <t>1048643589.758906</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>10708653199</v>
+        <v>4661687858</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>35.08</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>415575</t>
+          <t>405265</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>141242.686</t>
+          <t>187213.322</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>53.41</t>
+          <t>22.40</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -7518,12 +7518,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>126477</t>
+          <t>68850</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>76.27</t>
+          <t>95.02</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>92.09</t>
+          <t>90.43</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>55.96</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>45.98</t>
+          <t>46.69</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.49</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>45.57</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-24.09</t>
+          <t>-14.32</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1327917603.891834</t>
+          <t>1333555681.457082</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>7717712495.0</t>
+          <t>10708653199.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>12994233691.4</t>
+          <t>11555043688.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>8470087592.9</t>
+          <t>9440522375.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>3233128694.92</t>
+          <t>3413291777.02</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>2114521313</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>1116563206.577178</t>
+          <t>1194818526.125685</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>1742974531.810349</t>
+          <t>1625222783.642477</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>7717712495</v>
+        <v>10708653199</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>28.40</t>
+          <t>35.08</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>415575</t>
+          <t>405265</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="CG17" t="inlineStr">
+        <is>
           <t>56.6</t>
-        </is>
-      </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>56.8</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="CG17" t="inlineStr">
-        <is>
-          <t>53.8</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>237895.796</t>
+          <t>141242.686</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>67.79</t>
+          <t>53.41</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>70.60</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>126477</t>
+          <t>68850</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.27</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.09</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>45.39</t>
+          <t>45.98</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>41.49</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>77.41</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-34.55</t>
+          <t>-24.09</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,27 +8080,27 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1327917603.891834</t>
+          <t>1333555681.457082</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>13894804772.0</t>
+          <t>7717712495.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>13127790722.4</t>
+          <t>12994233691.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>7823899971.0</t>
+          <t>8470087592.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>3109382048.22</t>
+          <t>3233128694.92</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -8110,16 +8110,16 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1002670238.352965</t>
+          <t>1116563206.577178</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>2169400157.056937</t>
+          <t>1742974531.810349</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>13894804772</v>
+        <v>7717712495</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>28.40</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>415575</t>
+          <t>405265</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>216309.874</t>
+          <t>237895.796</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-7.82</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>67.79</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>26.49</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>64.20</t>
+          <t>70.60</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>126477</t>
+          <t>68850</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,57 +8446,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>20.30</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>44.62</t>
+          <t>45.39</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.22</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>91.69</t>
+          <t>77.41</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-47.22</t>
+          <t>-34.55</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,27 +8516,27 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1327917603.891834</t>
+          <t>1333555681.457082</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>12606646015.0</t>
+          <t>13894804772.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>11463824233.2</t>
+          <t>13127790722.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>6558502593.2</t>
+          <t>7823899971.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>2879764455.78</t>
+          <t>3109382048.22</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -8546,16 +8546,16 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>790537525.8613333</t>
+          <t>1002670238.352965</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>2039269729.264316</t>
+          <t>2169400157.056937</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>12606646015</v>
+        <v>13894804772</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>415575</t>
+          <t>405265</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>235389.305</t>
+          <t>216309.874</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>73.90</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.57</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>64.20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>126477</t>
+          <t>68850</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8882,57 +8882,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.62</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>41.17</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>104.45</t>
+          <t>91.69</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-59.32</t>
+          <t>-47.22</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,27 +8952,27 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1327917603.891834</t>
+          <t>1333555681.457082</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>12847401961.0</t>
+          <t>12606646015.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>9374723094.8</t>
+          <t>11463824233.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>5390815186.5</t>
+          <t>6558502593.2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>2722439698.1</t>
+          <t>2879764455.78</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
@@ -8982,16 +8982,16 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>563495307.060791</t>
+          <t>790537525.8613333</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>1918555066.051131</t>
+          <t>2039269729.264316</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>12847401961</v>
+        <v>12606646015</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>32.70</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>415575</t>
+          <t>405265</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>336947.705</t>
+          <t>235389.305</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-8.81</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>70.38</t>
+          <t>73.90</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>22.74</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>126477</t>
+          <t>68850</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9318,57 +9318,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>43.19</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.17</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>105.78</t>
+          <t>104.45</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-69.94</t>
+          <t>-59.32</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,27 +9388,27 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1327917603.891834</t>
+          <t>1333555681.457082</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>17904603214.0</t>
+          <t>12847401961.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>7326001062.4</t>
+          <t>9374723094.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>4299803431.4</t>
+          <t>5390815186.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>2525457286.94</t>
+          <t>2722439698.1</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
@@ -9418,16 +9418,16 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>317120805.4261836</t>
+          <t>563495307.060791</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>1651790443.45904</t>
+          <t>1918555066.051131</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>17904603214</v>
+        <v>12847401961</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>28.40</t>
+          <t>32.70</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>415575</t>
+          <t>405265</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>174611.856</t>
+          <t>336947.705</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>51.82</t>
+          <t>70.38</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -9698,12 +9698,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,33 +9713,33 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>51.82</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>126477</t>
+          <t>68850</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9754,57 +9754,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>44.51000000000001</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>43.19</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>105.78</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-77.89</t>
+          <t>-69.94</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1327917603.891834</t>
+          <t>1333555681.457082</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>8385497650.0</t>
+          <t>17904603214.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>3945941494.4</t>
+          <t>7326001062.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>2599113437.9</t>
+          <t>4299803431.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>2229827006.08</t>
+          <t>2525457286.94</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>1346828056</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>74453598.5111188</t>
+          <t>317120805.4261836</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>669862618.2396603</t>
+          <t>1651790443.45904</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>8385497650</v>
+        <v>17904603214</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>28.40</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>415575</t>
+          <t>405265</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>123131.763</t>
+          <t>174611.856</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,74 +10054,74 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>49.8</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>51.82</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>13.55</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>33.84</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>51.1</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
       <c r="T23" t="inlineStr">
         <is>
           <t>41.45</t>
@@ -10134,12 +10134,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>51.82</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>126477</t>
+          <t>68850</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10190,57 +10190,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>44.51000000000001</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>42.04</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>39.67</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-82.23</t>
+          <t>-77.89</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1327917603.891834</t>
+          <t>1333555681.457082</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>5574972326.0</t>
+          <t>8385497650.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>2520009219.6</t>
+          <t>3945941494.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1882831584.8</t>
+          <t>2599113437.9</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>2124977087.88</t>
+          <t>2229827006.08</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>637177634</t>
+          <t>1346828056</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-33802586.89407057</t>
+          <t>74453598.5111188</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>263089084.8462725</t>
+          <t>669862618.2396603</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>5574972326</v>
+        <v>8385497650</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>415575</t>
+          <t>405265</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/酚醛樹脂.xlsx
+++ b/Result/checksun_type/酚醛樹脂.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,21 +1057,17 @@
           <t>39.02</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AM2" t="n">
+        <v>39.53</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>39.53</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>40.2</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>39.53</t>
-        </is>
-      </c>
       <c r="AP2" t="inlineStr">
         <is>
           <t>-19.58</t>
@@ -1112,20 +1108,16 @@
           <t>201657416.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>252360977.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>252360977.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>282417854.9</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>423553251.3</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>423553251.3</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-36974729.3629033</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>201657416</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>201657416.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>39.04000000000001</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>39.71</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>40.26</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>39.71</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>40.26</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>195613562.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>255801795.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>255801795.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>285762642.3</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>457544220.78</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>457544220.78</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-35925485.46414912</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>195613562</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>195613562.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>39.16</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>39.91</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>40.4</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>39.91</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>40.4</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>188357162.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>277240412.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>277240412.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>297413036.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>528814161.92</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>528814161.92</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-32495956.77078068</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>188357162</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>188357162.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>39.25</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>39.94</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>40.53</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>39.94</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>40.53</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>355837208.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>346026858.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>346026858.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>290442567.6</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>558638708.96</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>558638708.96</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-25658588.75272644</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>355837208</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>355837208.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>39.4</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>39.93</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>40.66</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>39.93</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>40.66</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>320339540.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>322944767.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>322944767</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>273188557.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>613979125.7</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>613979125.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-32918832.62862295</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>320339540</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>320339540.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>39.4</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>39.85</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>40.74</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>39.85</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>40.74</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>218861506.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>312474732.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>312474732.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>262014209.7</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>631667121.94</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>631667121.9400001</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-38311615.42888141</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>218861506</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>218861506.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>39.55</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>39.83</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>40.77</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>39.83</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>40.77</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>302806648.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>315723489.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>315723489</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>267936291.1</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>654424013.3</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>654424013.3</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-33774672.37821913</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>302806648</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>302806648.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>39.57000000000001</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>39.78</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>40.87</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>40.87</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>532289392.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>317585660.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>317585660.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>263274442.8</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>673739372.28</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>673739372.28</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-35081209.22090816</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>532289392</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>532289392.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>39.51000000000001</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>39.76</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>39.76</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>41</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>240426749.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>234858276.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>234858276.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>236240878.5</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>679732391.62</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>679732391.62</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-60282226.95257431</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>240426749</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>240426749.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>39.5</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>39.78</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>41.14</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>41.14</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>267989366.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>223432348.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>223432348.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>270578244.9</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>693037521.34</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>693037521.34</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-62859746.71379119</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>267989366</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>267989366.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>39.52</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>39.72</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>41.21</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>39.72</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>41.21</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>235105290.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>211553687.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>211553687.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>317718579.4</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>694915339.42</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>694915339.42</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-67250064.3828941</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>235105290</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>235105290.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>53.48</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>48.7</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>43.68</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>43.68</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>3512622548.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>6095469315.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>6095469315</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>9544851503.2</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>3663541757.9</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>3663541757.9</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>98808707.88450241</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>3512622548</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>3512622548.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>54.02</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>48.25</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>43.41</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>43.41</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>6744255965.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>6936487304.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>6936487304.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>10032139013.4</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>3632131847.42</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>3632131847.42</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>468208784.7071676</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>6744255965</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>6744255965.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>55.0</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>47.74</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>43.12</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>47.74</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>43.12</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>4850127005.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>8366597065.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>8366597065.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>9915210649.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>3525171118.12</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>3525171118.12</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>632955000.321434</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>4850127005</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>4850127005.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>55.34</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>47.15</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>42.8</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>42.8</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>4661687858.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>9917900867.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>9917900867.799999</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>9646311981.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>3483979320.62</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>3483979320.62</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>1048643589.758906</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>4661687858</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>4661687858.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>55.96</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>46.69</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>42.52</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>46.69</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>42.52</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>10708653199.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>11555043688.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>11555043688.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>9440522375.4</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>3413291777.02</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>3413291777.02</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>1625222783.642477</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>10708653199</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>10708653199.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>55.4</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>45.98</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>42.16</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>42.16</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>7717712495.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>12994233691.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>12994233691.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>8470087592.9</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>3233128694.92</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>3233128694.92</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>1742974531.810349</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>7717712495</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>7717712495.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>54.6</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>45.39</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>41.86</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>41.86</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>13894804772.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>13127790722.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>13127790722.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>7823899971.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>3109382048.22</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>3109382048.22</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>2169400157.056937</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>13894804772</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>13894804772.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>52.2</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>44.62</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>41.5</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>12606646015.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>11463824233.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>11463824233.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>6558502593.2</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>2879764455.78</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>2879764455.78</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>2039269729.264316</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>12606646015</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>12606646015.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>49.55</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>43.9</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>41.17</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>41.17</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>12847401961.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>9374723094.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>9374723094.799999</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>5390815186.5</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>2722439698.1</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>2722439698.1</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>1918555066.051131</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>12847401961</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>12847401961.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>46.94</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>43.19</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>40.9</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>43.19</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>40.9</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>17904603214.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>7326001062.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>7326001062.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>4299803431.4</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>2525457286.94</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>2525457286.94</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>1651790443.45904</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>17904603214</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>17904603214.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>44.51000000000001</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>42.52</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>40.69</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>40.69</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>8385497650.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>3945941494.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>3945941494.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>2599113437.9</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>2229827006.08</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>2229827006.08</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>669862618.2396603</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>8385497650</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>8385497650.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/酚醛樹脂.xlsx
+++ b/Result/checksun_type/酚醛樹脂.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5128.692</t>
+          <t>4713.942</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-10.64</t>
+          <t>-17.78</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>71.05</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1049,33 +1049,33 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>38.91</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>39.53</v>
+        <v>39.48</v>
       </c>
       <c r="AN2" t="n">
-        <v>40.2</v>
+        <v>40.15</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-19.58</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.73</t>
+          <t>-106.75</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>208656413.7982833</t>
+          <t>208756120.875</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>201657416.0</t>
+          <t>185634245.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>252360977.6</v>
+        <v>225419918.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>282417854.9</t>
+          <t>274182342.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>423553251.3</v>
+        <v>413674654.36</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-30056877</t>
+          <t>-48762424</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-35760325.94395395</t>
+          <t>-36102824.98072391</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-36974729.3629033</t>
+          <t>-37986569.68295866</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>201657416.0</t>
+          <t>185634245.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>42.78</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>46362</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5013.788</t>
+          <t>5128.692</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-10.48</t>
+          <t>-10.64</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,63 +1444,63 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>39.04000000000001</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>39.71</v>
+        <v>39.53</v>
       </c>
       <c r="AN3" t="n">
-        <v>40.26</v>
+        <v>40.2</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-27.08</t>
+          <t>-19.58</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.40</t>
+          <t>-106.73</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>208656413.7982833</t>
+          <t>208756120.875</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>195613562.0</t>
+          <t>201657416.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>255801795.6</v>
+        <v>252360977.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>285762642.3</t>
+          <t>282417854.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>457544220.78</v>
+        <v>423553251.3</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-29960846</t>
+          <t>-30056877</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-35539525.3223268</t>
+          <t>-35760325.94395395</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-35925485.46414912</t>
+          <t>-36974729.3629033</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>195613562.0</t>
+          <t>201657416.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>46362</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4826.572</t>
+          <t>5013.788</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-10.48</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>39.16</t>
+          <t>39.04000000000001</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>39.91</v>
+        <v>39.71</v>
       </c>
       <c r="AN4" t="n">
-        <v>40.4</v>
+        <v>40.26</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-27.86</t>
+          <t>-27.08</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-105.97</t>
+          <t>-106.40</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>208656413.7982833</t>
+          <t>208756120.875</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>188357162.0</t>
+          <t>195613562.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>277240412.8</v>
+        <v>255801795.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>297413036.7</t>
+          <t>285762642.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>528814161.92</v>
+        <v>457544220.78</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-20172623</t>
+          <t>-29960846</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-35469350.75108638</t>
+          <t>-35539525.3223268</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-32495956.77078068</t>
+          <t>-35925485.46414912</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>188357162.0</t>
+          <t>195613562.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>46362</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9258.407</t>
+          <t>4826.572</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.16</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>39.94</v>
+        <v>39.91</v>
       </c>
       <c r="AN5" t="n">
-        <v>40.53</v>
+        <v>40.4</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-32.78</t>
+          <t>-27.86</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.55</t>
+          <t>-105.97</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>208656413.7982833</t>
+          <t>208756120.875</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>355837208.0</t>
+          <t>188357162.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>346026858.8</v>
+        <v>277240412.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>290442567.6</t>
+          <t>297413036.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>558638708.96</v>
+        <v>528814161.92</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>55584291</t>
+          <t>-20172623</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-36009967.83841468</t>
+          <t>-35469350.75108638</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-25658588.75272644</t>
+          <t>-32495956.77078068</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>355837208.0</t>
+          <t>188357162.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>46362</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7921.053</t>
+          <t>9258.407</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>19.14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>39.93</v>
+        <v>39.94</v>
       </c>
       <c r="AN6" t="n">
-        <v>40.66</v>
+        <v>40.53</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>38.97</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-32.78</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.10</t>
+          <t>-105.55</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>208656413.7982833</t>
+          <t>208756120.875</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>320339540.0</t>
+          <t>355837208.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>322944767</v>
+        <v>346026858.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>273188557.9</t>
+          <t>290442567.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>613979125.7</v>
+        <v>558638708.96</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>49756209</t>
+          <t>55584291</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-37892036.76308528</t>
+          <t>-36009967.83841468</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-32918832.62862295</t>
+          <t>-25658588.75272644</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>320339540.0</t>
+          <t>355837208.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>46362</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5612.57</t>
+          <t>7921.053</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>18.21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,42 +3164,42 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>51.71</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3208,24 +3208,24 @@
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>39.85</v>
+        <v>39.93</v>
       </c>
       <c r="AN7" t="n">
-        <v>40.74</v>
+        <v>40.66</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>38.97</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-26.63</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.13</t>
+          <t>-105.10</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>208656413.7982833</t>
+          <t>208756120.875</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>218861506.0</t>
+          <t>320339540.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>312474732.2</v>
+        <v>322944767</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>262014209.7</t>
+          <t>273188557.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>631667121.9400001</v>
+        <v>613979125.7</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>50460522</t>
+          <t>49756209</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-38796255.69662388</t>
+          <t>-37892036.76308528</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-38311615.42888141</t>
+          <t>-32918832.62862295</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>218861506.0</t>
+          <t>320339540.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>46362</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7632.447</t>
+          <t>5612.57</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>39.83</v>
+        <v>39.85</v>
       </c>
       <c r="AN8" t="n">
-        <v>40.77</v>
+        <v>40.74</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>38.66</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-23.20</t>
+          <t>-26.63</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.79</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>208656413.7982833</t>
+          <t>208756120.875</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>302806648.0</t>
+          <t>218861506.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>315723489</v>
+        <v>312474732.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>267936291.1</t>
+          <t>262014209.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>654424013.3</v>
+        <v>631667121.9400001</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>47787197</t>
+          <t>50460522</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-38884372.1089407</t>
+          <t>-38796255.69662388</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-33774672.37821913</t>
+          <t>-38311615.42888141</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>302806648.0</t>
+          <t>218861506.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>46362</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>38.5</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>39.1</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>40.45</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>38.85</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>39.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13085.646</t>
+          <t>7632.447</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.70</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,63 +4024,63 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>42.31</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>41.19</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>39.57000000000001</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>39.78</v>
+        <v>39.83</v>
       </c>
       <c r="AN9" t="n">
-        <v>40.87</v>
+        <v>40.77</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.66</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-28.47</t>
+          <t>-23.20</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.51</t>
+          <t>-104.79</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>208656413.7982833</t>
+          <t>208756120.875</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>532289392.0</t>
+          <t>302806648.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>317585660.6</v>
+        <v>315723489</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>263274442.8</t>
+          <t>267936291.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>673739372.28</v>
+        <v>654424013.3</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>54311217</t>
+          <t>47787197</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-39813408.42361735</t>
+          <t>-38884372.1089407</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-35081209.22090816</t>
+          <t>-33774672.37821913</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>532289392.0</t>
+          <t>302806648.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>42.24</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>46362</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6136.175</t>
+          <t>13085.646</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>11.70</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>42.31</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>41.19</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>39.51000000000001</t>
+          <t>39.57000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>39.76</v>
+        <v>39.78</v>
       </c>
       <c r="AN10" t="n">
-        <v>41</v>
+        <v>40.87</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-36.08</t>
+          <t>-28.47</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.19</t>
+          <t>-104.51</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>208656413.7982833</t>
+          <t>208756120.875</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>240426749.0</t>
+          <t>532289392.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>234858276.4</v>
+        <v>317585660.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>236240878.5</t>
+          <t>263274442.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>679732391.62</v>
+        <v>673739372.28</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1382602</t>
+          <t>54311217</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-40673808.27865538</t>
+          <t>-39813408.42361735</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-60282226.95257431</t>
+          <t>-35081209.22090816</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>240426749.0</t>
+          <t>532289392.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>46362</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6635.823</t>
+          <t>6136.175</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,102 +4778,102 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-1.67</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-0.59</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>39.25</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>40.85</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-0.76</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>5.49</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
           <t>-2.82</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-2.18</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-17.42</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>39.25</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>27.6</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>40.85</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>4.04</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>5.94</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>-0.73</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>7.80</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.51000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>39.78</v>
+        <v>39.76</v>
       </c>
       <c r="AN11" t="n">
-        <v>41.14</v>
+        <v>41</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>38.33</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>-36.08</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.81</t>
+          <t>-104.19</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>208656413.7982833</t>
+          <t>208756120.875</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>267989366.0</t>
+          <t>240426749.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>223432348.8</v>
+        <v>234858276.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>270578244.9</t>
+          <t>236240878.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>693037521.34</v>
+        <v>679732391.62</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-47145896</t>
+          <t>-1382602</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-37108641.24703376</t>
+          <t>-40673808.27865538</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-62859746.71379119</t>
+          <t>-60282226.95257431</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>267989366.0</t>
+          <t>240426749.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>40.61</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>46362</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5872.775</t>
+          <t>6635.823</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-33.41</t>
+          <t>-17.42</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>77.42</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>7.80</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>39.52</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>39.72</v>
+        <v>39.78</v>
       </c>
       <c r="AN12" t="n">
-        <v>41.21</v>
+        <v>41.14</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>38.16</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-40.75</t>
+          <t>-11.77</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.70</t>
+          <t>-103.81</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>208656413.7982833</t>
+          <t>208756120.875</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>235105290.0</t>
+          <t>267989366.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>211553687.2</v>
+        <v>223432348.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>317718579.4</t>
+          <t>270578244.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>694915339.42</v>
+        <v>693037521.34</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-106164892</t>
+          <t>-47145896</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-32426622.07125968</t>
+          <t>-37108641.24703376</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-67250064.3828941</t>
+          <t>-62859746.71379119</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>235105290.0</t>
+          <t>267989366.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>43.86</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>46362</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>68850.257</t>
+          <t>153271.208</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,112 +5628,112 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-34.41</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
           <t>51.1</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>-36.14</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>41.45</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>45.49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,110 +5744,110 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>726</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>68850</t>
+          <t>153271</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>82.26</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>9.80</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>53.48</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>48.7</v>
+        <v>49.42</v>
       </c>
       <c r="AN13" t="n">
-        <v>43.68</v>
+        <v>44.05</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>42.71</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/11/11</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1333555681.457082</t>
+          <t>1349701199.475</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>3512622548.0</t>
+          <t>8423612196.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>6095469315</v>
+        <v>5638461114.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>9544851503.2</t>
+          <t>8596752401.4</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>3663541757.9</v>
+        <v>3818531527.48</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5856,22 +5856,22 @@
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>856099906.5838505</t>
+          <t>756097253.2650311</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>98808707.88450241</t>
+          <t>206082660.0115242</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>3512622548.0</t>
+          <t>8423612196.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>34.13</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>405265</t>
+          <t>445712</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6033,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>126477.283</t>
+          <t>68850.257</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-30.86</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6088,82 +6088,82 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>2025-11-11 00:00:00</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>2025-11-26 00:00:00</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
       <c r="Q14" t="inlineStr">
         <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
         <is>
           <t>51.1</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>41.45</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>726</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>68850</t>
+          <t>153271</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,53 +6189,53 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>9.80</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>53.48</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>48.25</v>
+        <v>48.7</v>
       </c>
       <c r="AN14" t="n">
-        <v>43.41</v>
+        <v>43.68</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6245,39 +6245,39 @@
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2025/11/11</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1333555681.457082</t>
+          <t>1349701199.475</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>6744255965.0</t>
+          <t>3512622548.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>6936487304.4</v>
+        <v>6095469315</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>10032139013.4</t>
+          <t>9544851503.2</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>3632131847.42</v>
+        <v>3663541757.9</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6286,17 +6286,17 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>993789215.4382774</t>
+          <t>856099906.5838505</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>468208784.7071676</t>
+          <t>98808707.88450241</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>6744255965.0</t>
+          <t>3512622548.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>405265</t>
+          <t>445712</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>89940.447</t>
+          <t>126477.283</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-15.62</t>
+          <t>-30.86</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6518,82 +6518,82 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
           <t>2025-11-11 00:00:00</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>2025-11-26 00:00:00</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t>51.1</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>41.45</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>26.69</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,129 +6604,129 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>726</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>68850</t>
+          <t>153271</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>73.89</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>47.74</v>
+        <v>48.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>43.12</v>
+        <v>43.41</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>42.21</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>21.20</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2025/11/11</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1333555681.457082</t>
+          <t>1349701199.475</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>4850127005.0</t>
+          <t>6744255965.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>8366597065.8</v>
+        <v>6936487304.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>9915210649.5</t>
+          <t>10032139013.4</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>3525171118.12</v>
+        <v>3632131847.42</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-1548613583</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>1089349293.753025</t>
+          <t>993789215.4382774</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>632955000.321434</t>
+          <t>468208784.7071676</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>4850127005.0</t>
+          <t>6744255965.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>30.79</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>405265</t>
+          <t>445712</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>87722.137</t>
+          <t>89940.447</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6948,82 +6948,82 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>2025-11-11 00:00:00</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>2025-11-26 00:00:00</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
         <is>
           <t>51.1</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>41.45</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>20.97</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.69</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,129 +7034,129 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>726</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>68850</t>
+          <t>153271</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>73.89</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>15.21</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>55.34</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>47.15</v>
+        <v>47.74</v>
       </c>
       <c r="AN16" t="n">
-        <v>42.8</v>
+        <v>43.12</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.97</t>
+          <t>42.21</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>21.20</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2025/11/11</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1333555681.457082</t>
+          <t>1349701199.475</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>4661687858.0</t>
+          <t>4850127005.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>9917900867.799999</v>
+        <v>8366597065.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>9646311981.3</t>
+          <t>9915210649.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>3483979320.62</v>
+        <v>3525171118.12</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>271588886</t>
+          <t>-1548613583</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>1172330074.37695</t>
+          <t>1089349293.753025</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>1048643589.758906</t>
+          <t>632955000.321434</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>4661687858.0</t>
+          <t>4850127005.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>30.79</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>405265</t>
+          <t>445712</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>187213.322</t>
+          <t>87722.137</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22.40</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7378,82 +7378,82 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
           <t>2025-11-11 00:00:00</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>2025-11-26 00:00:00</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>51.1</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>41.45</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,129 +7464,129 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>726</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>68850</t>
+          <t>153271</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>95.02</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>90.43</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>17.38</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>55.96</t>
+          <t>55.34</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>46.69</v>
+        <v>47.15</v>
       </c>
       <c r="AN17" t="n">
-        <v>42.52</v>
+        <v>42.8</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>41.97</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>45.57</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-14.32</t>
+          <t>-8.31</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2025/11/11</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1333555681.457082</t>
+          <t>1349701199.475</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>10708653199.0</t>
+          <t>4661687858.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>11555043688.4</v>
+        <v>9917900867.799999</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>9440522375.4</t>
+          <t>9646311981.3</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>3413291777.02</v>
+        <v>3483979320.62</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>2114521313</t>
+          <t>271588886</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>1194818526.125685</t>
+          <t>1172330074.37695</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>1625222783.642477</t>
+          <t>1048643589.758906</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>10708653199.0</t>
+          <t>4661687858.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>35.08</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>405265</t>
+          <t>445712</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>141242.686</t>
+          <t>187213.322</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>53.41</t>
+          <t>22.40</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7808,82 +7808,82 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>2025-11-11 00:00:00</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>2025-11-26 00:00:00</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
       <c r="Q18" t="inlineStr">
         <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
         <is>
           <t>51.1</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>41.45</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,129 +7894,129 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>726</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>68850</t>
+          <t>153271</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>76.27</t>
+          <t>95.02</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>92.09</t>
+          <t>90.43</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>55.96</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>45.98</v>
+        <v>46.69</v>
       </c>
       <c r="AN18" t="n">
-        <v>42.16</v>
+        <v>42.52</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.49</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>45.57</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-24.09</t>
+          <t>-14.84</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2025/11/11</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1333555681.457082</t>
+          <t>1349701199.475</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>7717712495.0</t>
+          <t>10708653199.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>12994233691.4</v>
+        <v>11555043688.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>8470087592.9</t>
+          <t>9440522375.4</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>3233128694.92</v>
+        <v>3413291777.02</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>2114521313</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1116563206.577178</t>
+          <t>1194818526.125685</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>1742974531.810349</t>
+          <t>1625222783.642477</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>7717712495.0</t>
+          <t>10708653199.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>28.40</t>
+          <t>35.08</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>405265</t>
+          <t>445712</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="CG18" t="inlineStr">
+        <is>
           <t>56.6</t>
-        </is>
-      </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>56.8</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="CG18" t="inlineStr">
-        <is>
-          <t>53.8</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>237895.796</t>
+          <t>141242.686</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>67.79</t>
+          <t>53.41</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8238,82 +8238,82 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
           <t>2025-11-11 00:00:00</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>2025-11-26 00:00:00</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
       <c r="Q19" t="inlineStr">
         <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
         <is>
           <t>51.1</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>41.45</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>70.60</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,110 +8324,110 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>726</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>68850</t>
+          <t>153271</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.27</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.09</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>45.39</v>
+        <v>45.98</v>
       </c>
       <c r="AN19" t="n">
-        <v>41.86</v>
+        <v>42.16</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>41.49</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>77.41</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-34.55</t>
+          <t>-24.54</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2025/11/11</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1333555681.457082</t>
+          <t>1349701199.475</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>13894804772.0</t>
+          <t>7717712495.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>13127790722.4</v>
+        <v>12994233691.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>7823899971.0</t>
+          <t>8470087592.9</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>3109382048.22</v>
+        <v>3233128694.92</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8436,17 +8436,17 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1002670238.352965</t>
+          <t>1116563206.577178</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>2169400157.056937</t>
+          <t>1742974531.810349</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>13894804772.0</t>
+          <t>7717712495.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>28.40</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>405265</t>
+          <t>445712</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>216309.874</t>
+          <t>237895.796</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>67.79</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8668,82 +8668,82 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
           <t>2025-11-11 00:00:00</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>2025-11-26 00:00:00</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
         <is>
           <t>51.1</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>41.45</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>26.49</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>10.57</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>64.20</t>
+          <t>70.60</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>726</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>68850</t>
+          <t>153271</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,90 +8774,90 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>20.30</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>44.62</v>
+        <v>45.39</v>
       </c>
       <c r="AN20" t="n">
-        <v>41.5</v>
+        <v>41.86</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.22</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>91.69</t>
+          <t>77.41</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-47.22</t>
+          <t>-34.95</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2025/11/11</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1333555681.457082</t>
+          <t>1349701199.475</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>12606646015.0</t>
+          <t>13894804772.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>11463824233.2</v>
+        <v>13127790722.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>6558502593.2</t>
+          <t>7823899971.0</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>2879764455.78</v>
+        <v>3109382048.22</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8866,17 +8866,17 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>790537525.8613333</t>
+          <t>1002670238.352965</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>2039269729.264316</t>
+          <t>2169400157.056937</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>12606646015.0</t>
+          <t>13894804772.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>405265</t>
+          <t>445712</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>235389.305</t>
+          <t>216309.874</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-8.81</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>73.90</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9098,82 +9098,82 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>2025-11-11 00:00:00</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>2025-11-26 00:00:00</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
       <c r="Q21" t="inlineStr">
         <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
         <is>
           <t>51.1</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>41.45</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>64.20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>726</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>68850</t>
+          <t>153271</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,90 +9204,90 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>43.9</v>
+        <v>44.62</v>
       </c>
       <c r="AN21" t="n">
-        <v>41.17</v>
+        <v>41.5</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>104.45</t>
+          <t>91.69</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-59.32</t>
+          <t>-47.54</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2025/11/11</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1333555681.457082</t>
+          <t>1349701199.475</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>12847401961.0</t>
+          <t>12606646015.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>9374723094.799999</v>
+        <v>11463824233.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>5390815186.5</t>
+          <t>6558502593.2</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>2722439698.1</v>
+        <v>2879764455.78</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9296,17 +9296,17 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>563495307.060791</t>
+          <t>790537525.8613333</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>1918555066.051131</t>
+          <t>2039269729.264316</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>12847401961.0</t>
+          <t>12606646015.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>32.70</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>405265</t>
+          <t>445712</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>336947.705</t>
+          <t>235389.305</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>70.38</t>
+          <t>73.90</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9528,82 +9528,82 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
           <t>2025-11-11 00:00:00</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>2025-11-26 00:00:00</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
       <c r="Q22" t="inlineStr">
         <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
         <is>
           <t>51.1</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>41.45</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>22.74</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>726</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>68850</t>
+          <t>153271</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,90 +9634,90 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>43.19</v>
+        <v>43.9</v>
       </c>
       <c r="AN22" t="n">
-        <v>40.9</v>
+        <v>41.17</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>105.78</t>
+          <t>104.45</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-69.94</t>
+          <t>-59.56</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2025/11/11</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1333555681.457082</t>
+          <t>1349701199.475</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>17904603214.0</t>
+          <t>12847401961.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>7326001062.4</v>
+        <v>9374723094.799999</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>4299803431.4</t>
+          <t>5390815186.5</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>2525457286.94</v>
+        <v>2722439698.1</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9726,17 +9726,17 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>317120805.4261836</t>
+          <t>563495307.060791</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>1651790443.45904</t>
+          <t>1918555066.051131</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>17904603214.0</t>
+          <t>12847401961.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>28.40</t>
+          <t>32.70</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>405265</t>
+          <t>445712</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>174611.856</t>
+          <t>336947.705</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>51.82</t>
+          <t>70.38</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9958,98 +9958,98 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
           <t>2025-11-11 00:00:00</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>2025-11-26 00:00:00</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
       <c r="Q23" t="inlineStr">
         <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
         <is>
           <t>51.1</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>41.45</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>51.82</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>726</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>68850</t>
+          <t>153271</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,109 +10064,109 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>44.51000000000001</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>42.52</v>
+        <v>43.19</v>
       </c>
       <c r="AN23" t="n">
-        <v>40.69</v>
+        <v>40.9</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>105.78</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-77.89</t>
+          <t>-70.12</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2025/11/11</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1333555681.457082</t>
+          <t>1349701199.475</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>8385497650.0</t>
+          <t>17904603214.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>3945941494.4</v>
+        <v>7326001062.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>2599113437.9</t>
+          <t>4299803431.4</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>2229827006.08</v>
+        <v>2525457286.94</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>1346828056</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>74453598.5111188</t>
+          <t>317120805.4261836</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>669862618.2396603</t>
+          <t>1651790443.45904</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>8385497650.0</t>
+          <t>17904603214.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>28.40</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.19</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>405265</t>
+          <t>445712</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/酚醛樹脂.xlsx
+++ b/Result/checksun_type/酚醛樹脂.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4713.942</t>
+          <t>8360.012</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-17.78</t>
+          <t>-21.99</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
           <t>71.05</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>48.25</t>
-        </is>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>38.91</t>
+          <t>39.32000000000001</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>39.48</v>
+        <v>39.45</v>
       </c>
       <c r="AN2" t="n">
-        <v>40.15</v>
+        <v>40.13</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>39.84</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>29.60</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,53 +1090,53 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.75</t>
+          <t>-106.28</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/11/20</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>208756120.875</t>
+          <t>209175344.6319543</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>185634245.0</t>
+          <t>335087983.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>225419918.6</v>
+        <v>221270073.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>274182342.8</t>
+          <t>283648466.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>413674654.36</v>
+        <v>409053915.06</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-48762424</t>
+          <t>-62378392</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-36102824.98072391</t>
+          <t>-34631030.87829307</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-37986569.68295866</t>
+          <t>-26536163.31492347</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>185634245.0</t>
+          <t>335087983.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>42.78</t>
+          <t>45.31</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>26.66</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>46362</t>
+          <t>47183</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5128.692</t>
+          <t>4713.942</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-10.64</t>
+          <t>-17.78</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,32 +1444,32 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>71.05</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1479,33 +1479,33 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>38.91</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>39.53</v>
+        <v>39.48</v>
       </c>
       <c r="AN3" t="n">
-        <v>40.2</v>
+        <v>40.15</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-19.58</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1520,53 +1520,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.73</t>
+          <t>-106.75</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/11/20</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>208756120.875</t>
+          <t>209175344.6319543</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>201657416.0</t>
+          <t>185634245.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>252360977.6</v>
+        <v>225419918.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>282417854.9</t>
+          <t>274182342.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>423553251.3</v>
+        <v>413674654.36</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-30056877</t>
+          <t>-48762424</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-35760325.94395395</t>
+          <t>-36102824.98072391</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-36974729.3629033</t>
+          <t>-37986569.68295866</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>201657416.0</t>
+          <t>185634245.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>42.78</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>26.66</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>46362</t>
+          <t>47183</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5013.788</t>
+          <t>5128.692</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-10.48</t>
+          <t>-10.64</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,63 +1874,63 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>39.04000000000001</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>39.71</v>
+        <v>39.53</v>
       </c>
       <c r="AN4" t="n">
-        <v>40.26</v>
+        <v>40.2</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-27.08</t>
+          <t>-19.58</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,53 +1950,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.40</t>
+          <t>-106.73</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/11/20</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>208756120.875</t>
+          <t>209175344.6319543</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>195613562.0</t>
+          <t>201657416.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>255801795.6</v>
+        <v>252360977.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>285762642.3</t>
+          <t>282417854.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>457544220.78</v>
+        <v>423553251.3</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-29960846</t>
+          <t>-30056877</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-35539525.3223268</t>
+          <t>-35760325.94395395</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-35925485.46414912</t>
+          <t>-36974729.3629033</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>195613562.0</t>
+          <t>201657416.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>26.66</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>46362</t>
+          <t>47183</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4826.572</t>
+          <t>5013.788</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-10.48</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>39.16</t>
+          <t>39.04000000000001</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>39.91</v>
+        <v>39.71</v>
       </c>
       <c r="AN5" t="n">
-        <v>40.4</v>
+        <v>40.26</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-27.86</t>
+          <t>-27.08</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,53 +2380,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.97</t>
+          <t>-106.40</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/11/20</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>208756120.875</t>
+          <t>209175344.6319543</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>188357162.0</t>
+          <t>195613562.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>277240412.8</v>
+        <v>255801795.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>297413036.7</t>
+          <t>285762642.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>528814161.92</v>
+        <v>457544220.78</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-20172623</t>
+          <t>-29960846</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-35469350.75108638</t>
+          <t>-35539525.3223268</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-32495956.77078068</t>
+          <t>-35925485.46414912</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>188357162.0</t>
+          <t>195613562.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>26.66</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>46362</t>
+          <t>47183</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9258.407</t>
+          <t>4826.572</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.16</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>39.94</v>
+        <v>39.91</v>
       </c>
       <c r="AN6" t="n">
-        <v>40.53</v>
+        <v>40.4</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-32.78</t>
+          <t>-27.86</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,53 +2810,53 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.55</t>
+          <t>-105.97</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/11/20</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>208756120.875</t>
+          <t>209175344.6319543</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>355837208.0</t>
+          <t>188357162.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>346026858.8</v>
+        <v>277240412.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>290442567.6</t>
+          <t>297413036.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>558638708.96</v>
+        <v>528814161.92</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>55584291</t>
+          <t>-20172623</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-36009967.83841468</t>
+          <t>-35469350.75108638</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-25658588.75272644</t>
+          <t>-32495956.77078068</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>355837208.0</t>
+          <t>188357162.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>26.66</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>46362</t>
+          <t>47183</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7921.053</t>
+          <t>9258.407</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>19.14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>39.93</v>
+        <v>39.94</v>
       </c>
       <c r="AN7" t="n">
-        <v>40.66</v>
+        <v>40.53</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>38.97</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-32.78</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,53 +3240,53 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.10</t>
+          <t>-105.55</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/11/20</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>208756120.875</t>
+          <t>209175344.6319543</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>320339540.0</t>
+          <t>355837208.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>322944767</v>
+        <v>346026858.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>273188557.9</t>
+          <t>290442567.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>613979125.7</v>
+        <v>558638708.96</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>49756209</t>
+          <t>55584291</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-37892036.76308528</t>
+          <t>-36009967.83841468</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-32918832.62862295</t>
+          <t>-25658588.75272644</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>320339540.0</t>
+          <t>355837208.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>26.66</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>46362</t>
+          <t>47183</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5612.57</t>
+          <t>7921.053</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>18.21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,42 +3594,42 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>51.71</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -3638,24 +3638,24 @@
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>39.85</v>
+        <v>39.93</v>
       </c>
       <c r="AN8" t="n">
-        <v>40.74</v>
+        <v>40.66</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>38.97</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-26.63</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3670,53 +3670,53 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.13</t>
+          <t>-105.10</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/11/20</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>208756120.875</t>
+          <t>209175344.6319543</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>218861506.0</t>
+          <t>320339540.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>312474732.2</v>
+        <v>322944767</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>262014209.7</t>
+          <t>273188557.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>631667121.9400001</v>
+        <v>613979125.7</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>50460522</t>
+          <t>49756209</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-38796255.69662388</t>
+          <t>-37892036.76308528</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-38311615.42888141</t>
+          <t>-32918832.62862295</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>218861506.0</t>
+          <t>320339540.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>26.66</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>46362</t>
+          <t>47183</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7632.447</t>
+          <t>5612.57</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>39.83</v>
+        <v>39.85</v>
       </c>
       <c r="AN9" t="n">
-        <v>40.77</v>
+        <v>40.74</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>38.66</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-23.20</t>
+          <t>-26.63</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,53 +4100,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.79</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/11/20</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>208756120.875</t>
+          <t>209175344.6319543</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>302806648.0</t>
+          <t>218861506.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>315723489</v>
+        <v>312474732.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>267936291.1</t>
+          <t>262014209.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>654424013.3</v>
+        <v>631667121.9400001</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>47787197</t>
+          <t>50460522</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-38884372.1089407</t>
+          <t>-38796255.69662388</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-33774672.37821913</t>
+          <t>-38311615.42888141</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>302806648.0</t>
+          <t>218861506.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>26.66</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>46362</t>
+          <t>47183</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>38.5</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>39.1</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>40.45</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>38.85</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>39.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13085.646</t>
+          <t>7632.447</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.70</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,63 +4454,63 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>42.31</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>41.19</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>39.57000000000001</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>39.78</v>
+        <v>39.83</v>
       </c>
       <c r="AN10" t="n">
-        <v>40.87</v>
+        <v>40.77</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.66</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-28.47</t>
+          <t>-23.20</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,53 +4530,53 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.51</t>
+          <t>-104.79</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/11/20</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>208756120.875</t>
+          <t>209175344.6319543</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>532289392.0</t>
+          <t>302806648.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>317585660.6</v>
+        <v>315723489</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>263274442.8</t>
+          <t>267936291.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>673739372.28</v>
+        <v>654424013.3</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>54311217</t>
+          <t>47787197</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-39813408.42361735</t>
+          <t>-38884372.1089407</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-35081209.22090816</t>
+          <t>-33774672.37821913</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>532289392.0</t>
+          <t>302806648.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>42.24</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>26.66</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>46362</t>
+          <t>47183</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6136.175</t>
+          <t>13085.646</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>11.70</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>42.31</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>41.19</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>39.51000000000001</t>
+          <t>39.57000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>39.76</v>
+        <v>39.78</v>
       </c>
       <c r="AN11" t="n">
-        <v>41</v>
+        <v>40.87</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-36.08</t>
+          <t>-28.47</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,53 +4960,53 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.19</t>
+          <t>-104.51</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/11/20</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>208756120.875</t>
+          <t>209175344.6319543</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>240426749.0</t>
+          <t>532289392.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>234858276.4</v>
+        <v>317585660.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>236240878.5</t>
+          <t>263274442.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>679732391.62</v>
+        <v>673739372.28</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1382602</t>
+          <t>54311217</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-40673808.27865538</t>
+          <t>-39813408.42361735</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-60282226.95257431</t>
+          <t>-35081209.22090816</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>240426749.0</t>
+          <t>532289392.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>26.66</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>46362</t>
+          <t>47183</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6635.823</t>
+          <t>6136.175</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-17.42</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>7.80</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.51000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>39.78</v>
+        <v>39.76</v>
       </c>
       <c r="AN12" t="n">
-        <v>41.14</v>
+        <v>41</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>38.33</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>-36.08</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,53 +5390,53 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.81</t>
+          <t>-104.19</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/11/20</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>208756120.875</t>
+          <t>209175344.6319543</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>267989366.0</t>
+          <t>240426749.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>223432348.8</v>
+        <v>234858276.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>270578244.9</t>
+          <t>236240878.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>693037521.34</v>
+        <v>679732391.62</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-47145896</t>
+          <t>-1382602</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-37108641.24703376</t>
+          <t>-40673808.27865538</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-62859746.71379119</t>
+          <t>-60282226.95257431</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>267989366.0</t>
+          <t>240426749.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>40.61</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>26.66</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>46362</t>
+          <t>47183</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>153271.208</t>
+          <t>252999.258</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,74 +5628,74 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-12.69</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-11-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>56.2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>-34.41</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>56.2</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
           <t>45.3</t>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>45.49</t>
+          <t>75.09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,78 +5744,78 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>1,290</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>153271</t>
+          <t>252999</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>82.26</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>60.75</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>13.06</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>49.42</v>
+        <v>50.29</v>
       </c>
       <c r="AN13" t="n">
-        <v>44.05</v>
+        <v>44.48</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>42.71</t>
+          <t>42.98</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
@@ -5830,48 +5830,48 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1349701199.475</t>
+          <t>1379646183.246077</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>8423612196.0</t>
+          <t>14894089882.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>5638461114.4</v>
+        <v>7684941519.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>8596752401.4</t>
+          <t>8801421193.5</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>3818531527.48</v>
+        <v>4102103371.86</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-1116479674</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>756097253.2650311</t>
+          <t>756898935.2935112</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>206082660.0115242</t>
+          <t>761308186.4501514</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>8423612196.0</t>
+          <t>14894089882.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>34.13</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>445712</t>
+          <t>467918</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6033,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>68850.257</t>
+          <t>153271.208</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,87 +6058,87 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-34.41</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
           <t>51.1</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>9.07</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-36.14</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>45.49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,83 +6174,83 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>1,290</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>153271</t>
+          <t>252999</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>82.26</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>9.80</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>53.48</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>48.7</v>
+        <v>49.42</v>
       </c>
       <c r="AN14" t="n">
-        <v>43.68</v>
+        <v>44.05</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>42.71</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,24 +6260,24 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1349701199.475</t>
+          <t>1379646183.246077</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>3512622548.0</t>
+          <t>8423612196.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>6095469315</v>
+        <v>5638461114.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>9544851503.2</t>
+          <t>8596752401.4</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>3663541757.9</v>
+        <v>3818531527.48</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6286,22 +6286,22 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>856099906.5838505</t>
+          <t>756097253.2650311</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>98808707.88450241</t>
+          <t>206082660.0115242</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>3512622548.0</t>
+          <t>8423612196.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>34.13</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>445712</t>
+          <t>467918</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>126477.283</t>
+          <t>68850.257</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-30.86</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,12 +6604,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>1,290</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>153271</t>
+          <t>252999</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6619,53 +6619,53 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>9.80</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>53.48</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>48.25</v>
+        <v>48.7</v>
       </c>
       <c r="AN15" t="n">
-        <v>43.41</v>
+        <v>43.68</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6675,12 +6675,12 @@
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,24 +6690,24 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1349701199.475</t>
+          <t>1379646183.246077</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>6744255965.0</t>
+          <t>3512622548.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>6936487304.4</v>
+        <v>6095469315</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>10032139013.4</t>
+          <t>9544851503.2</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>3632131847.42</v>
+        <v>3663541757.9</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6716,17 +6716,17 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>993789215.4382774</t>
+          <t>856099906.5838505</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>468208784.7071676</t>
+          <t>98808707.88450241</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>6744255965.0</t>
+          <t>3512622548.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>445712</t>
+          <t>467918</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>89940.447</t>
+          <t>126477.283</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>11.19</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-15.62</t>
+          <t>-30.86</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>26.69</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,83 +7034,83 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>1,290</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>153271</t>
+          <t>252999</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>73.89</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>47.74</v>
+        <v>48.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>43.12</v>
+        <v>43.41</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>42.21</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>21.20</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1349701199.475</t>
+          <t>1379646183.246077</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>4850127005.0</t>
+          <t>6744255965.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>8366597065.8</v>
+        <v>6936487304.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>9915210649.5</t>
+          <t>10032139013.4</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>3525171118.12</v>
+        <v>3632131847.42</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-1548613583</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>1089349293.753025</t>
+          <t>993789215.4382774</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>632955000.321434</t>
+          <t>468208784.7071676</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>4850127005.0</t>
+          <t>6744255965.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>30.79</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>445712</t>
+          <t>467918</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>87722.137</t>
+          <t>89940.447</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>20.97</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.69</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,83 +7464,83 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>1,290</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>153271</t>
+          <t>252999</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>73.89</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>15.21</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>55.34</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>47.15</v>
+        <v>47.74</v>
       </c>
       <c r="AN17" t="n">
-        <v>42.8</v>
+        <v>43.12</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.97</t>
+          <t>42.21</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>21.20</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-8.31</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1349701199.475</t>
+          <t>1379646183.246077</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>4661687858.0</t>
+          <t>4850127005.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>9917900867.799999</v>
+        <v>8366597065.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>9646311981.3</t>
+          <t>9915210649.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>3483979320.62</v>
+        <v>3525171118.12</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>271588886</t>
+          <t>-1548613583</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>1172330074.37695</t>
+          <t>1089349293.753025</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>1048643589.758906</t>
+          <t>632955000.321434</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>4661687858.0</t>
+          <t>4850127005.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>30.79</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>445712</t>
+          <t>467918</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>187213.322</t>
+          <t>87722.137</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>22.40</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,83 +7894,83 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>1,290</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>153271</t>
+          <t>252999</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>95.02</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>90.43</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>17.38</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>55.96</t>
+          <t>55.34</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>46.69</v>
+        <v>47.15</v>
       </c>
       <c r="AN18" t="n">
-        <v>42.52</v>
+        <v>42.8</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>41.97</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>45.57</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-14.84</t>
+          <t>-10.26</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1349701199.475</t>
+          <t>1379646183.246077</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>10708653199.0</t>
+          <t>4661687858.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>11555043688.4</v>
+        <v>9917900867.799999</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>9440522375.4</t>
+          <t>9646311981.3</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>3413291777.02</v>
+        <v>3483979320.62</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>2114521313</t>
+          <t>271588886</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1194818526.125685</t>
+          <t>1172330074.37695</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>1625222783.642477</t>
+          <t>1048643589.758906</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>10708653199.0</t>
+          <t>4661687858.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>35.08</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>445712</t>
+          <t>467918</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>141242.686</t>
+          <t>187213.322</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>53.41</t>
+          <t>22.40</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,83 +8324,83 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>1,290</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>153271</t>
+          <t>252999</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>76.27</t>
+          <t>95.02</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>92.09</t>
+          <t>90.43</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>55.96</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>45.98</v>
+        <v>46.69</v>
       </c>
       <c r="AN19" t="n">
-        <v>42.16</v>
+        <v>42.52</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.49</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>45.57</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-24.54</t>
+          <t>-16.65</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1349701199.475</t>
+          <t>1379646183.246077</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>7717712495.0</t>
+          <t>10708653199.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>12994233691.4</v>
+        <v>11555043688.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>8470087592.9</t>
+          <t>9440522375.4</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>3233128694.92</v>
+        <v>3413291777.02</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>2114521313</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1116563206.577178</t>
+          <t>1194818526.125685</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>1742974531.810349</t>
+          <t>1625222783.642477</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>7717712495.0</t>
+          <t>10708653199.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>28.40</t>
+          <t>35.08</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>445712</t>
+          <t>467918</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="CG19" t="inlineStr">
+        <is>
           <t>56.6</t>
-        </is>
-      </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>56.8</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="CG19" t="inlineStr">
-        <is>
-          <t>53.8</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>237895.796</t>
+          <t>141242.686</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>67.79</t>
+          <t>53.41</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>70.60</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,83 +8754,83 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>1,290</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>153271</t>
+          <t>252999</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.27</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.09</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>45.39</v>
+        <v>45.98</v>
       </c>
       <c r="AN20" t="n">
-        <v>41.86</v>
+        <v>42.16</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>41.49</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>77.41</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-34.95</t>
+          <t>-26.15</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,24 +8840,24 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1349701199.475</t>
+          <t>1379646183.246077</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>13894804772.0</t>
+          <t>7717712495.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>13127790722.4</v>
+        <v>12994233691.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>7823899971.0</t>
+          <t>8470087592.9</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>3109382048.22</v>
+        <v>3233128694.92</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8866,17 +8866,17 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1002670238.352965</t>
+          <t>1116563206.577178</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>2169400157.056937</t>
+          <t>1742974531.810349</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>13894804772.0</t>
+          <t>7717712495.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>28.40</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>445712</t>
+          <t>467918</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>216309.874</t>
+          <t>237895.796</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>67.79</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>26.49</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>64.20</t>
+          <t>70.60</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>1,290</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>153271</t>
+          <t>252999</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,63 +9204,63 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>20.30</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>44.62</v>
+        <v>45.39</v>
       </c>
       <c r="AN21" t="n">
-        <v>41.5</v>
+        <v>41.86</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.22</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>91.69</t>
+          <t>77.41</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-47.54</t>
+          <t>-36.33</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,24 +9270,24 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1349701199.475</t>
+          <t>1379646183.246077</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>12606646015.0</t>
+          <t>13894804772.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>11463824233.2</v>
+        <v>13127790722.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>6558502593.2</t>
+          <t>7823899971.0</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>2879764455.78</v>
+        <v>3109382048.22</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9296,17 +9296,17 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>790537525.8613333</t>
+          <t>1002670238.352965</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>2039269729.264316</t>
+          <t>2169400157.056937</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>12606646015.0</t>
+          <t>13894804772.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>445712</t>
+          <t>467918</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>235389.305</t>
+          <t>216309.874</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>73.90</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>64.20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>1,290</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>153271</t>
+          <t>252999</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,63 +9634,63 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>43.9</v>
+        <v>44.62</v>
       </c>
       <c r="AN22" t="n">
-        <v>41.17</v>
+        <v>41.5</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>104.45</t>
+          <t>91.69</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-59.56</t>
+          <t>-48.65</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,24 +9700,24 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1349701199.475</t>
+          <t>1379646183.246077</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>12847401961.0</t>
+          <t>12606646015.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>9374723094.799999</v>
+        <v>11463824233.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>5390815186.5</t>
+          <t>6558502593.2</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>2722439698.1</v>
+        <v>2879764455.78</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9726,17 +9726,17 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>563495307.060791</t>
+          <t>790537525.8613333</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>1918555066.051131</t>
+          <t>2039269729.264316</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>12847401961.0</t>
+          <t>12606646015.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>32.70</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>445712</t>
+          <t>467918</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>336947.705</t>
+          <t>235389.305</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>70.38</t>
+          <t>73.90</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>22.74</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>1,290</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>153271</t>
+          <t>252999</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,63 +10064,63 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>43.19</v>
+        <v>43.9</v>
       </c>
       <c r="AN23" t="n">
-        <v>40.9</v>
+        <v>41.17</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>105.78</t>
+          <t>104.45</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-70.12</t>
+          <t>-60.42</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,24 +10130,24 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1349701199.475</t>
+          <t>1379646183.246077</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>17904603214.0</t>
+          <t>12847401961.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>7326001062.4</v>
+        <v>9374723094.799999</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>4299803431.4</t>
+          <t>5390815186.5</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>2525457286.94</v>
+        <v>2722439698.1</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10156,17 +10156,17 @@
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>317120805.4261836</t>
+          <t>563495307.060791</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>1651790443.45904</t>
+          <t>1918555066.051131</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>17904603214.0</t>
+          <t>12847401961.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>28.40</t>
+          <t>32.70</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>445712</t>
+          <t>467918</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/酚醛樹脂.xlsx
+++ b/Result/checksun_type/酚醛樹脂.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8360.012</t>
+          <t>5475.163</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-21.99</t>
+          <t>-9.98</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>71.05</t>
+          <t>71.65</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>39.32000000000001</t>
+          <t>39.34</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>39.45</v>
+        <v>39.38</v>
       </c>
       <c r="AN2" t="n">
-        <v>40.13</v>
+        <v>40.07</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>39.84</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>29.60</t>
+          <t>20.85</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.28</t>
+          <t>-105.97</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>209175344.6319543</t>
+          <t>209340330.3376068</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>335087983.0</t>
+          <t>216663540.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>221270073.6</v>
+        <v>226931349.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>283648466.2</t>
+          <t>252085881.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>409053915.06</v>
+        <v>403055695.96</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-62378392</t>
+          <t>-25154531</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-34631030.87829307</t>
+          <t>-33416919.66615964</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-26536163.31492347</t>
+          <t>-26739307.99942577</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>335087983.0</t>
+          <t>216663540.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>45.31</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>47183</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4713.942</t>
+          <t>8360.012</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-17.78</t>
+          <t>-21.99</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>71.05</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>48.25</t>
-        </is>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>38.91</t>
+          <t>39.32000000000001</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>39.48</v>
+        <v>39.45</v>
       </c>
       <c r="AN3" t="n">
-        <v>40.15</v>
+        <v>40.13</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>39.84</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>29.60</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.75</t>
+          <t>-106.28</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>209175344.6319543</t>
+          <t>209340330.3376068</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>185634245.0</t>
+          <t>335087983.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>225419918.6</v>
+        <v>221270073.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>274182342.8</t>
+          <t>283648466.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>413674654.36</v>
+        <v>409053915.06</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-48762424</t>
+          <t>-62378392</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-36102824.98072391</t>
+          <t>-34631030.87829307</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-37986569.68295866</t>
+          <t>-26536163.31492347</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>185634245.0</t>
+          <t>335087983.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>42.78</t>
+          <t>45.31</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>47183</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5128.692</t>
+          <t>4713.942</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-10.64</t>
+          <t>-17.78</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,32 +1874,32 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>71.05</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1909,33 +1909,33 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>38.91</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>39.53</v>
+        <v>39.48</v>
       </c>
       <c r="AN4" t="n">
-        <v>40.2</v>
+        <v>40.15</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-19.58</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.73</t>
+          <t>-106.75</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>209175344.6319543</t>
+          <t>209340330.3376068</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>201657416.0</t>
+          <t>185634245.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>252360977.6</v>
+        <v>225419918.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>282417854.9</t>
+          <t>274182342.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>423553251.3</v>
+        <v>413674654.36</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-30056877</t>
+          <t>-48762424</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-35760325.94395395</t>
+          <t>-36102824.98072391</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-36974729.3629033</t>
+          <t>-37986569.68295866</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>201657416.0</t>
+          <t>185634245.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>42.78</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>47183</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5013.788</t>
+          <t>5128.692</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-10.48</t>
+          <t>-10.64</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,63 +2304,63 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>39.04000000000001</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>39.71</v>
+        <v>39.53</v>
       </c>
       <c r="AN5" t="n">
-        <v>40.26</v>
+        <v>40.2</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-27.08</t>
+          <t>-19.58</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.40</t>
+          <t>-106.73</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>209175344.6319543</t>
+          <t>209340330.3376068</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>195613562.0</t>
+          <t>201657416.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>255801795.6</v>
+        <v>252360977.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>285762642.3</t>
+          <t>282417854.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>457544220.78</v>
+        <v>423553251.3</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-29960846</t>
+          <t>-30056877</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-35539525.3223268</t>
+          <t>-35760325.94395395</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-35925485.46414912</t>
+          <t>-36974729.3629033</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>195613562.0</t>
+          <t>201657416.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>47183</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4826.572</t>
+          <t>5013.788</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-10.48</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>39.16</t>
+          <t>39.04000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>39.91</v>
+        <v>39.71</v>
       </c>
       <c r="AN6" t="n">
-        <v>40.4</v>
+        <v>40.26</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-27.86</t>
+          <t>-27.08</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.97</t>
+          <t>-106.40</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>209175344.6319543</t>
+          <t>209340330.3376068</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>188357162.0</t>
+          <t>195613562.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>277240412.8</v>
+        <v>255801795.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>297413036.7</t>
+          <t>285762642.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>528814161.92</v>
+        <v>457544220.78</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-20172623</t>
+          <t>-29960846</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-35469350.75108638</t>
+          <t>-35539525.3223268</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-32495956.77078068</t>
+          <t>-35925485.46414912</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>188357162.0</t>
+          <t>195613562.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>47183</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9258.407</t>
+          <t>4826.572</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.16</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>39.94</v>
+        <v>39.91</v>
       </c>
       <c r="AN7" t="n">
-        <v>40.53</v>
+        <v>40.4</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-32.78</t>
+          <t>-27.86</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.55</t>
+          <t>-105.97</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>209175344.6319543</t>
+          <t>209340330.3376068</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>355837208.0</t>
+          <t>188357162.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>346026858.8</v>
+        <v>277240412.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>290442567.6</t>
+          <t>297413036.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>558638708.96</v>
+        <v>528814161.92</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>55584291</t>
+          <t>-20172623</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-36009967.83841468</t>
+          <t>-35469350.75108638</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-25658588.75272644</t>
+          <t>-32495956.77078068</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>355837208.0</t>
+          <t>188357162.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>47183</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7921.053</t>
+          <t>9258.407</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>19.14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>39.93</v>
+        <v>39.94</v>
       </c>
       <c r="AN8" t="n">
-        <v>40.66</v>
+        <v>40.53</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>38.97</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-32.78</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.10</t>
+          <t>-105.55</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>209175344.6319543</t>
+          <t>209340330.3376068</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>320339540.0</t>
+          <t>355837208.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>322944767</v>
+        <v>346026858.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>273188557.9</t>
+          <t>290442567.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>613979125.7</v>
+        <v>558638708.96</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>49756209</t>
+          <t>55584291</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-37892036.76308528</t>
+          <t>-36009967.83841468</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-32918832.62862295</t>
+          <t>-25658588.75272644</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>320339540.0</t>
+          <t>355837208.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>47183</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5612.57</t>
+          <t>7921.053</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>18.21</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,42 +4024,42 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>51.71</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -4068,24 +4068,24 @@
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>39.85</v>
+        <v>39.93</v>
       </c>
       <c r="AN9" t="n">
-        <v>40.74</v>
+        <v>40.66</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>38.97</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-26.63</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.13</t>
+          <t>-105.10</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>209175344.6319543</t>
+          <t>209340330.3376068</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>218861506.0</t>
+          <t>320339540.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>312474732.2</v>
+        <v>322944767</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>262014209.7</t>
+          <t>273188557.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>631667121.9400001</v>
+        <v>613979125.7</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>50460522</t>
+          <t>49756209</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-38796255.69662388</t>
+          <t>-37892036.76308528</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-38311615.42888141</t>
+          <t>-32918832.62862295</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>218861506.0</t>
+          <t>320339540.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>47183</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7632.447</t>
+          <t>5612.57</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>39.83</v>
+        <v>39.85</v>
       </c>
       <c r="AN10" t="n">
-        <v>40.77</v>
+        <v>40.74</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>38.66</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-23.20</t>
+          <t>-26.63</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.79</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>209175344.6319543</t>
+          <t>209340330.3376068</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>302806648.0</t>
+          <t>218861506.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>315723489</v>
+        <v>312474732.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>267936291.1</t>
+          <t>262014209.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>654424013.3</v>
+        <v>631667121.9400001</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>47787197</t>
+          <t>50460522</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-38884372.1089407</t>
+          <t>-38796255.69662388</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-33774672.37821913</t>
+          <t>-38311615.42888141</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>302806648.0</t>
+          <t>218861506.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>47183</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>38.5</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>39.1</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>40.45</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>38.85</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>39.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13085.646</t>
+          <t>7632.447</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.70</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,63 +4884,63 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>42.31</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>41.19</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>39.57000000000001</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>39.78</v>
+        <v>39.83</v>
       </c>
       <c r="AN11" t="n">
-        <v>40.87</v>
+        <v>40.77</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.66</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-28.47</t>
+          <t>-23.20</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.51</t>
+          <t>-104.79</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>209175344.6319543</t>
+          <t>209340330.3376068</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>532289392.0</t>
+          <t>302806648.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>317585660.6</v>
+        <v>315723489</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>263274442.8</t>
+          <t>267936291.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>673739372.28</v>
+        <v>654424013.3</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>54311217</t>
+          <t>47787197</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-39813408.42361735</t>
+          <t>-38884372.1089407</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-35081209.22090816</t>
+          <t>-33774672.37821913</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>532289392.0</t>
+          <t>302806648.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>42.24</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>47183</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6136.175</t>
+          <t>13085.646</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>11.70</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>42.31</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>41.19</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>39.51000000000001</t>
+          <t>39.57000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>39.76</v>
+        <v>39.78</v>
       </c>
       <c r="AN12" t="n">
-        <v>41</v>
+        <v>40.87</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-36.08</t>
+          <t>-28.47</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.19</t>
+          <t>-104.51</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>209175344.6319543</t>
+          <t>209340330.3376068</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>240426749.0</t>
+          <t>532289392.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>234858276.4</v>
+        <v>317585660.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>236240878.5</t>
+          <t>263274442.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>679732391.62</v>
+        <v>673739372.28</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1382602</t>
+          <t>54311217</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-40673808.27865538</t>
+          <t>-39813408.42361735</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-60282226.95257431</t>
+          <t>-35081209.22090816</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>240426749.0</t>
+          <t>532289392.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>47183</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>252999.258</t>
+          <t>234435.298</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-12.69</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>75.09</t>
+          <t>69.58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,12 +5744,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1,290</t>
+          <t>1,154</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>252999</t>
+          <t>234435</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5759,63 +5759,63 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>60.75</t>
+          <t>94.09</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>13.06</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>55.96</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>50.29</v>
+        <v>51.28</v>
       </c>
       <c r="AN13" t="n">
-        <v>44.48</v>
+        <v>44.97</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>42.98</t>
+          <t>43.28</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
@@ -5830,48 +5830,48 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1379646183.246077</t>
+          <t>1408524930.754273</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>14894089882.0</t>
+          <t>14435017956.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>7684941519.2</v>
+        <v>9601919709.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>8801421193.5</t>
+          <t>8984258387.6</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>4102103371.86</v>
+        <v>4361742818</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-1116479674</t>
+          <t>617661321</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>756898935.2935112</t>
+          <t>809145707.6861923</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>761308186.4501514</t>
+          <t>1096502955.845938</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>14894089882.0</t>
+          <t>14435017956.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>40.81</t>
+          <t>45.82</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>467918</t>
+          <t>484573</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>153271.208</t>
+          <t>252999.258</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,74 +6058,74 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-12.69</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>56.2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-34.41</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>56.2</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
       <c r="T14" t="inlineStr">
         <is>
           <t>45.3</t>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>45.49</t>
+          <t>75.09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,83 +6174,83 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1,290</t>
+          <t>1,154</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>252999</t>
+          <t>234435</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>82.26</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>60.75</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>13.06</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>49.42</v>
+        <v>50.29</v>
       </c>
       <c r="AN14" t="n">
-        <v>44.05</v>
+        <v>44.48</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>42.71</t>
+          <t>42.98</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,48 +6260,48 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1379646183.246077</t>
+          <t>1408524930.754273</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>8423612196.0</t>
+          <t>14894089882.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>5638461114.4</v>
+        <v>7684941519.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>8596752401.4</t>
+          <t>8801421193.5</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>3818531527.48</v>
+        <v>4102103371.86</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-1116479674</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>756097253.2650311</t>
+          <t>756898935.2935112</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>206082660.0115242</t>
+          <t>761308186.4501514</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>8423612196.0</t>
+          <t>14894089882.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>34.13</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>467918</t>
+          <t>484573</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>68850.257</t>
+          <t>153271.208</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,87 +6488,87 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>8.02</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-34.41</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
           <t>51.1</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>13.39</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-36.14</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-11-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>45.49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,83 +6604,83 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1,290</t>
+          <t>1,154</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>252999</t>
+          <t>234435</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>82.26</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>9.80</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>53.48</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>48.7</v>
+        <v>49.42</v>
       </c>
       <c r="AN15" t="n">
-        <v>43.68</v>
+        <v>44.05</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>42.71</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,24 +6690,24 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1379646183.246077</t>
+          <t>1408524930.754273</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>3512622548.0</t>
+          <t>8423612196.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>6095469315</v>
+        <v>5638461114.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>9544851503.2</t>
+          <t>8596752401.4</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>3663541757.9</v>
+        <v>3818531527.48</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6716,22 +6716,22 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>856099906.5838505</t>
+          <t>756097253.2650311</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>98808707.88450241</t>
+          <t>206082660.0115242</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>3512622548.0</t>
+          <t>8423612196.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>34.13</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>467918</t>
+          <t>484573</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6893,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>126477.283</t>
+          <t>68850.257</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>16.37</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-30.86</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,12 +7034,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1,290</t>
+          <t>1,154</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>252999</t>
+          <t>234435</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7049,53 +7049,53 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>9.80</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>53.48</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>48.25</v>
+        <v>48.7</v>
       </c>
       <c r="AN16" t="n">
-        <v>43.41</v>
+        <v>43.68</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,24 +7120,24 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1379646183.246077</t>
+          <t>1408524930.754273</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>6744255965.0</t>
+          <t>3512622548.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>6936487304.4</v>
+        <v>6095469315</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>10032139013.4</t>
+          <t>9544851503.2</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>3632131847.42</v>
+        <v>3663541757.9</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7146,17 +7146,17 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>993789215.4382774</t>
+          <t>856099906.5838505</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>468208784.7071676</t>
+          <t>98808707.88450241</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>6744255965.0</t>
+          <t>3512622548.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>467918</t>
+          <t>484573</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>89940.447</t>
+          <t>126477.283</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>14.24</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-15.62</t>
+          <t>-30.86</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>26.69</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,83 +7464,83 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1,290</t>
+          <t>1,154</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>252999</t>
+          <t>234435</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>73.89</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>47.74</v>
+        <v>48.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>43.12</v>
+        <v>43.41</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>42.21</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>21.20</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1379646183.246077</t>
+          <t>1408524930.754273</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>4850127005.0</t>
+          <t>6744255965.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>8366597065.8</v>
+        <v>6936487304.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>9915210649.5</t>
+          <t>10032139013.4</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>3525171118.12</v>
+        <v>3632131847.42</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-1548613583</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>1089349293.753025</t>
+          <t>993789215.4382774</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>632955000.321434</t>
+          <t>468208784.7071676</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>4850127005.0</t>
+          <t>6744255965.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>30.79</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>467918</t>
+          <t>484573</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>87722.137</t>
+          <t>89940.447</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>20.97</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.69</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,83 +7894,83 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1,290</t>
+          <t>1,154</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>252999</t>
+          <t>234435</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>73.89</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>15.21</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>55.34</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>47.15</v>
+        <v>47.74</v>
       </c>
       <c r="AN18" t="n">
-        <v>42.8</v>
+        <v>43.12</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.97</t>
+          <t>42.21</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>21.20</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-10.26</t>
+          <t>-8.66</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1379646183.246077</t>
+          <t>1408524930.754273</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>4661687858.0</t>
+          <t>4850127005.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>9917900867.799999</v>
+        <v>8366597065.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>9646311981.3</t>
+          <t>9915210649.5</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>3483979320.62</v>
+        <v>3525171118.12</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>271588886</t>
+          <t>-1548613583</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1172330074.37695</t>
+          <t>1089349293.753025</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>1048643589.758906</t>
+          <t>632955000.321434</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>4661687858.0</t>
+          <t>4850127005.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>30.79</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>467918</t>
+          <t>484573</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>187213.322</t>
+          <t>87722.137</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>22.40</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,83 +8324,83 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1,290</t>
+          <t>1,154</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>252999</t>
+          <t>234435</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>95.02</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>90.43</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>17.38</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>55.96</t>
+          <t>55.34</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>46.69</v>
+        <v>47.15</v>
       </c>
       <c r="AN19" t="n">
-        <v>42.52</v>
+        <v>42.8</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>41.97</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>45.57</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-16.65</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1379646183.246077</t>
+          <t>1408524930.754273</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>10708653199.0</t>
+          <t>4661687858.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>11555043688.4</v>
+        <v>9917900867.799999</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>9440522375.4</t>
+          <t>9646311981.3</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>3413291777.02</v>
+        <v>3483979320.62</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>2114521313</t>
+          <t>271588886</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1194818526.125685</t>
+          <t>1172330074.37695</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>1625222783.642477</t>
+          <t>1048643589.758906</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>10708653199.0</t>
+          <t>4661687858.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>35.08</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>467918</t>
+          <t>484573</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>141242.686</t>
+          <t>187213.322</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>53.41</t>
+          <t>22.40</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,83 +8754,83 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1,290</t>
+          <t>1,154</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>252999</t>
+          <t>234435</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>76.27</t>
+          <t>95.02</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>92.09</t>
+          <t>90.43</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>55.96</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>45.98</v>
+        <v>46.69</v>
       </c>
       <c r="AN20" t="n">
-        <v>42.16</v>
+        <v>42.52</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>41.49</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>45.57</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-26.15</t>
+          <t>-19.67</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1379646183.246077</t>
+          <t>1408524930.754273</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>7717712495.0</t>
+          <t>10708653199.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>12994233691.4</v>
+        <v>11555043688.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>8470087592.9</t>
+          <t>9440522375.4</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>3233128694.92</v>
+        <v>3413291777.02</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>2114521313</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1116563206.577178</t>
+          <t>1194818526.125685</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>1742974531.810349</t>
+          <t>1625222783.642477</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>7717712495.0</t>
+          <t>10708653199.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>28.40</t>
+          <t>35.08</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>467918</t>
+          <t>484573</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="CG20" t="inlineStr">
+        <is>
           <t>56.6</t>
-        </is>
-      </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>56.8</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="CG20" t="inlineStr">
-        <is>
-          <t>53.8</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>237895.796</t>
+          <t>141242.686</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>67.79</t>
+          <t>53.41</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>70.60</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,83 +9184,83 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1,290</t>
+          <t>1,154</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>252999</t>
+          <t>234435</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.27</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.09</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>45.39</v>
+        <v>45.98</v>
       </c>
       <c r="AN21" t="n">
-        <v>41.86</v>
+        <v>42.16</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>41.49</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>77.41</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-36.33</t>
+          <t>-28.82</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,24 +9270,24 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1379646183.246077</t>
+          <t>1408524930.754273</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>13894804772.0</t>
+          <t>7717712495.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>13127790722.4</v>
+        <v>12994233691.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>7823899971.0</t>
+          <t>8470087592.9</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>3109382048.22</v>
+        <v>3233128694.92</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9296,17 +9296,17 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1002670238.352965</t>
+          <t>1116563206.577178</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>2169400157.056937</t>
+          <t>1742974531.810349</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>13894804772.0</t>
+          <t>7717712495.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>28.40</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>467918</t>
+          <t>484573</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>216309.874</t>
+          <t>237895.796</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>67.79</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>26.49</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>64.20</t>
+          <t>70.60</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1,290</t>
+          <t>1,154</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>252999</t>
+          <t>234435</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,63 +9634,63 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>20.30</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>44.62</v>
+        <v>45.39</v>
       </c>
       <c r="AN22" t="n">
-        <v>41.5</v>
+        <v>41.86</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.22</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>91.69</t>
+          <t>77.41</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-48.65</t>
+          <t>-38.63</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,24 +9700,24 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1379646183.246077</t>
+          <t>1408524930.754273</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>12606646015.0</t>
+          <t>13894804772.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>11463824233.2</v>
+        <v>13127790722.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>6558502593.2</t>
+          <t>7823899971.0</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>2879764455.78</v>
+        <v>3109382048.22</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9726,17 +9726,17 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>790537525.8613333</t>
+          <t>1002670238.352965</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>2039269729.264316</t>
+          <t>2169400157.056937</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>12606646015.0</t>
+          <t>13894804772.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>467918</t>
+          <t>484573</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>235389.305</t>
+          <t>216309.874</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>73.90</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>64.20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1,290</t>
+          <t>1,154</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>252999</t>
+          <t>234435</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,63 +10064,63 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>43.9</v>
+        <v>44.62</v>
       </c>
       <c r="AN23" t="n">
-        <v>41.17</v>
+        <v>41.5</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>104.45</t>
+          <t>91.69</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-60.42</t>
+          <t>-50.51</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,24 +10130,24 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1379646183.246077</t>
+          <t>1408524930.754273</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>12847401961.0</t>
+          <t>12606646015.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>9374723094.799999</v>
+        <v>11463824233.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>5390815186.5</t>
+          <t>6558502593.2</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>2722439698.1</v>
+        <v>2879764455.78</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10156,17 +10156,17 @@
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>563495307.060791</t>
+          <t>790537525.8613333</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>1918555066.051131</t>
+          <t>2039269729.264316</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>12847401961.0</t>
+          <t>12606646015.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>32.70</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>467918</t>
+          <t>484573</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/酚醛樹脂.xlsx
+++ b/Result/checksun_type/酚醛樹脂.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5475.163</t>
+          <t>8001.481</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-9.98</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>80.49</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>71.65</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>39.34</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="AM2" t="n">
         <v>39.38</v>
       </c>
       <c r="AN2" t="n">
-        <v>40.07</v>
+        <v>40.02</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>36.83</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-105.97</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>209340330.3376068</t>
+          <t>209725872.4715505</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>216663540.0</t>
+          <t>320250967.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>226931349.2</v>
+        <v>251858830.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>252085881.0</t>
+          <t>253830312.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>403055695.96</v>
+        <v>402572081.14</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-25154531</t>
+          <t>-1971482</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-33416919.66615964</t>
+          <t>-31113388.87961073</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-26739307.99942577</t>
+          <t>-18443969.5535917</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>216663540.0</t>
+          <t>320250967.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>43.86</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>46714</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>39.15</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>40.5</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>40.65</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
           <t>39.1</t>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8360.012</t>
+          <t>5475.163</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-21.99</t>
+          <t>-9.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>71.05</t>
+          <t>71.65</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>39.32000000000001</t>
+          <t>39.34</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>39.45</v>
+        <v>39.38</v>
       </c>
       <c r="AN3" t="n">
-        <v>40.13</v>
+        <v>40.07</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>39.84</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>29.60</t>
+          <t>20.85</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.28</t>
+          <t>-105.97</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>209340330.3376068</t>
+          <t>209725872.4715505</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>335087983.0</t>
+          <t>216663540.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>221270073.6</v>
+        <v>226931349.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>283648466.2</t>
+          <t>252085881.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>409053915.06</v>
+        <v>403055695.96</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-62378392</t>
+          <t>-25154531</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-34631030.87829307</t>
+          <t>-33416919.66615964</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-26536163.31492347</t>
+          <t>-26739307.99942577</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>335087983.0</t>
+          <t>216663540.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>45.31</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>46714</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4713.942</t>
+          <t>8360.012</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-17.78</t>
+          <t>-21.99</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
           <t>71.05</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>48.25</t>
-        </is>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>38.91</t>
+          <t>39.32000000000001</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>39.48</v>
+        <v>39.45</v>
       </c>
       <c r="AN4" t="n">
-        <v>40.15</v>
+        <v>40.13</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>39.84</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>29.60</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.75</t>
+          <t>-106.28</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>209340330.3376068</t>
+          <t>209725872.4715505</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>185634245.0</t>
+          <t>335087983.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>225419918.6</v>
+        <v>221270073.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>274182342.8</t>
+          <t>283648466.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>413674654.36</v>
+        <v>409053915.06</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-48762424</t>
+          <t>-62378392</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-36102824.98072391</t>
+          <t>-34631030.87829307</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-37986569.68295866</t>
+          <t>-26536163.31492347</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>185634245.0</t>
+          <t>335087983.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>42.78</t>
+          <t>45.31</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>46714</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5128.692</t>
+          <t>4713.942</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-10.64</t>
+          <t>-17.78</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,32 +2304,32 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>71.05</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2339,33 +2339,33 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>38.91</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>39.53</v>
+        <v>39.48</v>
       </c>
       <c r="AN5" t="n">
-        <v>40.2</v>
+        <v>40.15</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-19.58</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.73</t>
+          <t>-106.75</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>209340330.3376068</t>
+          <t>209725872.4715505</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>201657416.0</t>
+          <t>185634245.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>252360977.6</v>
+        <v>225419918.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>282417854.9</t>
+          <t>274182342.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>423553251.3</v>
+        <v>413674654.36</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-30056877</t>
+          <t>-48762424</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-35760325.94395395</t>
+          <t>-36102824.98072391</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-36974729.3629033</t>
+          <t>-37986569.68295866</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>201657416.0</t>
+          <t>185634245.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>42.78</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>46714</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5013.788</t>
+          <t>5128.692</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-10.48</t>
+          <t>-10.64</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,63 +2734,63 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>39.04000000000001</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>39.71</v>
+        <v>39.53</v>
       </c>
       <c r="AN6" t="n">
-        <v>40.26</v>
+        <v>40.2</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-27.08</t>
+          <t>-19.58</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.40</t>
+          <t>-106.73</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>209340330.3376068</t>
+          <t>209725872.4715505</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>195613562.0</t>
+          <t>201657416.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>255801795.6</v>
+        <v>252360977.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>285762642.3</t>
+          <t>282417854.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>457544220.78</v>
+        <v>423553251.3</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-29960846</t>
+          <t>-30056877</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-35539525.3223268</t>
+          <t>-35760325.94395395</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-35925485.46414912</t>
+          <t>-36974729.3629033</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>195613562.0</t>
+          <t>201657416.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>46714</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4826.572</t>
+          <t>5013.788</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-10.48</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>39.16</t>
+          <t>39.04000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>39.91</v>
+        <v>39.71</v>
       </c>
       <c r="AN7" t="n">
-        <v>40.4</v>
+        <v>40.26</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-27.86</t>
+          <t>-27.08</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.97</t>
+          <t>-106.40</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>209340330.3376068</t>
+          <t>209725872.4715505</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>188357162.0</t>
+          <t>195613562.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>277240412.8</v>
+        <v>255801795.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>297413036.7</t>
+          <t>285762642.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>528814161.92</v>
+        <v>457544220.78</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-20172623</t>
+          <t>-29960846</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-35469350.75108638</t>
+          <t>-35539525.3223268</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-32495956.77078068</t>
+          <t>-35925485.46414912</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>188357162.0</t>
+          <t>195613562.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>46714</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9258.407</t>
+          <t>4826.572</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.16</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>39.94</v>
+        <v>39.91</v>
       </c>
       <c r="AN8" t="n">
-        <v>40.53</v>
+        <v>40.4</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-32.78</t>
+          <t>-27.86</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.55</t>
+          <t>-105.97</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>209340330.3376068</t>
+          <t>209725872.4715505</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>355837208.0</t>
+          <t>188357162.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>346026858.8</v>
+        <v>277240412.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>290442567.6</t>
+          <t>297413036.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>558638708.96</v>
+        <v>528814161.92</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>55584291</t>
+          <t>-20172623</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-36009967.83841468</t>
+          <t>-35469350.75108638</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-25658588.75272644</t>
+          <t>-32495956.77078068</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>355837208.0</t>
+          <t>188357162.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>46714</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7921.053</t>
+          <t>9258.407</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>19.14</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>39.93</v>
+        <v>39.94</v>
       </c>
       <c r="AN9" t="n">
-        <v>40.66</v>
+        <v>40.53</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>38.97</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-32.78</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.10</t>
+          <t>-105.55</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>209340330.3376068</t>
+          <t>209725872.4715505</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>320339540.0</t>
+          <t>355837208.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>322944767</v>
+        <v>346026858.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>273188557.9</t>
+          <t>290442567.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>613979125.7</v>
+        <v>558638708.96</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>49756209</t>
+          <t>55584291</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-37892036.76308528</t>
+          <t>-36009967.83841468</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-32918832.62862295</t>
+          <t>-25658588.75272644</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>320339540.0</t>
+          <t>355837208.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>46714</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5612.57</t>
+          <t>7921.053</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>18.21</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,42 +4454,42 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>51.71</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -4498,24 +4498,24 @@
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>39.85</v>
+        <v>39.93</v>
       </c>
       <c r="AN10" t="n">
-        <v>40.74</v>
+        <v>40.66</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>38.97</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-26.63</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-105.13</t>
+          <t>-105.10</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>209340330.3376068</t>
+          <t>209725872.4715505</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>218861506.0</t>
+          <t>320339540.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>312474732.2</v>
+        <v>322944767</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>262014209.7</t>
+          <t>273188557.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>631667121.9400001</v>
+        <v>613979125.7</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>50460522</t>
+          <t>49756209</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-38796255.69662388</t>
+          <t>-37892036.76308528</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-38311615.42888141</t>
+          <t>-32918832.62862295</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>218861506.0</t>
+          <t>320339540.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>46714</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7632.447</t>
+          <t>5612.57</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>39.83</v>
+        <v>39.85</v>
       </c>
       <c r="AN11" t="n">
-        <v>40.77</v>
+        <v>40.74</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>38.66</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-23.20</t>
+          <t>-26.63</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.79</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>209340330.3376068</t>
+          <t>209725872.4715505</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>302806648.0</t>
+          <t>218861506.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>315723489</v>
+        <v>312474732.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>267936291.1</t>
+          <t>262014209.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>654424013.3</v>
+        <v>631667121.9400001</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>47787197</t>
+          <t>50460522</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-38884372.1089407</t>
+          <t>-38796255.69662388</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-33774672.37821913</t>
+          <t>-38311615.42888141</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>302806648.0</t>
+          <t>218861506.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>46714</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>38.5</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>39.1</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>40.45</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>38.85</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>39.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13085.646</t>
+          <t>7632.447</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.70</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,63 +5314,63 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>42.31</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>41.19</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>39.57000000000001</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>39.78</v>
+        <v>39.83</v>
       </c>
       <c r="AN12" t="n">
-        <v>40.87</v>
+        <v>40.77</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.66</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-28.47</t>
+          <t>-23.20</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.51</t>
+          <t>-104.79</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>209340330.3376068</t>
+          <t>209725872.4715505</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>532289392.0</t>
+          <t>302806648.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>317585660.6</v>
+        <v>315723489</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>263274442.8</t>
+          <t>267936291.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>673739372.28</v>
+        <v>654424013.3</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>54311217</t>
+          <t>47787197</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-39813408.42361735</t>
+          <t>-38884372.1089407</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-35081209.22090816</t>
+          <t>-33774672.37821913</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>532289392.0</t>
+          <t>302806648.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>42.24</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>46714</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>234435.298</t>
+          <t>234676.835</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>14.59</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>69.58</t>
+          <t>69.65</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,12 +5744,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1,154</t>
+          <t>1,253</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>234435</t>
+          <t>234677</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5759,63 +5759,63 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>94.09</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>11.31</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>55.96</t>
+          <t>58.36</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>51.28</v>
+        <v>52.43</v>
       </c>
       <c r="AN13" t="n">
-        <v>44.97</v>
+        <v>45.5</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>43.28</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>21.62</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
@@ -5830,48 +5830,48 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1408524930.754273</t>
+          <t>1438585437.375533</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>14435017956.0</t>
+          <t>15027374057.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>9601919709.4</v>
+        <v>11258543327.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>8984258387.6</t>
+          <t>9097515316.1</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>4361742818</v>
+        <v>4638106412.14</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>617661321</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>809145707.6861923</t>
+          <t>892069972.3655224</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>1096502955.845938</t>
+          <t>1348153428.101837</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>14435017956.0</t>
+          <t>15027374057.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>45.82</t>
+          <t>53.70</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5936,17 +5936,17 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>484573</t>
+          <t>510745</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5991,27 +5991,27 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右上上市</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>61.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>252999.258</t>
+          <t>234435.298</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-12.69</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>75.09</t>
+          <t>69.58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1,154</t>
+          <t>1,253</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>234435</t>
+          <t>234677</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,68 +6189,68 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>60.75</t>
+          <t>94.09</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>13.06</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>55.96</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>50.29</v>
+        <v>51.28</v>
       </c>
       <c r="AN14" t="n">
-        <v>44.48</v>
+        <v>44.97</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>42.98</t>
+          <t>43.28</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,48 +6260,48 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1408524930.754273</t>
+          <t>1438585437.375533</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>14894089882.0</t>
+          <t>14435017956.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>7684941519.2</v>
+        <v>9601919709.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>8801421193.5</t>
+          <t>8984258387.6</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>4102103371.86</v>
+        <v>4361742818</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-1116479674</t>
+          <t>617661321</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>756898935.2935112</t>
+          <t>809145707.6861923</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>761308186.4501514</t>
+          <t>1096502955.845938</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>14894089882.0</t>
+          <t>14435017956.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>40.81</t>
+          <t>45.82</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>484573</t>
+          <t>510745</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6421,27 +6421,27 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右上上市</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>153271.208</t>
+          <t>252999.258</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,74 +6488,74 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>8.39</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-12.69</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>56.2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>8.02</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-34.41</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>56.2</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
       <c r="T15" t="inlineStr">
         <is>
           <t>45.3</t>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>45.49</t>
+          <t>75.09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,83 +6604,83 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1,154</t>
+          <t>1,253</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>234435</t>
+          <t>234677</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>82.26</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>60.75</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>13.06</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>49.42</v>
+        <v>50.29</v>
       </c>
       <c r="AN15" t="n">
-        <v>44.05</v>
+        <v>44.48</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>42.71</t>
+          <t>42.98</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-8.82</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,48 +6690,48 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1408524930.754273</t>
+          <t>1438585437.375533</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>8423612196.0</t>
+          <t>14894089882.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>5638461114.4</v>
+        <v>7684941519.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>8596752401.4</t>
+          <t>8801421193.5</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>3818531527.48</v>
+        <v>4102103371.86</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-1116479674</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>756097253.2650311</t>
+          <t>756898935.2935112</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>206082660.0115242</t>
+          <t>761308186.4501514</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>8423612196.0</t>
+          <t>14894089882.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>34.13</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>484573</t>
+          <t>510745</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6851,27 +6851,27 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右上上市</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6893,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>68850.257</t>
+          <t>153271.208</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,87 +6918,87 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>12.73</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-34.41</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
           <t>51.1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>16.37</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-36.14</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>45.49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,83 +7034,83 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1,154</t>
+          <t>1,253</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>234435</t>
+          <t>234677</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>82.26</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>9.80</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>53.48</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>48.7</v>
+        <v>49.42</v>
       </c>
       <c r="AN16" t="n">
-        <v>43.68</v>
+        <v>44.05</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>42.71</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,24 +7120,24 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1408524930.754273</t>
+          <t>1438585437.375533</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>3512622548.0</t>
+          <t>8423612196.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>6095469315</v>
+        <v>5638461114.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>9544851503.2</t>
+          <t>8596752401.4</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>3663541757.9</v>
+        <v>3818531527.48</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7146,22 +7146,22 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>856099906.5838505</t>
+          <t>756097253.2650311</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>98808707.88450241</t>
+          <t>206082660.0115242</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>3512622548.0</t>
+          <t>8423612196.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>34.13</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>484573</t>
+          <t>510745</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7281,27 +7281,27 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右上上市</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7323,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>126477.283</t>
+          <t>68850.257</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>14.24</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-30.86</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,12 +7464,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1,154</t>
+          <t>1,253</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>234435</t>
+          <t>234677</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7479,53 +7479,53 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>9.80</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>53.48</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>48.25</v>
+        <v>48.7</v>
       </c>
       <c r="AN17" t="n">
-        <v>43.41</v>
+        <v>43.68</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,24 +7550,24 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1408524930.754273</t>
+          <t>1438585437.375533</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>6744255965.0</t>
+          <t>3512622548.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>6936487304.4</v>
+        <v>6095469315</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>10032139013.4</t>
+          <t>9544851503.2</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>3632131847.42</v>
+        <v>3663541757.9</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7576,17 +7576,17 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>993789215.4382774</t>
+          <t>856099906.5838505</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>468208784.7071676</t>
+          <t>98808707.88450241</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>6744255965.0</t>
+          <t>3512622548.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>484573</t>
+          <t>510745</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7711,27 +7711,27 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右上上市</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>89940.447</t>
+          <t>126477.283</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>18.63</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-15.62</t>
+          <t>-30.86</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>26.69</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,83 +7894,83 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1,154</t>
+          <t>1,253</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>234435</t>
+          <t>234677</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>73.89</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>47.74</v>
+        <v>48.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>43.12</v>
+        <v>43.41</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>42.21</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>21.20</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-8.66</t>
+          <t>-11.30</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1408524930.754273</t>
+          <t>1438585437.375533</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>4850127005.0</t>
+          <t>6744255965.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>8366597065.8</v>
+        <v>6936487304.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>9915210649.5</t>
+          <t>10032139013.4</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>3525171118.12</v>
+        <v>3632131847.42</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-1548613583</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1089349293.753025</t>
+          <t>993789215.4382774</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>632955000.321434</t>
+          <t>468208784.7071676</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>4850127005.0</t>
+          <t>6744255965.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>30.79</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>484573</t>
+          <t>510745</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8141,27 +8141,27 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右上上市</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>87722.137</t>
+          <t>89940.447</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>14.91</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>-15.62</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>20.97</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.69</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,83 +8324,83 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1,154</t>
+          <t>1,253</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>234435</t>
+          <t>234677</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>73.89</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>15.21</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>55.34</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>47.15</v>
+        <v>47.74</v>
       </c>
       <c r="AN19" t="n">
-        <v>42.8</v>
+        <v>43.12</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.97</t>
+          <t>42.21</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>21.20</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-13.50</t>
+          <t>-13.60</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1408524930.754273</t>
+          <t>1438585437.375533</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>4661687858.0</t>
+          <t>4850127005.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>9917900867.799999</v>
+        <v>8366597065.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>9646311981.3</t>
+          <t>9915210649.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>3483979320.62</v>
+        <v>3525171118.12</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>271588886</t>
+          <t>-1548613583</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1172330074.37695</t>
+          <t>1089349293.753025</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>1048643589.758906</t>
+          <t>632955000.321434</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>4661687858.0</t>
+          <t>4850127005.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>30.79</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>484573</t>
+          <t>510745</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8571,27 +8571,27 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右上上市</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>187213.322</t>
+          <t>87722.137</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>18.48</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>22.40</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,83 +8754,83 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1,154</t>
+          <t>1,253</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>234435</t>
+          <t>234677</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>95.02</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>90.43</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>17.38</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>55.96</t>
+          <t>55.34</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>46.69</v>
+        <v>47.15</v>
       </c>
       <c r="AN20" t="n">
-        <v>42.52</v>
+        <v>42.8</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>41.97</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>45.57</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-19.67</t>
+          <t>-18.18</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1408524930.754273</t>
+          <t>1438585437.375533</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>10708653199.0</t>
+          <t>4661687858.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>11555043688.4</v>
+        <v>9917900867.799999</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>9440522375.4</t>
+          <t>9646311981.3</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>3413291777.02</v>
+        <v>3483979320.62</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>2114521313</t>
+          <t>271588886</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1194818526.125685</t>
+          <t>1172330074.37695</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>1625222783.642477</t>
+          <t>1048643589.758906</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>10708653199.0</t>
+          <t>4661687858.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>35.08</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>484573</t>
+          <t>510745</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9001,27 +9001,27 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右上上市</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>141242.686</t>
+          <t>187213.322</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.11</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>53.41</t>
+          <t>22.40</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,83 +9184,83 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1,154</t>
+          <t>1,253</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>234435</t>
+          <t>234677</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>76.27</t>
+          <t>95.02</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>92.09</t>
+          <t>90.43</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>55.96</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>45.98</v>
+        <v>46.69</v>
       </c>
       <c r="AN21" t="n">
-        <v>42.16</v>
+        <v>42.52</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>41.49</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>45.57</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-28.82</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1408524930.754273</t>
+          <t>1438585437.375533</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>7717712495.0</t>
+          <t>10708653199.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>12994233691.4</v>
+        <v>11555043688.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>8470087592.9</t>
+          <t>9440522375.4</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>3233128694.92</v>
+        <v>3413291777.02</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>2114521313</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1116563206.577178</t>
+          <t>1194818526.125685</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>1742974531.810349</t>
+          <t>1625222783.642477</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>7717712495.0</t>
+          <t>10708653199.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>28.40</t>
+          <t>35.08</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>484573</t>
+          <t>510745</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9431,27 +9431,27 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右上上市</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="CG21" t="inlineStr">
+        <is>
           <t>56.6</t>
-        </is>
-      </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>56.8</t>
-        </is>
-      </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="CG21" t="inlineStr">
-        <is>
-          <t>53.8</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>237895.796</t>
+          <t>141242.686</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>16.46</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>67.79</t>
+          <t>53.41</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>70.60</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,83 +9614,83 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1,154</t>
+          <t>1,253</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>234435</t>
+          <t>234677</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.27</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.09</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>45.39</v>
+        <v>45.98</v>
       </c>
       <c r="AN22" t="n">
-        <v>41.86</v>
+        <v>42.16</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>41.49</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>77.41</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-38.63</t>
+          <t>-32.67</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,24 +9700,24 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1408524930.754273</t>
+          <t>1438585437.375533</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>13894804772.0</t>
+          <t>7717712495.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>13127790722.4</v>
+        <v>12994233691.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>7823899971.0</t>
+          <t>8470087592.9</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>3109382048.22</v>
+        <v>3233128694.92</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9726,17 +9726,17 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1002670238.352965</t>
+          <t>1116563206.577178</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>2169400157.056937</t>
+          <t>1742974531.810349</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>13894804772.0</t>
+          <t>7717712495.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>28.40</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>484573</t>
+          <t>510745</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9861,27 +9861,27 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右上上市</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>216309.874</t>
+          <t>237895.796</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>67.79</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>26.49</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>64.20</t>
+          <t>70.60</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1,154</t>
+          <t>1,253</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>234435</t>
+          <t>234677</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,63 +10064,63 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>20.30</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>44.62</v>
+        <v>45.39</v>
       </c>
       <c r="AN23" t="n">
-        <v>41.5</v>
+        <v>41.86</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.22</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>91.69</t>
+          <t>77.41</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-50.51</t>
+          <t>-41.95</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,24 +10130,24 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1408524930.754273</t>
+          <t>1438585437.375533</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>12606646015.0</t>
+          <t>13894804772.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>11463824233.2</v>
+        <v>13127790722.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>6558502593.2</t>
+          <t>7823899971.0</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>2879764455.78</v>
+        <v>3109382048.22</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10156,17 +10156,17 @@
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>790537525.8613333</t>
+          <t>1002670238.352965</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>2039269729.264316</t>
+          <t>2169400157.056937</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>12606646015.0</t>
+          <t>13894804772.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>484573</t>
+          <t>510745</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10291,27 +10291,27 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右上上市</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/酚醛樹脂.xlsx
+++ b/Result/checksun_type/酚醛樹脂.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8001.481</t>
+          <t>14517.521</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>13.34</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>12.99</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>68.29</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>39.38</v>
+        <v>39.42</v>
       </c>
       <c r="AN2" t="n">
-        <v>40.02</v>
+        <v>39.99</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>40.27</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>36.83</t>
+          <t>50.22</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-104.86</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>209725872.4715505</t>
+          <t>210690735.2620739</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>320250967.0</t>
+          <t>592659518.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>251858830.2</v>
+        <v>330059250.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>253830312.9</t>
+          <t>291210114.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>402572081.14</v>
+        <v>402478507.04</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1971482</t>
+          <t>38849136</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-31113388.87961073</t>
+          <t>-25056789.37161956</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-18443969.5535917</t>
+          <t>8254507.922331929</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>320250967.0</t>
+          <t>592659518.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>47.81</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5475.163</t>
+          <t>8001.481</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-9.98</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>80.49</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>71.65</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>39.34</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="AM3" t="n">
         <v>39.38</v>
       </c>
       <c r="AN3" t="n">
-        <v>40.07</v>
+        <v>40.02</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>36.83</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-105.97</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>209725872.4715505</t>
+          <t>210690735.2620739</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>216663540.0</t>
+          <t>320250967.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>226931349.2</v>
+        <v>251858830.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>252085881.0</t>
+          <t>253830312.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>403055695.96</v>
+        <v>402572081.14</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-25154531</t>
+          <t>-1971482</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-33416919.66615964</t>
+          <t>-31113388.87961073</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-26739307.99942577</t>
+          <t>-18443969.5535917</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>216663540.0</t>
+          <t>320250967.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>43.86</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>47.81</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,14 +1696,14 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>39.15</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>40.5</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>40.65</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
           <t>39.1</t>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8360.012</t>
+          <t>5475.163</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-21.99</t>
+          <t>-9.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>71.05</t>
+          <t>71.65</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>39.32000000000001</t>
+          <t>39.34</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>39.45</v>
+        <v>39.38</v>
       </c>
       <c r="AN4" t="n">
-        <v>40.13</v>
+        <v>40.07</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>39.84</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>29.60</t>
+          <t>20.85</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.28</t>
+          <t>-105.97</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>209725872.4715505</t>
+          <t>210690735.2620739</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>335087983.0</t>
+          <t>216663540.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>221270073.6</v>
+        <v>226931349.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>283648466.2</t>
+          <t>252085881.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>409053915.06</v>
+        <v>403055695.96</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-62378392</t>
+          <t>-25154531</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-34631030.87829307</t>
+          <t>-33416919.66615964</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-26536163.31492347</t>
+          <t>-26739307.99942577</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>335087983.0</t>
+          <t>216663540.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>45.31</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>47.81</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4713.942</t>
+          <t>8360.012</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-17.78</t>
+          <t>-21.99</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
           <t>71.05</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>48.25</t>
-        </is>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>38.91</t>
+          <t>39.32000000000001</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>39.48</v>
+        <v>39.45</v>
       </c>
       <c r="AN5" t="n">
-        <v>40.15</v>
+        <v>40.13</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>39.84</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>29.60</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.75</t>
+          <t>-106.28</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>209725872.4715505</t>
+          <t>210690735.2620739</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>185634245.0</t>
+          <t>335087983.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>225419918.6</v>
+        <v>221270073.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>274182342.8</t>
+          <t>283648466.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>413674654.36</v>
+        <v>409053915.06</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-48762424</t>
+          <t>-62378392</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-36102824.98072391</t>
+          <t>-34631030.87829307</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-37986569.68295866</t>
+          <t>-26536163.31492347</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>185634245.0</t>
+          <t>335087983.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>42.78</t>
+          <t>45.31</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>47.81</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5128.692</t>
+          <t>4713.942</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-10.64</t>
+          <t>-17.78</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,32 +2734,32 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>71.05</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2769,33 +2769,33 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>38.91</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>39.53</v>
+        <v>39.48</v>
       </c>
       <c r="AN6" t="n">
-        <v>40.2</v>
+        <v>40.15</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-19.58</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.73</t>
+          <t>-106.75</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>209725872.4715505</t>
+          <t>210690735.2620739</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>201657416.0</t>
+          <t>185634245.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>252360977.6</v>
+        <v>225419918.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>282417854.9</t>
+          <t>274182342.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>423553251.3</v>
+        <v>413674654.36</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-30056877</t>
+          <t>-48762424</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-35760325.94395395</t>
+          <t>-36102824.98072391</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-36974729.3629033</t>
+          <t>-37986569.68295866</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>201657416.0</t>
+          <t>185634245.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>42.78</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>47.81</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5013.788</t>
+          <t>5128.692</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-10.48</t>
+          <t>-10.64</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,63 +3164,63 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>39.04000000000001</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>39.71</v>
+        <v>39.53</v>
       </c>
       <c r="AN7" t="n">
-        <v>40.26</v>
+        <v>40.2</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-27.08</t>
+          <t>-19.58</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.40</t>
+          <t>-106.73</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>209725872.4715505</t>
+          <t>210690735.2620739</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>195613562.0</t>
+          <t>201657416.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>255801795.6</v>
+        <v>252360977.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>285762642.3</t>
+          <t>282417854.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>457544220.78</v>
+        <v>423553251.3</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-29960846</t>
+          <t>-30056877</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-35539525.3223268</t>
+          <t>-35760325.94395395</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-35925485.46414912</t>
+          <t>-36974729.3629033</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>195613562.0</t>
+          <t>201657416.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>47.81</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4826.572</t>
+          <t>5013.788</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-10.48</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>39.16</t>
+          <t>39.04000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>39.91</v>
+        <v>39.71</v>
       </c>
       <c r="AN8" t="n">
-        <v>40.4</v>
+        <v>40.26</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-27.86</t>
+          <t>-27.08</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.97</t>
+          <t>-106.40</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>209725872.4715505</t>
+          <t>210690735.2620739</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>188357162.0</t>
+          <t>195613562.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>277240412.8</v>
+        <v>255801795.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>297413036.7</t>
+          <t>285762642.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>528814161.92</v>
+        <v>457544220.78</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-20172623</t>
+          <t>-29960846</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-35469350.75108638</t>
+          <t>-35539525.3223268</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-32495956.77078068</t>
+          <t>-35925485.46414912</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>188357162.0</t>
+          <t>195613562.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>47.81</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9258.407</t>
+          <t>4826.572</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.16</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>39.94</v>
+        <v>39.91</v>
       </c>
       <c r="AN9" t="n">
-        <v>40.53</v>
+        <v>40.4</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-32.78</t>
+          <t>-27.86</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.55</t>
+          <t>-105.97</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>209725872.4715505</t>
+          <t>210690735.2620739</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>355837208.0</t>
+          <t>188357162.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>346026858.8</v>
+        <v>277240412.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>290442567.6</t>
+          <t>297413036.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>558638708.96</v>
+        <v>528814161.92</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>55584291</t>
+          <t>-20172623</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-36009967.83841468</t>
+          <t>-35469350.75108638</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-25658588.75272644</t>
+          <t>-32495956.77078068</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>355837208.0</t>
+          <t>188357162.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>47.81</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7921.053</t>
+          <t>9258.407</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>19.14</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>39.93</v>
+        <v>39.94</v>
       </c>
       <c r="AN10" t="n">
-        <v>40.66</v>
+        <v>40.53</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>38.97</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-32.78</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-105.10</t>
+          <t>-105.55</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>209725872.4715505</t>
+          <t>210690735.2620739</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>320339540.0</t>
+          <t>355837208.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>322944767</v>
+        <v>346026858.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>273188557.9</t>
+          <t>290442567.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>613979125.7</v>
+        <v>558638708.96</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>49756209</t>
+          <t>55584291</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-37892036.76308528</t>
+          <t>-36009967.83841468</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-32918832.62862295</t>
+          <t>-25658588.75272644</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>320339540.0</t>
+          <t>355837208.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>47.81</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5612.57</t>
+          <t>7921.053</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>18.21</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,42 +4884,42 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>51.71</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -4928,24 +4928,24 @@
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>39.85</v>
+        <v>39.93</v>
       </c>
       <c r="AN11" t="n">
-        <v>40.74</v>
+        <v>40.66</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>38.97</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-26.63</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-105.13</t>
+          <t>-105.10</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>209725872.4715505</t>
+          <t>210690735.2620739</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>218861506.0</t>
+          <t>320339540.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>312474732.2</v>
+        <v>322944767</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>262014209.7</t>
+          <t>273188557.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>631667121.9400001</v>
+        <v>613979125.7</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>50460522</t>
+          <t>49756209</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-38796255.69662388</t>
+          <t>-37892036.76308528</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-38311615.42888141</t>
+          <t>-32918832.62862295</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>218861506.0</t>
+          <t>320339540.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>47.81</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7632.447</t>
+          <t>5612.57</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>39.83</v>
+        <v>39.85</v>
       </c>
       <c r="AN12" t="n">
-        <v>40.77</v>
+        <v>40.74</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>38.66</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-23.20</t>
+          <t>-26.63</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.79</t>
+          <t>-105.13</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>209725872.4715505</t>
+          <t>210690735.2620739</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>302806648.0</t>
+          <t>218861506.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>315723489</v>
+        <v>312474732.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>267936291.1</t>
+          <t>262014209.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>654424013.3</v>
+        <v>631667121.9400001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>47787197</t>
+          <t>50460522</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-38884372.1089407</t>
+          <t>-38796255.69662388</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-33774672.37821913</t>
+          <t>-38311615.42888141</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>302806648.0</t>
+          <t>218861506.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>47.81</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>38.5</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>39.1</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>40.45</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>38.85</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>39.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>234676.835</t>
+          <t>262513.069</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>67.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>39.52</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>20.46</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>69.65</t>
+          <t>77.91</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,12 +5744,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1,253</t>
+          <t>1,344</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>234677</t>
+          <t>262513</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5764,58 +5764,58 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>16.58</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>58.36</t>
+          <t>61.68000000000001</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>52.43</v>
+        <v>53.77</v>
       </c>
       <c r="AN13" t="n">
-        <v>45.5</v>
+        <v>46.12</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>21.62</t>
+          <t>28.24</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
@@ -5830,24 +5830,24 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1438585437.375533</t>
+          <t>1473877052.744318</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>15027374057.0</t>
+          <t>17522588438.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>11258543327.8</v>
+        <v>14060536505.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>9097515316.1</t>
+          <t>10078002910.4</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>4638106412.14</v>
+        <v>4962930311.1</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5856,22 +5856,22 @@
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>892069972.3655224</t>
+          <t>1012943207.625199</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>1348153428.101837</t>
+          <t>1677746001.553423</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>15027374057.0</t>
+          <t>17522588438.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>53.70</t>
+          <t>61.58</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5936,17 +5936,17 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>510745</t>
+          <t>536917</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>61.5</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>67.7</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>234435.298</t>
+          <t>234676.835</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>14.59</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>69.58</t>
+          <t>69.65</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1,253</t>
+          <t>1,344</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>234677</t>
+          <t>262513</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,68 +6189,68 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>94.09</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>11.31</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>55.96</t>
+          <t>58.36</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>51.28</v>
+        <v>52.43</v>
       </c>
       <c r="AN14" t="n">
-        <v>44.97</v>
+        <v>45.5</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>43.28</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>21.62</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-7.06</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,48 +6260,48 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1438585437.375533</t>
+          <t>1473877052.744318</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>14435017956.0</t>
+          <t>15027374057.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>9601919709.4</v>
+        <v>11258543327.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>8984258387.6</t>
+          <t>9097515316.1</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>4361742818</v>
+        <v>4638106412.14</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>617661321</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>809145707.6861923</t>
+          <t>892069972.3655224</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>1096502955.845938</t>
+          <t>1348153428.101837</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>14435017956.0</t>
+          <t>15027374057.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>45.82</t>
+          <t>53.70</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6366,17 +6366,17 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>510745</t>
+          <t>536917</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>61.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>252999.258</t>
+          <t>234435.298</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-12.69</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>75.09</t>
+          <t>69.58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,12 +6604,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1,253</t>
+          <t>1,344</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>234677</t>
+          <t>262513</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6619,68 +6619,68 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>60.75</t>
+          <t>94.09</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>13.06</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>55.96</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>50.29</v>
+        <v>51.28</v>
       </c>
       <c r="AN15" t="n">
-        <v>44.48</v>
+        <v>44.97</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>42.98</t>
+          <t>43.28</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-8.82</t>
+          <t>-12.08</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,48 +6690,48 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1438585437.375533</t>
+          <t>1473877052.744318</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>14894089882.0</t>
+          <t>14435017956.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>7684941519.2</v>
+        <v>9601919709.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>8801421193.5</t>
+          <t>8984258387.6</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>4102103371.86</v>
+        <v>4361742818</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-1116479674</t>
+          <t>617661321</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>756898935.2935112</t>
+          <t>809145707.6861923</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>761308186.4501514</t>
+          <t>1096502955.845938</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>14894089882.0</t>
+          <t>14435017956.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>40.81</t>
+          <t>45.82</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>510745</t>
+          <t>536917</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>153271.208</t>
+          <t>252999.258</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,74 +6918,74 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>12.85</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-12.69</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>56.2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>12.73</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-34.41</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-12-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>56.2</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
       <c r="T16" t="inlineStr">
         <is>
           <t>45.3</t>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>45.49</t>
+          <t>75.09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,83 +7034,83 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1,253</t>
+          <t>1,344</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>234677</t>
+          <t>262513</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>82.26</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>60.75</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>13.06</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>49.42</v>
+        <v>50.29</v>
       </c>
       <c r="AN16" t="n">
-        <v>44.05</v>
+        <v>44.48</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>42.71</t>
+          <t>42.98</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-15.26</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,48 +7120,48 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1438585437.375533</t>
+          <t>1473877052.744318</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>8423612196.0</t>
+          <t>14894089882.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>5638461114.4</v>
+        <v>7684941519.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>8596752401.4</t>
+          <t>8801421193.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>3818531527.48</v>
+        <v>4102103371.86</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-1116479674</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>756097253.2650311</t>
+          <t>756898935.2935112</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>206082660.0115242</t>
+          <t>761308186.4501514</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>8423612196.0</t>
+          <t>14894089882.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>34.13</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>510745</t>
+          <t>536917</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7323,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>68850.257</t>
+          <t>153271.208</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,87 +7348,87 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>16.99</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-34.41</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
           <t>51.1</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>20.65</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-36.14</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-12-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>45.49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,83 +7464,83 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1,253</t>
+          <t>1,344</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>234677</t>
+          <t>262513</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>82.26</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>9.80</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>53.48</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>48.7</v>
+        <v>49.42</v>
       </c>
       <c r="AN17" t="n">
-        <v>43.68</v>
+        <v>44.05</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>42.71</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-17.06</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,24 +7550,24 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1438585437.375533</t>
+          <t>1473877052.744318</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>3512622548.0</t>
+          <t>8423612196.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>6095469315</v>
+        <v>5638461114.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>9544851503.2</t>
+          <t>8596752401.4</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>3663541757.9</v>
+        <v>3818531527.48</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7576,22 +7576,22 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>856099906.5838505</t>
+          <t>756097253.2650311</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>98808707.88450241</t>
+          <t>206082660.0115242</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>3512622548.0</t>
+          <t>8423612196.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>34.13</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>510745</t>
+          <t>536917</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7753,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>126477.283</t>
+          <t>68850.257</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>24.52</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-30.86</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,12 +7894,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1,253</t>
+          <t>1,344</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>234677</t>
+          <t>262513</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7909,53 +7909,53 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>9.80</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>53.48</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>48.25</v>
+        <v>48.7</v>
       </c>
       <c r="AN18" t="n">
-        <v>43.41</v>
+        <v>43.68</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -7965,12 +7965,12 @@
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-11.30</t>
+          <t>-17.59</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,24 +7980,24 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1438585437.375533</t>
+          <t>1473877052.744318</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>6744255965.0</t>
+          <t>3512622548.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>6936487304.4</v>
+        <v>6095469315</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>10032139013.4</t>
+          <t>9544851503.2</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>3632131847.42</v>
+        <v>3663541757.9</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8006,17 +8006,17 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>993789215.4382774</t>
+          <t>856099906.5838505</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>468208784.7071676</t>
+          <t>98808707.88450241</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>6744255965.0</t>
+          <t>3512622548.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>510745</t>
+          <t>536917</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>89940.447</t>
+          <t>126477.283</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-15.62</t>
+          <t>-30.86</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>26.69</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,83 +8324,83 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1,253</t>
+          <t>1,344</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>234677</t>
+          <t>262513</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>73.89</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>47.74</v>
+        <v>48.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>43.12</v>
+        <v>43.41</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>42.21</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>21.20</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-13.60</t>
+          <t>-17.56</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1438585437.375533</t>
+          <t>1473877052.744318</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>4850127005.0</t>
+          <t>6744255965.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>8366597065.8</v>
+        <v>6936487304.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>9915210649.5</t>
+          <t>10032139013.4</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>3525171118.12</v>
+        <v>3632131847.42</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-1548613583</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1089349293.753025</t>
+          <t>993789215.4382774</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>632955000.321434</t>
+          <t>468208784.7071676</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>4850127005.0</t>
+          <t>6744255965.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>30.79</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>510745</t>
+          <t>536917</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>56.4</t>
         </is>